--- a/BRISAS/EXPENSAS/2026/OCTUBRE/BRISAS-OCTUBRE.xlsx
+++ b/BRISAS/EXPENSAS/2026/OCTUBRE/BRISAS-OCTUBRE.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\USUARIOS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BRISAS\EXPENSAS\2026\OCTUBRE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F63367-3AF2-4AA8-A32E-3D304B4D0B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F70762F-278F-40BC-8030-737BC0520334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="504">
   <si>
     <t>Dpto.</t>
   </si>
@@ -1310,9 +1310,6 @@
     <t>Pamela Ronsisky</t>
   </si>
   <si>
-    <t>28(?)</t>
-  </si>
-  <si>
     <t>Creo lote 28 deposito $600.000 el 14/10</t>
   </si>
   <si>
@@ -1554,12 +1551,6 @@
   </si>
   <si>
     <t>Multa mal cobrada L77</t>
-  </si>
-  <si>
-    <t>PENDIENTE</t>
-  </si>
-  <si>
-    <t>PENDIENTE PONER LA MULTA AL 79</t>
   </si>
 </sst>
 </file>
@@ -2444,7 +2435,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="432">
+  <cellXfs count="431">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -2925,49 +2916,23 @@
     </xf>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="27" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="27" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="12" fillId="24" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="24" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="27" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3029,36 +2994,54 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="17" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3117,10 +3100,27 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3154,26 +3154,12 @@
     <xf numFmtId="6" fontId="0" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="27" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="27" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="24" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="24" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="27" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="33" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3568,34 +3554,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="363"/>
-      <c r="B1" s="358" t="s">
+      <c r="A1" s="355"/>
+      <c r="B1" s="350" t="s">
         <v>155</v>
       </c>
-      <c r="C1" s="359"/>
-      <c r="D1" s="359"/>
-      <c r="E1" s="360"/>
+      <c r="C1" s="351"/>
+      <c r="D1" s="351"/>
+      <c r="E1" s="352"/>
     </row>
     <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="364"/>
-      <c r="B2" s="358" t="s">
+      <c r="A2" s="356"/>
+      <c r="B2" s="350" t="s">
         <v>157</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="360"/>
+      <c r="C2" s="351"/>
+      <c r="D2" s="351"/>
+      <c r="E2" s="352"/>
     </row>
     <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="364"/>
-      <c r="B3" s="375" t="s">
+      <c r="A3" s="356"/>
+      <c r="B3" s="367" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="376"/>
-      <c r="D3" s="376"/>
-      <c r="E3" s="377"/>
+      <c r="C3" s="368"/>
+      <c r="D3" s="368"/>
+      <c r="E3" s="369"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="364"/>
+      <c r="A4" s="356"/>
       <c r="B4" s="258" t="s">
         <v>154</v>
       </c>
@@ -3604,16 +3590,16 @@
       <c r="E4" s="259"/>
     </row>
     <row r="5" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="364"/>
+      <c r="A5" s="356"/>
       <c r="B5" s="260" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C5" s="261"/>
       <c r="D5" s="261"/>
       <c r="E5" s="262"/>
     </row>
     <row r="6" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="364"/>
+      <c r="A6" s="356"/>
       <c r="B6" s="263" t="s">
         <v>280</v>
       </c>
@@ -3622,7 +3608,7 @@
       <c r="E6" s="262"/>
     </row>
     <row r="7" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="364"/>
+      <c r="A7" s="356"/>
       <c r="B7" s="263" t="s">
         <v>279</v>
       </c>
@@ -3631,13 +3617,13 @@
       <c r="E7" s="262"/>
     </row>
     <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="365"/>
-      <c r="B8" s="361" t="s">
+      <c r="A8" s="357"/>
+      <c r="B8" s="353" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="361"/>
-      <c r="D8" s="361"/>
-      <c r="E8" s="362"/>
+      <c r="C8" s="353"/>
+      <c r="D8" s="353"/>
+      <c r="E8" s="354"/>
     </row>
     <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
@@ -3647,27 +3633,27 @@
       <c r="E9" s="27"/>
     </row>
     <row r="10" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="366" t="s">
-        <v>438</v>
-      </c>
-      <c r="B10" s="367"/>
-      <c r="C10" s="367"/>
-      <c r="D10" s="367"/>
-      <c r="E10" s="368"/>
+      <c r="A10" s="358" t="s">
+        <v>437</v>
+      </c>
+      <c r="B10" s="359"/>
+      <c r="C10" s="359"/>
+      <c r="D10" s="359"/>
+      <c r="E10" s="360"/>
     </row>
     <row r="11" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="369"/>
-      <c r="B11" s="370"/>
-      <c r="C11" s="370"/>
-      <c r="D11" s="370"/>
-      <c r="E11" s="371"/>
+      <c r="A11" s="361"/>
+      <c r="B11" s="362"/>
+      <c r="C11" s="362"/>
+      <c r="D11" s="362"/>
+      <c r="E11" s="363"/>
     </row>
     <row r="12" spans="1:5" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="372"/>
-      <c r="B12" s="373"/>
-      <c r="C12" s="373"/>
-      <c r="D12" s="373"/>
-      <c r="E12" s="374"/>
+      <c r="A12" s="364"/>
+      <c r="B12" s="365"/>
+      <c r="C12" s="365"/>
+      <c r="D12" s="365"/>
+      <c r="E12" s="366"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="27"/>
@@ -3684,34 +3670,34 @@
       <c r="E14" s="27"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="353" t="s">
+      <c r="A15" s="370" t="s">
         <v>238</v>
       </c>
-      <c r="B15" s="353"/>
-      <c r="C15" s="353"/>
-      <c r="D15" s="353"/>
-      <c r="E15" s="353"/>
+      <c r="B15" s="370"/>
+      <c r="C15" s="370"/>
+      <c r="D15" s="370"/>
+      <c r="E15" s="370"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="353"/>
-      <c r="B16" s="353"/>
-      <c r="C16" s="353"/>
-      <c r="D16" s="353"/>
-      <c r="E16" s="353"/>
+      <c r="A16" s="370"/>
+      <c r="B16" s="370"/>
+      <c r="C16" s="370"/>
+      <c r="D16" s="370"/>
+      <c r="E16" s="370"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="353"/>
-      <c r="B17" s="353"/>
-      <c r="C17" s="353"/>
-      <c r="D17" s="353"/>
-      <c r="E17" s="353"/>
+      <c r="A17" s="370"/>
+      <c r="B17" s="370"/>
+      <c r="C17" s="370"/>
+      <c r="D17" s="370"/>
+      <c r="E17" s="370"/>
     </row>
     <row r="18" spans="1:8" ht="243" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="353"/>
-      <c r="B18" s="353"/>
-      <c r="C18" s="353"/>
-      <c r="D18" s="353"/>
-      <c r="E18" s="353"/>
+      <c r="A18" s="370"/>
+      <c r="B18" s="370"/>
+      <c r="C18" s="370"/>
+      <c r="D18" s="370"/>
+      <c r="E18" s="370"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="27"/>
@@ -3758,7 +3744,7 @@
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="152" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B24" s="254"/>
       <c r="C24" s="19"/>
@@ -3770,10 +3756,10 @@
       <c r="G24" s="211"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="354" t="s">
-        <v>441</v>
-      </c>
-      <c r="B25" s="355"/>
+      <c r="A25" s="371" t="s">
+        <v>440</v>
+      </c>
+      <c r="B25" s="372"/>
       <c r="C25" s="19"/>
       <c r="D25" s="222">
         <v>-501641.09</v>
@@ -3783,10 +3769,10 @@
       <c r="G25" s="212"/>
     </row>
     <row r="26" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="356" t="s">
-        <v>442</v>
-      </c>
-      <c r="B26" s="357"/>
+      <c r="A26" s="373" t="s">
+        <v>441</v>
+      </c>
+      <c r="B26" s="374"/>
       <c r="C26" s="19"/>
       <c r="D26" s="222">
         <v>0</v>
@@ -3811,16 +3797,16 @@
       <c r="H27" s="61"/>
     </row>
     <row r="28" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="342" t="s">
+      <c r="A28" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="B28" s="343"/>
+      <c r="B28" s="349"/>
       <c r="C28" s="19"/>
       <c r="D28" s="335">
         <v>2450000</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F28" s="27"/>
       <c r="G28" s="212">
@@ -3869,7 +3855,7 @@
     </row>
     <row r="32" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B32" s="19"/>
       <c r="C32" s="85"/>
@@ -3885,7 +3871,7 @@
     </row>
     <row r="33" spans="1:9" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="86" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>11</v>
@@ -3965,10 +3951,10 @@
       <c r="G37" s="27"/>
     </row>
     <row r="38" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="342" t="s">
+      <c r="A38" s="347" t="s">
         <v>266</v>
       </c>
-      <c r="B38" s="343"/>
+      <c r="B38" s="349"/>
       <c r="C38" s="19"/>
       <c r="D38" s="163">
         <v>198615</v>
@@ -3980,10 +3966,10 @@
       <c r="G38" s="27"/>
     </row>
     <row r="39" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="342" t="s">
+      <c r="A39" s="347" t="s">
         <v>267</v>
       </c>
-      <c r="B39" s="343"/>
+      <c r="B39" s="349"/>
       <c r="C39" s="19"/>
       <c r="D39" s="163">
         <v>0</v>
@@ -3993,10 +3979,10 @@
       <c r="G39" s="27"/>
     </row>
     <row r="40" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="342" t="s">
+      <c r="A40" s="347" t="s">
         <v>304</v>
       </c>
-      <c r="B40" s="343"/>
+      <c r="B40" s="349"/>
       <c r="C40" s="234"/>
       <c r="D40" s="163">
         <v>26214.080000000002</v>
@@ -4008,10 +3994,10 @@
       <c r="G40" s="27"/>
     </row>
     <row r="41" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="342" t="s">
+      <c r="A41" s="347" t="s">
         <v>304</v>
       </c>
-      <c r="B41" s="343"/>
+      <c r="B41" s="349"/>
       <c r="C41" s="19"/>
       <c r="D41" s="163">
         <v>23573.47</v>
@@ -4048,16 +4034,16 @@
       <c r="G43" s="27"/>
     </row>
     <row r="44" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="342" t="s">
-        <v>500</v>
-      </c>
-      <c r="B44" s="344"/>
+      <c r="A44" s="347" t="s">
+        <v>499</v>
+      </c>
+      <c r="B44" s="348"/>
       <c r="C44" s="89"/>
       <c r="D44" s="334">
         <v>50982563.840000004</v>
       </c>
       <c r="E44" s="65" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F44" s="215">
         <f>D44</f>
@@ -4067,16 +4053,16 @@
       <c r="I44" s="34"/>
     </row>
     <row r="45" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="342" t="s">
-        <v>450</v>
-      </c>
-      <c r="B45" s="344"/>
+      <c r="A45" s="347" t="s">
+        <v>449</v>
+      </c>
+      <c r="B45" s="348"/>
       <c r="C45" s="89"/>
       <c r="D45" s="334">
         <v>6101488.7999999998</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F45" s="215"/>
       <c r="G45" s="27"/>
@@ -4109,25 +4095,25 @@
       <c r="G47" s="27"/>
     </row>
     <row r="48" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="342" t="s">
+      <c r="A48" s="347" t="s">
         <v>371</v>
       </c>
-      <c r="B48" s="344"/>
+      <c r="B48" s="348"/>
       <c r="C48" s="89"/>
       <c r="D48" s="334">
         <v>1472058.6</v>
       </c>
       <c r="E48" s="26" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F48" s="27"/>
       <c r="G48" s="27"/>
     </row>
     <row r="49" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="342" t="s">
+      <c r="A49" s="347" t="s">
         <v>356</v>
       </c>
-      <c r="B49" s="344"/>
+      <c r="B49" s="348"/>
       <c r="C49" s="89"/>
       <c r="D49" s="163">
         <v>890281.7</v>
@@ -4139,25 +4125,25 @@
       <c r="G49" s="27"/>
     </row>
     <row r="50" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="342" t="s">
-        <v>455</v>
-      </c>
-      <c r="B50" s="344"/>
+      <c r="A50" s="347" t="s">
+        <v>454</v>
+      </c>
+      <c r="B50" s="348"/>
       <c r="C50" s="89"/>
       <c r="D50" s="334">
         <v>32757.119999999999</v>
       </c>
       <c r="E50" s="26" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F50" s="27"/>
       <c r="G50" s="27"/>
     </row>
     <row r="51" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="342" t="s">
+      <c r="A51" s="347" t="s">
         <v>383</v>
       </c>
-      <c r="B51" s="344"/>
+      <c r="B51" s="348"/>
       <c r="C51" s="89"/>
       <c r="D51" s="163">
         <v>913550</v>
@@ -4169,10 +4155,10 @@
       <c r="G51" s="27"/>
     </row>
     <row r="52" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="342" t="s">
+      <c r="A52" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="B52" s="344"/>
+      <c r="B52" s="348"/>
       <c r="C52" s="89"/>
       <c r="D52" s="163">
         <v>756250</v>
@@ -4184,25 +4170,25 @@
       <c r="G52" s="27"/>
     </row>
     <row r="53" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="342" t="s">
-        <v>486</v>
-      </c>
-      <c r="B53" s="343"/>
+      <c r="A53" s="347" t="s">
+        <v>485</v>
+      </c>
+      <c r="B53" s="349"/>
       <c r="C53" s="90"/>
       <c r="D53" s="334">
         <v>7500000</v>
       </c>
       <c r="E53" s="220" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F53" s="27"/>
       <c r="G53" s="27"/>
     </row>
     <row r="54" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="342" t="s">
+      <c r="A54" s="347" t="s">
         <v>380</v>
       </c>
-      <c r="B54" s="343"/>
+      <c r="B54" s="349"/>
       <c r="C54" s="90"/>
       <c r="D54" s="163">
         <v>700000</v>
@@ -4214,10 +4200,10 @@
       <c r="G54" s="27"/>
     </row>
     <row r="55" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="342" t="s">
-        <v>445</v>
-      </c>
-      <c r="B55" s="343"/>
+      <c r="A55" s="347" t="s">
+        <v>444</v>
+      </c>
+      <c r="B55" s="349"/>
       <c r="C55" s="90"/>
       <c r="D55" s="163">
         <v>228690</v>
@@ -4229,10 +4215,10 @@
       <c r="G55" s="27"/>
     </row>
     <row r="56" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="342" t="s">
+      <c r="A56" s="347" t="s">
         <v>373</v>
       </c>
-      <c r="B56" s="343"/>
+      <c r="B56" s="349"/>
       <c r="C56" s="90"/>
       <c r="D56" s="163">
         <v>325668</v>
@@ -4244,10 +4230,10 @@
       <c r="G56" s="27"/>
     </row>
     <row r="57" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="342" t="s">
+      <c r="A57" s="347" t="s">
         <v>374</v>
       </c>
-      <c r="B57" s="343"/>
+      <c r="B57" s="349"/>
       <c r="C57" s="90"/>
       <c r="D57" s="163">
         <v>943800</v>
@@ -4259,10 +4245,10 @@
       <c r="G57" s="27"/>
     </row>
     <row r="58" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="342" t="s">
+      <c r="A58" s="347" t="s">
         <v>396</v>
       </c>
-      <c r="B58" s="343"/>
+      <c r="B58" s="349"/>
       <c r="C58" s="90"/>
       <c r="D58" s="163">
         <v>0</v>
@@ -4272,25 +4258,25 @@
       <c r="G58" s="27"/>
     </row>
     <row r="59" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="342" t="s">
-        <v>496</v>
-      </c>
-      <c r="B59" s="343"/>
+      <c r="A59" s="347" t="s">
+        <v>495</v>
+      </c>
+      <c r="B59" s="349"/>
       <c r="C59" s="90"/>
       <c r="D59" s="334">
         <v>120000</v>
       </c>
       <c r="E59" s="66" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F59" s="27"/>
       <c r="G59" s="27"/>
     </row>
     <row r="60" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="342" t="s">
+      <c r="A60" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="B60" s="343"/>
+      <c r="B60" s="349"/>
       <c r="C60" s="90"/>
       <c r="D60" s="163">
         <v>360000</v>
@@ -4302,10 +4288,10 @@
       <c r="G60" s="27"/>
     </row>
     <row r="61" spans="1:7" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="342" t="s">
+      <c r="A61" s="347" t="s">
         <v>379</v>
       </c>
-      <c r="B61" s="343"/>
+      <c r="B61" s="349"/>
       <c r="C61" s="90"/>
       <c r="D61" s="163">
         <v>480000</v>
@@ -4317,10 +4303,10 @@
       <c r="G61" s="27"/>
     </row>
     <row r="62" spans="1:7" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="342" t="s">
+      <c r="A62" s="347" t="s">
         <v>385</v>
       </c>
-      <c r="B62" s="343"/>
+      <c r="B62" s="349"/>
       <c r="C62" s="90"/>
       <c r="D62" s="163">
         <v>480000</v>
@@ -4332,10 +4318,10 @@
       <c r="G62" s="27"/>
     </row>
     <row r="63" spans="1:7" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="342" t="s">
+      <c r="A63" s="347" t="s">
         <v>399</v>
       </c>
-      <c r="B63" s="343"/>
+      <c r="B63" s="349"/>
       <c r="C63" s="90"/>
       <c r="D63" s="163">
         <v>360000</v>
@@ -4347,10 +4333,10 @@
       <c r="G63" s="27"/>
     </row>
     <row r="64" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="342" t="s">
+      <c r="A64" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="B64" s="343"/>
+      <c r="B64" s="349"/>
       <c r="C64" s="90"/>
       <c r="D64" s="163">
         <v>150000</v>
@@ -4362,31 +4348,31 @@
       <c r="G64" s="27"/>
     </row>
     <row r="65" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="342" t="s">
-        <v>446</v>
-      </c>
-      <c r="B65" s="343"/>
+      <c r="A65" s="347" t="s">
+        <v>445</v>
+      </c>
+      <c r="B65" s="349"/>
       <c r="C65" s="90"/>
       <c r="D65" s="334">
         <v>1600000</v>
       </c>
       <c r="E65" s="66" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F65" s="27"/>
       <c r="G65" s="27"/>
     </row>
     <row r="66" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="342" t="s">
-        <v>462</v>
-      </c>
-      <c r="B66" s="343"/>
+      <c r="A66" s="347" t="s">
+        <v>461</v>
+      </c>
+      <c r="B66" s="349"/>
       <c r="C66" s="19"/>
       <c r="D66" s="334">
         <v>2877995</v>
       </c>
       <c r="E66" s="66" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F66" s="27"/>
       <c r="G66" s="216"/>
@@ -4418,11 +4404,11 @@
       <c r="G68" s="27"/>
     </row>
     <row r="69" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="342" t="s">
+      <c r="A69" s="347" t="s">
         <v>359</v>
       </c>
-      <c r="B69" s="344"/>
-      <c r="C69" s="343"/>
+      <c r="B69" s="348"/>
+      <c r="C69" s="349"/>
       <c r="D69" s="264">
         <v>1798000</v>
       </c>
@@ -4433,10 +4419,10 @@
       <c r="G69" s="27"/>
     </row>
     <row r="70" spans="1:8" ht="166.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="342" t="s">
+      <c r="A70" s="347" t="s">
         <v>394</v>
       </c>
-      <c r="B70" s="344"/>
+      <c r="B70" s="348"/>
       <c r="C70" s="252"/>
       <c r="D70" s="264">
         <v>1900000</v>
@@ -4448,10 +4434,10 @@
       <c r="G70" s="27"/>
     </row>
     <row r="71" spans="1:8" ht="149.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="342" t="s">
+      <c r="A71" s="347" t="s">
         <v>395</v>
       </c>
-      <c r="B71" s="344"/>
+      <c r="B71" s="348"/>
       <c r="C71" s="252"/>
       <c r="D71" s="264">
         <v>2000000</v>
@@ -4463,11 +4449,11 @@
       <c r="G71" s="27"/>
     </row>
     <row r="72" spans="1:8" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="342" t="s">
+      <c r="A72" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="B72" s="344"/>
-      <c r="C72" s="343"/>
+      <c r="B72" s="348"/>
+      <c r="C72" s="349"/>
       <c r="D72" s="264">
         <v>1922000</v>
       </c>
@@ -4478,41 +4464,41 @@
       <c r="G72" s="27"/>
     </row>
     <row r="73" spans="1:8" ht="91.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="342" t="s">
-        <v>453</v>
-      </c>
-      <c r="B73" s="344"/>
-      <c r="C73" s="343"/>
+      <c r="A73" s="347" t="s">
+        <v>452</v>
+      </c>
+      <c r="B73" s="348"/>
+      <c r="C73" s="349"/>
       <c r="D73" s="336">
         <v>2570000</v>
       </c>
       <c r="E73" s="337" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F73" s="27"/>
       <c r="G73" s="27"/>
     </row>
     <row r="74" spans="1:8" ht="91.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="342" t="s">
-        <v>487</v>
-      </c>
-      <c r="B74" s="344"/>
-      <c r="C74" s="343"/>
+      <c r="A74" s="347" t="s">
+        <v>486</v>
+      </c>
+      <c r="B74" s="348"/>
+      <c r="C74" s="349"/>
       <c r="D74" s="336">
         <v>4500000</v>
       </c>
       <c r="E74" s="338" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F74" s="27"/>
       <c r="G74" s="27"/>
     </row>
     <row r="75" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="342" t="s">
-        <v>479</v>
-      </c>
-      <c r="B75" s="344"/>
-      <c r="C75" s="343"/>
+      <c r="A75" s="347" t="s">
+        <v>478</v>
+      </c>
+      <c r="B75" s="348"/>
+      <c r="C75" s="349"/>
       <c r="D75" s="336">
         <v>2000000</v>
       </c>
@@ -4523,25 +4509,25 @@
       <c r="G75" s="27"/>
     </row>
     <row r="76" spans="1:8" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="342" t="s">
-        <v>463</v>
-      </c>
-      <c r="B76" s="343"/>
+      <c r="A76" s="347" t="s">
+        <v>462</v>
+      </c>
+      <c r="B76" s="349"/>
       <c r="C76" s="19"/>
       <c r="D76" s="336">
         <v>13500000</v>
       </c>
       <c r="E76" s="338" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F76" s="27"/>
       <c r="G76" s="27"/>
     </row>
     <row r="77" spans="1:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="342" t="s">
+      <c r="A77" s="347" t="s">
         <v>378</v>
       </c>
-      <c r="B77" s="343"/>
+      <c r="B77" s="349"/>
       <c r="C77" s="86"/>
       <c r="D77" s="264">
         <v>130000</v>
@@ -4553,10 +4539,10 @@
       <c r="G77" s="27"/>
     </row>
     <row r="78" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="342" t="s">
+      <c r="A78" s="347" t="s">
         <v>355</v>
       </c>
-      <c r="B78" s="343"/>
+      <c r="B78" s="349"/>
       <c r="C78" s="86"/>
       <c r="D78" s="264">
         <v>350000</v>
@@ -4568,10 +4554,10 @@
       <c r="G78" s="27"/>
     </row>
     <row r="79" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="342" t="s">
+      <c r="A79" s="347" t="s">
         <v>368</v>
       </c>
-      <c r="B79" s="343"/>
+      <c r="B79" s="349"/>
       <c r="C79" s="86"/>
       <c r="D79" s="264">
         <v>36500</v>
@@ -4583,25 +4569,25 @@
       <c r="G79" s="27"/>
     </row>
     <row r="80" spans="1:8" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="342" t="s">
-        <v>477</v>
-      </c>
-      <c r="B80" s="343"/>
+      <c r="A80" s="347" t="s">
+        <v>476</v>
+      </c>
+      <c r="B80" s="349"/>
       <c r="C80" s="86"/>
       <c r="D80" s="336">
         <v>605784.14</v>
       </c>
       <c r="E80" s="129" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F80" s="216"/>
       <c r="G80" s="27"/>
     </row>
     <row r="81" spans="1:7" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="342" t="s">
+      <c r="A81" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="B81" s="343"/>
+      <c r="B81" s="349"/>
       <c r="C81" s="86"/>
       <c r="D81" s="264">
         <v>365000</v>
@@ -4613,10 +4599,10 @@
       <c r="G81" s="27"/>
     </row>
     <row r="82" spans="1:7" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="342" t="s">
+      <c r="A82" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="B82" s="343"/>
+      <c r="B82" s="349"/>
       <c r="C82" s="86"/>
       <c r="D82" s="264">
         <v>34010</v>
@@ -4628,10 +4614,10 @@
       <c r="G82" s="27"/>
     </row>
     <row r="83" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="342" t="s">
+      <c r="A83" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="B83" s="343"/>
+      <c r="B83" s="349"/>
       <c r="C83" s="86"/>
       <c r="D83" s="264">
         <v>363000</v>
@@ -4643,100 +4629,100 @@
       <c r="G83" s="27"/>
     </row>
     <row r="84" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="342" t="s">
-        <v>466</v>
-      </c>
-      <c r="B84" s="343"/>
+      <c r="A84" s="347" t="s">
+        <v>465</v>
+      </c>
+      <c r="B84" s="349"/>
       <c r="C84" s="86"/>
       <c r="D84" s="336">
         <v>100000</v>
       </c>
       <c r="E84" s="129" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F84" s="27"/>
       <c r="G84" s="27"/>
     </row>
     <row r="85" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="342" t="s">
-        <v>467</v>
-      </c>
-      <c r="B85" s="343"/>
+      <c r="A85" s="347" t="s">
+        <v>466</v>
+      </c>
+      <c r="B85" s="349"/>
       <c r="C85" s="86"/>
       <c r="D85" s="336">
         <v>939969.03</v>
       </c>
       <c r="E85" s="129" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F85" s="27"/>
       <c r="G85" s="27"/>
     </row>
     <row r="86" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="342" t="s">
-        <v>484</v>
-      </c>
-      <c r="B86" s="343"/>
+      <c r="A86" s="347" t="s">
+        <v>483</v>
+      </c>
+      <c r="B86" s="349"/>
       <c r="C86" s="86"/>
       <c r="D86" s="336">
         <v>835644.15</v>
       </c>
       <c r="E86" s="129" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F86" s="27"/>
       <c r="G86" s="27"/>
     </row>
     <row r="87" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="342" t="s">
-        <v>468</v>
-      </c>
-      <c r="B87" s="343"/>
+      <c r="A87" s="347" t="s">
+        <v>467</v>
+      </c>
+      <c r="B87" s="349"/>
       <c r="C87" s="86"/>
       <c r="D87" s="336">
         <v>1468500</v>
       </c>
       <c r="E87" s="129" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F87" s="27"/>
       <c r="G87" s="27"/>
     </row>
     <row r="88" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="342" t="s">
-        <v>482</v>
-      </c>
-      <c r="B88" s="343"/>
+      <c r="A88" s="347" t="s">
+        <v>481</v>
+      </c>
+      <c r="B88" s="349"/>
       <c r="C88" s="86"/>
       <c r="D88" s="336">
         <v>71703.600000000006</v>
       </c>
       <c r="E88" s="129" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F88" s="27"/>
       <c r="G88" s="27"/>
     </row>
     <row r="89" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="342" t="s">
-        <v>483</v>
-      </c>
-      <c r="B89" s="343"/>
+      <c r="A89" s="347" t="s">
+        <v>482</v>
+      </c>
+      <c r="B89" s="349"/>
       <c r="C89" s="86"/>
       <c r="D89" s="336">
         <v>76916.460000000006</v>
       </c>
       <c r="E89" s="129" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F89" s="27"/>
       <c r="G89" s="27"/>
     </row>
     <row r="90" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="342" t="s">
+      <c r="A90" s="347" t="s">
         <v>354</v>
       </c>
-      <c r="B90" s="343"/>
+      <c r="B90" s="349"/>
       <c r="C90" s="86"/>
       <c r="D90" s="264">
         <v>1200000</v>
@@ -4748,85 +4734,85 @@
       <c r="G90" s="27"/>
     </row>
     <row r="91" spans="1:7" ht="271.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="342" t="s">
-        <v>493</v>
-      </c>
-      <c r="B91" s="343"/>
+      <c r="A91" s="347" t="s">
+        <v>492</v>
+      </c>
+      <c r="B91" s="349"/>
       <c r="C91" s="86"/>
       <c r="D91" s="336">
         <v>8174440</v>
       </c>
       <c r="E91" s="129" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F91" s="27"/>
       <c r="G91" s="27"/>
     </row>
     <row r="92" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="342" t="s">
-        <v>475</v>
-      </c>
-      <c r="B92" s="343"/>
+      <c r="A92" s="347" t="s">
+        <v>474</v>
+      </c>
+      <c r="B92" s="349"/>
       <c r="C92" s="86"/>
       <c r="D92" s="336">
         <v>90000</v>
       </c>
       <c r="E92" s="129" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F92" s="27"/>
       <c r="G92" s="27"/>
     </row>
     <row r="93" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="342" t="s">
-        <v>489</v>
-      </c>
-      <c r="B93" s="343"/>
+      <c r="A93" s="347" t="s">
+        <v>488</v>
+      </c>
+      <c r="B93" s="349"/>
       <c r="C93" s="86"/>
       <c r="D93" s="336">
         <v>502500.9</v>
       </c>
       <c r="E93" s="73" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F93" s="27"/>
       <c r="G93" s="27"/>
     </row>
     <row r="94" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="342" t="s">
-        <v>491</v>
-      </c>
-      <c r="B94" s="343"/>
+      <c r="A94" s="347" t="s">
+        <v>490</v>
+      </c>
+      <c r="B94" s="349"/>
       <c r="C94" s="86"/>
       <c r="D94" s="336">
         <v>57838</v>
       </c>
       <c r="E94" s="73" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F94" s="27"/>
       <c r="G94" s="27"/>
     </row>
     <row r="95" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="342" t="s">
-        <v>492</v>
-      </c>
-      <c r="B95" s="343"/>
+      <c r="A95" s="347" t="s">
+        <v>491</v>
+      </c>
+      <c r="B95" s="349"/>
       <c r="C95" s="86"/>
       <c r="D95" s="336">
         <v>260150</v>
       </c>
       <c r="E95" s="73" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F95" s="27"/>
       <c r="G95" s="27"/>
     </row>
     <row r="96" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="342" t="s">
+      <c r="A96" s="347" t="s">
         <v>390</v>
       </c>
-      <c r="B96" s="343"/>
+      <c r="B96" s="349"/>
       <c r="C96" s="86"/>
       <c r="D96" s="264">
         <v>112400</v>
@@ -4838,55 +4824,55 @@
       <c r="G96" s="27"/>
     </row>
     <row r="97" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="342" t="s">
-        <v>503</v>
-      </c>
-      <c r="B97" s="343"/>
+      <c r="A97" s="347" t="s">
+        <v>502</v>
+      </c>
+      <c r="B97" s="349"/>
       <c r="C97" s="86"/>
       <c r="D97" s="336">
         <v>162000</v>
       </c>
       <c r="E97" s="129" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F97" s="27"/>
       <c r="G97" s="27"/>
     </row>
     <row r="98" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="342" t="s">
-        <v>473</v>
-      </c>
-      <c r="B98" s="343"/>
+      <c r="A98" s="347" t="s">
+        <v>472</v>
+      </c>
+      <c r="B98" s="349"/>
       <c r="C98" s="86"/>
       <c r="D98" s="336">
         <v>37999</v>
       </c>
       <c r="E98" s="129" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F98" s="27"/>
       <c r="G98" s="27"/>
     </row>
     <row r="99" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="342" t="s">
-        <v>495</v>
-      </c>
-      <c r="B99" s="343"/>
+      <c r="A99" s="347" t="s">
+        <v>494</v>
+      </c>
+      <c r="B99" s="349"/>
       <c r="C99" s="86"/>
       <c r="D99" s="336">
         <v>1500000</v>
       </c>
       <c r="E99" s="129" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F99" s="27"/>
       <c r="G99" s="27"/>
     </row>
     <row r="100" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="342" t="s">
-        <v>478</v>
-      </c>
-      <c r="B100" s="343"/>
+      <c r="A100" s="347" t="s">
+        <v>477</v>
+      </c>
+      <c r="B100" s="349"/>
       <c r="C100" s="86"/>
       <c r="D100" s="336">
         <v>1500000</v>
@@ -4898,115 +4884,115 @@
       <c r="G100" s="27"/>
     </row>
     <row r="101" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="342" t="s">
-        <v>470</v>
-      </c>
-      <c r="B101" s="343"/>
+      <c r="A101" s="347" t="s">
+        <v>469</v>
+      </c>
+      <c r="B101" s="349"/>
       <c r="C101" s="86"/>
       <c r="D101" s="336">
         <v>1350000</v>
       </c>
       <c r="E101" s="129" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F101" s="27"/>
       <c r="G101" s="27"/>
     </row>
     <row r="102" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="342" t="s">
-        <v>465</v>
-      </c>
-      <c r="B102" s="343"/>
+      <c r="A102" s="347" t="s">
+        <v>464</v>
+      </c>
+      <c r="B102" s="349"/>
       <c r="C102" s="86"/>
       <c r="D102" s="336">
         <v>145200</v>
       </c>
       <c r="E102" s="129" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F102" s="27"/>
       <c r="G102" s="27"/>
     </row>
     <row r="103" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="342" t="s">
-        <v>481</v>
-      </c>
-      <c r="B103" s="343"/>
+      <c r="A103" s="347" t="s">
+        <v>480</v>
+      </c>
+      <c r="B103" s="349"/>
       <c r="C103" s="86"/>
       <c r="D103" s="336">
         <v>240306</v>
       </c>
       <c r="E103" s="129" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F103" s="27"/>
       <c r="G103" s="27"/>
     </row>
     <row r="104" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="342" t="s">
-        <v>472</v>
-      </c>
-      <c r="B104" s="343"/>
+      <c r="A104" s="347" t="s">
+        <v>471</v>
+      </c>
+      <c r="B104" s="349"/>
       <c r="C104" s="86"/>
       <c r="D104" s="336">
         <v>206785.71</v>
       </c>
       <c r="E104" s="73" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F104" s="27"/>
       <c r="G104" s="27"/>
     </row>
     <row r="105" spans="1:7" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="342" t="s">
-        <v>456</v>
-      </c>
-      <c r="B105" s="343"/>
+      <c r="A105" s="347" t="s">
+        <v>455</v>
+      </c>
+      <c r="B105" s="349"/>
       <c r="C105" s="86"/>
       <c r="D105" s="336">
         <v>41000</v>
       </c>
       <c r="E105" s="73" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F105" s="27"/>
       <c r="G105" s="27"/>
     </row>
     <row r="106" spans="1:7" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="342" t="s">
-        <v>497</v>
-      </c>
-      <c r="B106" s="343"/>
+      <c r="A106" s="347" t="s">
+        <v>496</v>
+      </c>
+      <c r="B106" s="349"/>
       <c r="C106" s="86"/>
       <c r="D106" s="336">
         <v>95582</v>
       </c>
       <c r="E106" s="73" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F106" s="27"/>
       <c r="G106" s="27"/>
     </row>
     <row r="107" spans="1:7" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="342" t="s">
-        <v>498</v>
-      </c>
-      <c r="B107" s="343"/>
+      <c r="A107" s="347" t="s">
+        <v>497</v>
+      </c>
+      <c r="B107" s="349"/>
       <c r="C107" s="86"/>
       <c r="D107" s="336">
         <v>480000</v>
       </c>
       <c r="E107" s="73" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F107" s="27"/>
       <c r="G107" s="27"/>
     </row>
     <row r="108" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="342" t="s">
-        <v>488</v>
-      </c>
-      <c r="B108" s="343"/>
+      <c r="A108" s="347" t="s">
+        <v>487</v>
+      </c>
+      <c r="B108" s="349"/>
       <c r="C108" s="86"/>
       <c r="D108" s="336">
         <v>322000</v>
@@ -5043,10 +5029,10 @@
       <c r="G110" s="27"/>
     </row>
     <row r="111" spans="1:7" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="342" t="s">
-        <v>447</v>
-      </c>
-      <c r="B111" s="343"/>
+      <c r="A111" s="347" t="s">
+        <v>446</v>
+      </c>
+      <c r="B111" s="349"/>
       <c r="C111" s="19"/>
       <c r="D111" s="265">
         <v>3218160</v>
@@ -5185,10 +5171,10 @@
       <c r="G122" s="27"/>
     </row>
     <row r="123" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="342" t="s">
+      <c r="A123" s="347" t="s">
         <v>352</v>
       </c>
-      <c r="B123" s="343"/>
+      <c r="B123" s="349"/>
       <c r="C123" s="19"/>
       <c r="D123" s="163">
         <v>2574957.5</v>
@@ -5203,10 +5189,10 @@
       <c r="G123" s="27"/>
     </row>
     <row r="124" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="342" t="s">
+      <c r="A124" s="347" t="s">
         <v>336</v>
       </c>
-      <c r="B124" s="343"/>
+      <c r="B124" s="349"/>
       <c r="C124" s="19"/>
       <c r="D124" s="163">
         <v>83694.649999999994</v>
@@ -5221,10 +5207,10 @@
       <c r="G124" s="27"/>
     </row>
     <row r="125" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="342" t="s">
+      <c r="A125" s="347" t="s">
         <v>337</v>
       </c>
-      <c r="B125" s="343"/>
+      <c r="B125" s="349"/>
       <c r="C125" s="19"/>
       <c r="D125" s="163">
         <v>83694.649999999994</v>
@@ -5240,10 +5226,10 @@
       <c r="G125" s="27"/>
     </row>
     <row r="126" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="342" t="s">
+      <c r="A126" s="347" t="s">
         <v>338</v>
       </c>
-      <c r="B126" s="343"/>
+      <c r="B126" s="349"/>
       <c r="C126" s="19"/>
       <c r="D126" s="163">
         <v>76773.23</v>
@@ -5259,10 +5245,10 @@
       <c r="G126" s="27"/>
     </row>
     <row r="127" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="342" t="s">
+      <c r="A127" s="347" t="s">
         <v>347</v>
       </c>
-      <c r="B127" s="343"/>
+      <c r="B127" s="349"/>
       <c r="C127" s="19"/>
       <c r="D127" s="163">
         <v>82044.789999999994</v>
@@ -5277,10 +5263,10 @@
       <c r="G127" s="27"/>
     </row>
     <row r="128" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="342" t="s">
+      <c r="A128" s="347" t="s">
         <v>339</v>
       </c>
-      <c r="B128" s="343"/>
+      <c r="B128" s="349"/>
       <c r="C128" s="19"/>
       <c r="D128" s="163">
         <v>512864.3</v>
@@ -5295,10 +5281,10 @@
       <c r="G128" s="27"/>
     </row>
     <row r="129" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="342" t="s">
+      <c r="A129" s="347" t="s">
         <v>340</v>
       </c>
-      <c r="B129" s="343"/>
+      <c r="B129" s="349"/>
       <c r="C129" s="19"/>
       <c r="D129" s="163">
         <v>1267805.3700000001</v>
@@ -5313,10 +5299,10 @@
       <c r="G129" s="27"/>
     </row>
     <row r="130" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="342" t="s">
+      <c r="A130" s="347" t="s">
         <v>341</v>
       </c>
-      <c r="B130" s="343"/>
+      <c r="B130" s="349"/>
       <c r="C130" s="19"/>
       <c r="D130" s="163">
         <v>184910.38</v>
@@ -5331,10 +5317,10 @@
       <c r="G130" s="27"/>
     </row>
     <row r="131" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="342" t="s">
+      <c r="A131" s="347" t="s">
         <v>341</v>
       </c>
-      <c r="B131" s="343"/>
+      <c r="B131" s="349"/>
       <c r="C131" s="19"/>
       <c r="D131" s="163">
         <v>227417.49</v>
@@ -5346,10 +5332,10 @@
       <c r="G131" s="27"/>
     </row>
     <row r="132" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="342" t="s">
+      <c r="A132" s="347" t="s">
         <v>406</v>
       </c>
-      <c r="B132" s="343"/>
+      <c r="B132" s="349"/>
       <c r="C132" s="19"/>
       <c r="D132" s="163">
         <v>180329.69</v>
@@ -5364,10 +5350,10 @@
       <c r="G132" s="27"/>
     </row>
     <row r="133" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="342" t="s">
+      <c r="A133" s="347" t="s">
         <v>342</v>
       </c>
-      <c r="B133" s="343"/>
+      <c r="B133" s="349"/>
       <c r="C133" s="234"/>
       <c r="D133" s="163">
         <v>282953.93</v>
@@ -5379,10 +5365,10 @@
       <c r="G133" s="27"/>
     </row>
     <row r="134" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="342" t="s">
+      <c r="A134" s="347" t="s">
         <v>343</v>
       </c>
-      <c r="B134" s="343"/>
+      <c r="B134" s="349"/>
       <c r="C134" s="19"/>
       <c r="D134" s="163">
         <v>285600.08</v>
@@ -5397,10 +5383,10 @@
       <c r="G134" s="27"/>
     </row>
     <row r="135" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="342" t="s">
+      <c r="A135" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="B135" s="343"/>
+      <c r="B135" s="349"/>
       <c r="C135" s="19"/>
       <c r="D135" s="163">
         <v>285600.08</v>
@@ -5415,25 +5401,25 @@
       <c r="G135" s="27"/>
     </row>
     <row r="136" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="345" t="s">
-        <v>458</v>
-      </c>
-      <c r="B136" s="346"/>
+      <c r="A136" s="381" t="s">
+        <v>457</v>
+      </c>
+      <c r="B136" s="382"/>
       <c r="C136" s="19"/>
       <c r="D136" s="334">
         <v>1390293.61</v>
       </c>
       <c r="E136" s="73" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F136" s="27"/>
       <c r="G136" s="27"/>
     </row>
     <row r="137" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="345" t="s">
-        <v>459</v>
-      </c>
-      <c r="B137" s="346"/>
+      <c r="A137" s="381" t="s">
+        <v>458</v>
+      </c>
+      <c r="B137" s="382"/>
       <c r="C137" s="19"/>
       <c r="D137" s="334">
         <v>467266.18</v>
@@ -5446,10 +5432,10 @@
       <c r="G137" s="27"/>
     </row>
     <row r="138" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="345" t="s">
-        <v>460</v>
-      </c>
-      <c r="B138" s="346"/>
+      <c r="A138" s="381" t="s">
+        <v>459</v>
+      </c>
+      <c r="B138" s="382"/>
       <c r="C138" s="19"/>
       <c r="D138" s="334">
         <v>127158.42</v>
@@ -5462,10 +5448,10 @@
       <c r="G138" s="27"/>
     </row>
     <row r="139" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="345" t="s">
-        <v>461</v>
-      </c>
-      <c r="B139" s="346"/>
+      <c r="A139" s="381" t="s">
+        <v>460</v>
+      </c>
+      <c r="B139" s="382"/>
       <c r="C139" s="19"/>
       <c r="D139" s="334">
         <v>94660.72</v>
@@ -5481,10 +5467,10 @@
       <c r="G139" s="27"/>
     </row>
     <row r="140" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="345" t="s">
+      <c r="A140" s="381" t="s">
         <v>189</v>
       </c>
-      <c r="B140" s="346"/>
+      <c r="B140" s="382"/>
       <c r="C140" s="19"/>
       <c r="D140" s="163">
         <v>31266.93</v>
@@ -5496,10 +5482,10 @@
       <c r="G140" s="27"/>
     </row>
     <row r="141" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="345" t="s">
+      <c r="A141" s="381" t="s">
         <v>335</v>
       </c>
-      <c r="B141" s="346"/>
+      <c r="B141" s="382"/>
       <c r="C141" s="19"/>
       <c r="D141" s="163">
         <v>9137.2099999999991</v>
@@ -5547,16 +5533,16 @@
       <c r="G144" s="27"/>
     </row>
     <row r="145" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="345" t="s">
-        <v>448</v>
-      </c>
-      <c r="B145" s="346"/>
+      <c r="A145" s="381" t="s">
+        <v>447</v>
+      </c>
+      <c r="B145" s="382"/>
       <c r="C145" s="19"/>
       <c r="D145" s="341">
         <v>9914839.9499999993</v>
       </c>
       <c r="E145" s="67" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F145" s="27"/>
       <c r="G145" s="27"/>
@@ -5637,10 +5623,10 @@
       <c r="G152" s="27"/>
     </row>
     <row r="153" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="348" t="s">
-        <v>451</v>
-      </c>
-      <c r="B153" s="348"/>
+      <c r="A153" s="376" t="s">
+        <v>450</v>
+      </c>
+      <c r="B153" s="376"/>
       <c r="C153" s="19"/>
       <c r="D153" s="334">
         <f>2886137-2450000</f>
@@ -5655,7 +5641,7 @@
     </row>
     <row r="154" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="253" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B154" s="254"/>
       <c r="C154" s="19"/>
@@ -5674,7 +5660,7 @@
     </row>
     <row r="155" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="253" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B155" s="254"/>
       <c r="C155" s="19"/>
@@ -5840,9 +5826,9 @@
       <c r="A172" s="136" t="s">
         <v>230</v>
       </c>
-      <c r="B172" s="426">
+      <c r="B172" s="345">
         <f>PRORRATEO!F161</f>
-        <v>117066792.15999998</v>
+        <v>124836840.20999998</v>
       </c>
       <c r="C172" s="137"/>
       <c r="D172" s="239"/>
@@ -5894,7 +5880,7 @@
       <c r="A177" s="119" t="s">
         <v>292</v>
       </c>
-      <c r="B177" s="425">
+      <c r="B177" s="344">
         <f>-B200</f>
         <v>-592968.33481199993</v>
       </c>
@@ -5905,7 +5891,7 @@
       <c r="A178" s="119" t="s">
         <v>387</v>
       </c>
-      <c r="B178" s="425">
+      <c r="B178" s="344">
         <f>--751000</f>
         <v>751000</v>
       </c>
@@ -5916,7 +5902,7 @@
       <c r="A179" s="119" t="s">
         <v>388</v>
       </c>
-      <c r="B179" s="425">
+      <c r="B179" s="344">
         <v>-21101</v>
       </c>
       <c r="C179" s="137"/>
@@ -5924,9 +5910,9 @@
     </row>
     <row r="180" spans="1:6" s="134" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="119" t="s">
-        <v>504</v>
-      </c>
-      <c r="B180" s="425">
+        <v>503</v>
+      </c>
+      <c r="B180" s="344">
         <v>-225800</v>
       </c>
       <c r="C180" s="137"/>
@@ -5967,7 +5953,7 @@
       <c r="A184" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="B184" s="425">
+      <c r="B184" s="344">
         <f>-E160</f>
         <v>-650606.91999999993</v>
       </c>
@@ -5979,7 +5965,7 @@
       <c r="A185" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B185" s="425">
+      <c r="B185" s="344">
         <f>-E142</f>
         <v>-8248429.21</v>
       </c>
@@ -5990,7 +5976,7 @@
       <c r="A186" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B186" s="425">
+      <c r="B186" s="344">
         <f>-E119</f>
         <v>-140860666.31</v>
       </c>
@@ -6003,7 +5989,7 @@
       <c r="A187" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="B187" s="425">
+      <c r="B187" s="344">
         <f>-E150</f>
         <v>-9914839.9499999993</v>
       </c>
@@ -6018,7 +6004,7 @@
       </c>
       <c r="B188" s="33">
         <f>SUM(B171:B187)</f>
-        <v>-15748458.280174803</v>
+        <v>-7978410.2301748209</v>
       </c>
       <c r="C188" s="5"/>
       <c r="D188" s="215"/>
@@ -6042,10 +6028,10 @@
       <c r="F190" s="63"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A191" s="351" t="s">
+      <c r="A191" s="379" t="s">
         <v>322</v>
       </c>
-      <c r="B191" s="352"/>
+      <c r="B191" s="380"/>
       <c r="C191" s="5"/>
       <c r="D191" s="215"/>
       <c r="E191" s="31"/>
@@ -6114,10 +6100,10 @@
       <c r="F197" s="63"/>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A198" s="349" t="s">
+      <c r="A198" s="377" t="s">
         <v>290</v>
       </c>
-      <c r="B198" s="350"/>
+      <c r="B198" s="378"/>
       <c r="C198" s="5"/>
       <c r="D198" s="12"/>
       <c r="E198" s="31"/>
@@ -6150,7 +6136,7 @@
     </row>
     <row r="201" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="194" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B201" s="251">
         <v>-6000</v>
@@ -6199,7 +6185,7 @@
       </c>
       <c r="B205" s="125">
         <f>B203+B188+B195</f>
-        <v>-2135883.5587520041</v>
+        <v>5634164.4912479781</v>
       </c>
       <c r="C205" s="5"/>
       <c r="D205" s="12"/>
@@ -6443,16 +6429,16 @@
       <c r="F221" s="32"/>
     </row>
     <row r="222" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A222" s="347" t="s">
+      <c r="A222" s="375" t="s">
         <v>17</v>
       </c>
-      <c r="B222" s="347"/>
-      <c r="C222" s="347"/>
+      <c r="B222" s="375"/>
+      <c r="C222" s="375"/>
     </row>
     <row r="223" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A223" s="347"/>
-      <c r="B223" s="347"/>
-      <c r="C223" s="347"/>
+      <c r="A223" s="375"/>
+      <c r="B223" s="375"/>
+      <c r="C223" s="375"/>
     </row>
     <row r="224" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="53"/>
@@ -6474,11 +6460,84 @@
     </row>
   </sheetData>
   <mergeCells count="100">
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A73:C73"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="A102:B102"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A106:B106"/>
+    <mergeCell ref="A105:B105"/>
+    <mergeCell ref="A135:B135"/>
+    <mergeCell ref="A124:B124"/>
+    <mergeCell ref="A125:B125"/>
+    <mergeCell ref="A126:B126"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="A130:B130"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="A127:B127"/>
+    <mergeCell ref="A128:B128"/>
+    <mergeCell ref="A129:B129"/>
+    <mergeCell ref="A111:B111"/>
+    <mergeCell ref="A132:B132"/>
+    <mergeCell ref="A134:B134"/>
+    <mergeCell ref="A131:B131"/>
+    <mergeCell ref="A133:B133"/>
+    <mergeCell ref="A222:C223"/>
+    <mergeCell ref="A153:B153"/>
+    <mergeCell ref="A198:B198"/>
+    <mergeCell ref="A191:B191"/>
+    <mergeCell ref="A145:B145"/>
+    <mergeCell ref="A141:B141"/>
+    <mergeCell ref="A140:B140"/>
+    <mergeCell ref="A139:B139"/>
+    <mergeCell ref="A138:B138"/>
+    <mergeCell ref="A137:B137"/>
+    <mergeCell ref="A136:B136"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A15:E18"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A1:A8"/>
+    <mergeCell ref="A10:E12"/>
+    <mergeCell ref="B3:E3"/>
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="A92:B92"/>
     <mergeCell ref="A76:B76"/>
@@ -6495,85 +6554,12 @@
     <mergeCell ref="A71:B71"/>
     <mergeCell ref="A70:B70"/>
     <mergeCell ref="A81:B81"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A1:A8"/>
-    <mergeCell ref="A10:E12"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A15:E18"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A134:B134"/>
-    <mergeCell ref="A131:B131"/>
-    <mergeCell ref="A133:B133"/>
-    <mergeCell ref="A222:C223"/>
-    <mergeCell ref="A153:B153"/>
-    <mergeCell ref="A198:B198"/>
-    <mergeCell ref="A191:B191"/>
-    <mergeCell ref="A127:B127"/>
-    <mergeCell ref="A128:B128"/>
-    <mergeCell ref="A129:B129"/>
-    <mergeCell ref="A111:B111"/>
-    <mergeCell ref="A132:B132"/>
-    <mergeCell ref="A145:B145"/>
-    <mergeCell ref="A141:B141"/>
-    <mergeCell ref="A106:B106"/>
-    <mergeCell ref="A105:B105"/>
-    <mergeCell ref="A135:B135"/>
-    <mergeCell ref="A124:B124"/>
-    <mergeCell ref="A125:B125"/>
-    <mergeCell ref="A126:B126"/>
-    <mergeCell ref="A123:B123"/>
-    <mergeCell ref="A130:B130"/>
-    <mergeCell ref="A140:B140"/>
-    <mergeCell ref="A139:B139"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="A138:B138"/>
-    <mergeCell ref="A137:B137"/>
-    <mergeCell ref="A136:B136"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A64:B64"/>
     <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A101:B101"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="A100:B100"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A74:C74"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="A104:B104"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="A102:B102"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="115" orientation="portrait" r:id="rId1"/>
@@ -6613,27 +6599,27 @@
     <row r="1" spans="1:24" ht="251.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="392" t="s">
+      <c r="C1" s="394" t="s">
         <v>334</v>
       </c>
-      <c r="D1" s="393"/>
-      <c r="E1" s="393"/>
-      <c r="F1" s="393"/>
-      <c r="G1" s="393"/>
-      <c r="H1" s="393"/>
-      <c r="I1" s="393"/>
-      <c r="J1" s="393"/>
-      <c r="K1" s="393"/>
-      <c r="L1" s="393"/>
+      <c r="D1" s="395"/>
+      <c r="E1" s="395"/>
+      <c r="F1" s="395"/>
+      <c r="G1" s="395"/>
+      <c r="H1" s="395"/>
+      <c r="I1" s="395"/>
+      <c r="J1" s="395"/>
+      <c r="K1" s="395"/>
+      <c r="L1" s="395"/>
       <c r="M1" s="128"/>
-      <c r="N1" s="394" t="s">
+      <c r="N1" s="396" t="s">
         <v>306</v>
       </c>
-      <c r="O1" s="394"/>
-      <c r="P1" s="389">
+      <c r="O1" s="396"/>
+      <c r="P1" s="391">
         <v>30000000</v>
       </c>
-      <c r="Q1" s="389"/>
+      <c r="Q1" s="391"/>
       <c r="R1" s="147"/>
       <c r="S1" s="3"/>
       <c r="T1" s="1"/>
@@ -6647,35 +6633,35 @@
     <row r="2" spans="1:24" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
-      <c r="C2" s="391" t="s">
+      <c r="C2" s="393" t="s">
         <v>225</v>
       </c>
-      <c r="D2" s="391"/>
-      <c r="E2" s="391"/>
+      <c r="D2" s="393"/>
+      <c r="E2" s="393"/>
       <c r="F2" s="128"/>
-      <c r="G2" s="386">
+      <c r="G2" s="390">
         <f>X2</f>
         <v>27518571.293111999</v>
       </c>
-      <c r="H2" s="386"/>
+      <c r="H2" s="390"/>
       <c r="I2" s="128" t="s">
         <v>272</v>
       </c>
       <c r="J2" s="128"/>
-      <c r="K2" s="386">
+      <c r="K2" s="390">
         <f>W1</f>
         <v>80675963.920000002</v>
       </c>
-      <c r="L2" s="386"/>
+      <c r="L2" s="390"/>
       <c r="M2" s="188"/>
       <c r="N2" s="189" t="s">
         <v>258</v>
       </c>
       <c r="O2" s="188"/>
-      <c r="P2" s="390">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="390"/>
+      <c r="P2" s="392">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="392"/>
       <c r="R2" s="148"/>
       <c r="T2" s="1"/>
       <c r="U2" t="s">
@@ -6687,112 +6673,112 @@
       </c>
     </row>
     <row r="3" spans="1:24" ht="91.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="399" t="str">
+      <c r="A3" s="401" t="str">
         <f>"ATENCIÓN: Si usted abona antes del " &amp; TEXT(RESUMEN!A10,"dd/mm/yyyy") &amp; ", deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste."</f>
         <v>ATENCIÓN: Si usted abona antes del Primer Vencimiento:  17/11, deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste.</v>
       </c>
-      <c r="B3" s="400"/>
-      <c r="C3" s="400"/>
-      <c r="D3" s="400"/>
-      <c r="E3" s="400"/>
-      <c r="F3" s="400"/>
-      <c r="G3" s="400"/>
-      <c r="H3" s="400"/>
-      <c r="I3" s="400"/>
-      <c r="J3" s="400"/>
-      <c r="K3" s="400"/>
-      <c r="L3" s="400"/>
-      <c r="M3" s="400"/>
-      <c r="N3" s="400"/>
-      <c r="O3" s="400"/>
-      <c r="P3" s="400"/>
-      <c r="Q3" s="400"/>
-      <c r="R3" s="400"/>
-      <c r="S3" s="400"/>
-      <c r="T3" s="401"/>
+      <c r="B3" s="402"/>
+      <c r="C3" s="402"/>
+      <c r="D3" s="402"/>
+      <c r="E3" s="402"/>
+      <c r="F3" s="402"/>
+      <c r="G3" s="402"/>
+      <c r="H3" s="402"/>
+      <c r="I3" s="402"/>
+      <c r="J3" s="402"/>
+      <c r="K3" s="402"/>
+      <c r="L3" s="402"/>
+      <c r="M3" s="402"/>
+      <c r="N3" s="402"/>
+      <c r="O3" s="402"/>
+      <c r="P3" s="402"/>
+      <c r="Q3" s="402"/>
+      <c r="R3" s="402"/>
+      <c r="S3" s="402"/>
+      <c r="T3" s="403"/>
       <c r="X3" s="34"/>
     </row>
     <row r="4" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="402" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="404" t="s">
+      <c r="A4" s="404" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="406" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="404" t="s">
+      <c r="C4" s="406" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="404" t="s">
+      <c r="D4" s="406" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="387" t="s">
+      <c r="E4" s="383" t="s">
         <v>181</v>
       </c>
-      <c r="F4" s="404" t="s">
+      <c r="F4" s="406" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="406" t="s">
+      <c r="G4" s="408" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="387" t="s">
+      <c r="H4" s="383" t="s">
         <v>231</v>
       </c>
-      <c r="I4" s="387" t="s">
+      <c r="I4" s="383" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="387"/>
-      <c r="K4" s="387" t="s">
+      <c r="J4" s="383"/>
+      <c r="K4" s="383" t="s">
         <v>182</v>
       </c>
-      <c r="L4" s="387" t="s">
+      <c r="L4" s="383" t="s">
         <v>146</v>
       </c>
-      <c r="M4" s="387" t="s">
+      <c r="M4" s="383" t="s">
         <v>184</v>
       </c>
-      <c r="N4" s="387" t="s">
+      <c r="N4" s="383" t="s">
         <v>183</v>
       </c>
-      <c r="O4" s="387" t="s">
+      <c r="O4" s="383" t="s">
         <v>316</v>
       </c>
-      <c r="P4" s="395" t="s">
+      <c r="P4" s="397" t="s">
         <v>314</v>
       </c>
-      <c r="Q4" s="396"/>
-      <c r="R4" s="395" t="s">
+      <c r="Q4" s="398"/>
+      <c r="R4" s="397" t="s">
         <v>309</v>
       </c>
-      <c r="S4" s="396"/>
-      <c r="T4" s="387" t="s">
+      <c r="S4" s="398"/>
+      <c r="T4" s="383" t="s">
         <v>256</v>
       </c>
       <c r="U4" s="12"/>
     </row>
     <row r="5" spans="1:24" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="403"/>
-      <c r="B5" s="405"/>
-      <c r="C5" s="405"/>
-      <c r="D5" s="405"/>
-      <c r="E5" s="388"/>
-      <c r="F5" s="405"/>
-      <c r="G5" s="407"/>
-      <c r="H5" s="388"/>
-      <c r="I5" s="388"/>
-      <c r="J5" s="388"/>
-      <c r="K5" s="388"/>
-      <c r="L5" s="388"/>
-      <c r="M5" s="388"/>
-      <c r="N5" s="388"/>
-      <c r="O5" s="388"/>
-      <c r="P5" s="397" t="str">
+      <c r="A5" s="405"/>
+      <c r="B5" s="407"/>
+      <c r="C5" s="407"/>
+      <c r="D5" s="407"/>
+      <c r="E5" s="384"/>
+      <c r="F5" s="407"/>
+      <c r="G5" s="409"/>
+      <c r="H5" s="384"/>
+      <c r="I5" s="384"/>
+      <c r="J5" s="384"/>
+      <c r="K5" s="384"/>
+      <c r="L5" s="384"/>
+      <c r="M5" s="384"/>
+      <c r="N5" s="384"/>
+      <c r="O5" s="384"/>
+      <c r="P5" s="399" t="str">
         <f>RESUMEN!A10</f>
         <v>Primer Vencimiento:  17/11</v>
       </c>
-      <c r="Q5" s="398"/>
-      <c r="R5" s="397"/>
-      <c r="S5" s="398"/>
-      <c r="T5" s="388"/>
+      <c r="Q5" s="400"/>
+      <c r="R5" s="399"/>
+      <c r="S5" s="400"/>
+      <c r="T5" s="384"/>
     </row>
     <row r="6" spans="1:24" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="151"/>
@@ -6808,7 +6794,7 @@
       <c r="E6" s="153">
         <v>759748.01</v>
       </c>
-      <c r="F6" s="427">
+      <c r="F6" s="346">
         <f>E6</f>
         <v>759748.01</v>
       </c>
@@ -6845,11 +6831,11 @@
       <c r="O6" s="266">
         <v>0</v>
       </c>
-      <c r="P6" s="408">
+      <c r="P6" s="385">
         <f t="shared" ref="P6:P37" si="2">ROUND(SUM(G6:O6),0) + S6</f>
         <v>759748.01</v>
       </c>
-      <c r="Q6" s="409"/>
+      <c r="Q6" s="386"/>
       <c r="R6" s="190">
         <f t="shared" ref="R6:R37" si="3">ROUND(P6+P6*3.033%,0) + S6</f>
         <v>782791.01</v>
@@ -6917,11 +6903,11 @@
       <c r="O7" s="266">
         <v>0</v>
       </c>
-      <c r="P7" s="410">
+      <c r="P7" s="387">
         <f t="shared" si="2"/>
         <v>6357990.0199999996</v>
       </c>
-      <c r="Q7" s="411"/>
+      <c r="Q7" s="388"/>
       <c r="R7" s="190">
         <f t="shared" si="3"/>
         <v>6550828.0199999996</v>
@@ -6950,7 +6936,7 @@
       <c r="E8" s="154">
         <v>737384.03</v>
       </c>
-      <c r="F8" s="423">
+      <c r="F8" s="342">
         <v>759749.03</v>
       </c>
       <c r="G8" s="46">
@@ -6986,11 +6972,11 @@
       <c r="O8" s="266">
         <v>0</v>
       </c>
-      <c r="P8" s="378">
+      <c r="P8" s="389">
         <f t="shared" si="2"/>
         <v>737383.03</v>
       </c>
-      <c r="Q8" s="378"/>
+      <c r="Q8" s="389"/>
       <c r="R8" s="190">
         <f t="shared" si="3"/>
         <v>759748.03</v>
@@ -7022,7 +7008,7 @@
       <c r="E9" s="154">
         <v>1078638.04</v>
       </c>
-      <c r="F9" s="423">
+      <c r="F9" s="342">
         <v>1079000</v>
       </c>
       <c r="G9" s="46">
@@ -7058,11 +7044,11 @@
       <c r="O9" s="266">
         <v>0</v>
       </c>
-      <c r="P9" s="378">
+      <c r="P9" s="389">
         <f t="shared" si="2"/>
         <v>767454.04</v>
       </c>
-      <c r="Q9" s="378"/>
+      <c r="Q9" s="389"/>
       <c r="R9" s="190">
         <f t="shared" si="3"/>
         <v>790731.04</v>
@@ -7095,7 +7081,7 @@
       <c r="E10" s="154">
         <v>767816.05</v>
       </c>
-      <c r="F10" s="423">
+      <c r="F10" s="342">
         <f>E10</f>
         <v>767816.05</v>
       </c>
@@ -7132,11 +7118,11 @@
       <c r="O10" s="266">
         <v>0</v>
       </c>
-      <c r="P10" s="378">
+      <c r="P10" s="389">
         <f t="shared" si="2"/>
         <v>767816.05</v>
       </c>
-      <c r="Q10" s="378"/>
+      <c r="Q10" s="389"/>
       <c r="R10" s="190">
         <f t="shared" si="3"/>
         <v>791104.05</v>
@@ -7166,7 +7152,7 @@
       <c r="E11" s="154">
         <v>751681.06</v>
       </c>
-      <c r="F11" s="424">
+      <c r="F11" s="343">
         <f>E11</f>
         <v>751681.06</v>
       </c>
@@ -7203,11 +7189,11 @@
       <c r="O11" s="266">
         <v>0</v>
       </c>
-      <c r="P11" s="378">
+      <c r="P11" s="389">
         <f t="shared" si="2"/>
         <v>751681.06</v>
       </c>
-      <c r="Q11" s="378"/>
+      <c r="Q11" s="389"/>
       <c r="R11" s="190">
         <f t="shared" si="3"/>
         <v>774480.06</v>
@@ -7239,7 +7225,7 @@
       <c r="E12" s="154">
         <v>735546.07</v>
       </c>
-      <c r="F12" s="424">
+      <c r="F12" s="343">
         <f>E12</f>
         <v>735546.07</v>
       </c>
@@ -7276,11 +7262,11 @@
       <c r="O12" s="266">
         <v>0</v>
       </c>
-      <c r="P12" s="378">
+      <c r="P12" s="389">
         <f t="shared" si="2"/>
         <v>735546.07</v>
       </c>
-      <c r="Q12" s="378"/>
+      <c r="Q12" s="389"/>
       <c r="R12" s="190">
         <f t="shared" si="3"/>
         <v>757855.07</v>
@@ -7312,7 +7298,7 @@
       <c r="E13" s="154">
         <v>767816.08</v>
       </c>
-      <c r="F13" s="424">
+      <c r="F13" s="343">
         <f>E13</f>
         <v>767816.08</v>
       </c>
@@ -7349,11 +7335,11 @@
       <c r="O13" s="266">
         <v>0</v>
       </c>
-      <c r="P13" s="378">
+      <c r="P13" s="389">
         <f t="shared" si="2"/>
         <v>767816.08</v>
       </c>
-      <c r="Q13" s="378"/>
+      <c r="Q13" s="389"/>
       <c r="R13" s="190">
         <f t="shared" si="3"/>
         <v>791104.08</v>
@@ -7421,11 +7407,11 @@
       <c r="O14" s="266">
         <v>0</v>
       </c>
-      <c r="P14" s="378">
+      <c r="P14" s="389">
         <f t="shared" si="2"/>
         <v>746257.09</v>
       </c>
-      <c r="Q14" s="378"/>
+      <c r="Q14" s="389"/>
       <c r="R14" s="190">
         <f t="shared" si="3"/>
         <v>768891.09</v>
@@ -7454,7 +7440,7 @@
       <c r="E15" s="154">
         <v>767816.1</v>
       </c>
-      <c r="F15" s="424">
+      <c r="F15" s="343">
         <f>E15</f>
         <v>767816.1</v>
       </c>
@@ -7491,11 +7477,11 @@
       <c r="O15" s="266">
         <v>0</v>
       </c>
-      <c r="P15" s="378">
+      <c r="P15" s="389">
         <f t="shared" si="2"/>
         <v>767816.1</v>
       </c>
-      <c r="Q15" s="378"/>
+      <c r="Q15" s="389"/>
       <c r="R15" s="190">
         <f t="shared" si="3"/>
         <v>791104.1</v>
@@ -7527,7 +7513,7 @@
       <c r="E16" s="154">
         <v>934803.11</v>
       </c>
-      <c r="F16" s="423">
+      <c r="F16" s="342">
         <f>963156.11</f>
         <v>963156.11</v>
       </c>
@@ -7564,11 +7550,11 @@
       <c r="O16" s="266">
         <v>0</v>
       </c>
-      <c r="P16" s="378">
+      <c r="P16" s="389">
         <f t="shared" si="2"/>
         <v>739463.11</v>
       </c>
-      <c r="Q16" s="378"/>
+      <c r="Q16" s="389"/>
       <c r="R16" s="190">
         <f t="shared" si="3"/>
         <v>761891.11</v>
@@ -7634,11 +7620,11 @@
       <c r="O17" s="266">
         <v>0</v>
       </c>
-      <c r="P17" s="378">
+      <c r="P17" s="389">
         <f t="shared" si="2"/>
         <v>7276300.1200000001</v>
       </c>
-      <c r="Q17" s="378"/>
+      <c r="Q17" s="389"/>
       <c r="R17" s="190">
         <f t="shared" si="3"/>
         <v>7496990.1200000001</v>
@@ -7670,7 +7656,7 @@
       <c r="E18" s="154">
         <v>759748.13</v>
       </c>
-      <c r="F18" s="423">
+      <c r="F18" s="342">
         <f>E18</f>
         <v>759748.13</v>
       </c>
@@ -7707,11 +7693,11 @@
       <c r="O18" s="266">
         <v>0</v>
       </c>
-      <c r="P18" s="378">
+      <c r="P18" s="389">
         <f t="shared" si="2"/>
         <v>759748.13</v>
       </c>
-      <c r="Q18" s="378"/>
+      <c r="Q18" s="389"/>
       <c r="R18" s="190">
         <f t="shared" si="3"/>
         <v>782791.13</v>
@@ -7740,7 +7726,7 @@
       <c r="E19" s="154">
         <v>767816.14</v>
       </c>
-      <c r="F19" s="424">
+      <c r="F19" s="343">
         <f>E19</f>
         <v>767816.14</v>
       </c>
@@ -7777,11 +7763,11 @@
       <c r="O19" s="266">
         <v>0</v>
       </c>
-      <c r="P19" s="378">
+      <c r="P19" s="389">
         <f t="shared" si="2"/>
         <v>767816.14</v>
       </c>
-      <c r="Q19" s="378"/>
+      <c r="Q19" s="389"/>
       <c r="R19" s="190">
         <f t="shared" si="3"/>
         <v>791104.14</v>
@@ -7849,11 +7835,11 @@
       <c r="O20" s="266">
         <v>0</v>
       </c>
-      <c r="P20" s="378">
+      <c r="P20" s="389">
         <f t="shared" si="2"/>
         <v>767581.15</v>
       </c>
-      <c r="Q20" s="378"/>
+      <c r="Q20" s="389"/>
       <c r="R20" s="190">
         <f t="shared" si="3"/>
         <v>790862.15</v>
@@ -7885,7 +7871,7 @@
       <c r="E21" s="154">
         <v>759748.16</v>
       </c>
-      <c r="F21" s="423">
+      <c r="F21" s="342">
         <f t="shared" ref="F21" si="11">E21</f>
         <v>759748.16</v>
       </c>
@@ -7922,11 +7908,11 @@
       <c r="O21" s="266">
         <v>0</v>
       </c>
-      <c r="P21" s="378">
+      <c r="P21" s="389">
         <f t="shared" si="2"/>
         <v>759748.16</v>
       </c>
-      <c r="Q21" s="378"/>
+      <c r="Q21" s="389"/>
       <c r="R21" s="190">
         <f t="shared" si="3"/>
         <v>782791.16</v>
@@ -7992,11 +7978,11 @@
       <c r="O22" s="266">
         <v>0</v>
       </c>
-      <c r="P22" s="378">
+      <c r="P22" s="389">
         <f t="shared" si="2"/>
         <v>658944.17000000004</v>
       </c>
-      <c r="Q22" s="378"/>
+      <c r="Q22" s="389"/>
       <c r="R22" s="190">
         <f t="shared" si="3"/>
         <v>678930.17</v>
@@ -8028,7 +8014,7 @@
       <c r="E23" s="155">
         <v>782791.18</v>
       </c>
-      <c r="F23" s="424">
+      <c r="F23" s="343">
         <v>782791.18</v>
       </c>
       <c r="G23" s="46">
@@ -8064,11 +8050,11 @@
       <c r="O23" s="266">
         <v>0</v>
       </c>
-      <c r="P23" s="378">
+      <c r="P23" s="389">
         <f t="shared" si="2"/>
         <v>759748.18</v>
       </c>
-      <c r="Q23" s="378"/>
+      <c r="Q23" s="389"/>
       <c r="R23" s="190">
         <f t="shared" si="3"/>
         <v>782791.18</v>
@@ -8136,11 +8122,11 @@
       <c r="O24" s="266">
         <v>0</v>
       </c>
-      <c r="P24" s="378">
+      <c r="P24" s="389">
         <f t="shared" si="2"/>
         <v>745940.19</v>
       </c>
-      <c r="Q24" s="378"/>
+      <c r="Q24" s="389"/>
       <c r="R24" s="190">
         <f t="shared" si="3"/>
         <v>768565.19</v>
@@ -8169,7 +8155,7 @@
       <c r="E25" s="154">
         <v>767816.2</v>
       </c>
-      <c r="F25" s="423">
+      <c r="F25" s="342">
         <f>E25</f>
         <v>767816.2</v>
       </c>
@@ -8206,11 +8192,11 @@
       <c r="O25" s="266">
         <v>0</v>
       </c>
-      <c r="P25" s="378">
+      <c r="P25" s="389">
         <f t="shared" si="2"/>
         <v>767816.2</v>
       </c>
-      <c r="Q25" s="378"/>
+      <c r="Q25" s="389"/>
       <c r="R25" s="190">
         <f t="shared" si="3"/>
         <v>791104.2</v>
@@ -8239,7 +8225,7 @@
       <c r="E26" s="154">
         <v>767816.21</v>
       </c>
-      <c r="F26" s="424">
+      <c r="F26" s="343">
         <f>E26</f>
         <v>767816.21</v>
       </c>
@@ -8276,11 +8262,11 @@
       <c r="O26" s="266">
         <v>0</v>
       </c>
-      <c r="P26" s="378">
+      <c r="P26" s="389">
         <f t="shared" si="2"/>
         <v>767816.21</v>
       </c>
-      <c r="Q26" s="378"/>
+      <c r="Q26" s="389"/>
       <c r="R26" s="190">
         <f t="shared" si="3"/>
         <v>791104.21</v>
@@ -8315,7 +8301,7 @@
       <c r="E27" s="154">
         <v>767816.22</v>
       </c>
-      <c r="F27" s="424">
+      <c r="F27" s="343">
         <f>E27</f>
         <v>767816.22</v>
       </c>
@@ -8352,11 +8338,11 @@
       <c r="O27" s="266">
         <v>0</v>
       </c>
-      <c r="P27" s="378">
+      <c r="P27" s="389">
         <f t="shared" si="2"/>
         <v>767816.22</v>
       </c>
-      <c r="Q27" s="378"/>
+      <c r="Q27" s="389"/>
       <c r="R27" s="190">
         <f t="shared" si="3"/>
         <v>791104.22</v>
@@ -8388,7 +8374,7 @@
       <c r="E28" s="154">
         <v>745213.23</v>
       </c>
-      <c r="F28" s="423">
+      <c r="F28" s="342">
         <v>767815</v>
       </c>
       <c r="G28" s="46">
@@ -8424,11 +8410,11 @@
       <c r="O28" s="266">
         <v>0</v>
       </c>
-      <c r="P28" s="378">
+      <c r="P28" s="389">
         <f t="shared" si="2"/>
         <v>745214.23</v>
       </c>
-      <c r="Q28" s="378"/>
+      <c r="Q28" s="389"/>
       <c r="R28" s="190">
         <f t="shared" si="3"/>
         <v>767817.23</v>
@@ -8496,11 +8482,11 @@
       <c r="O29" s="266">
         <v>0</v>
       </c>
-      <c r="P29" s="378">
+      <c r="P29" s="389">
         <f t="shared" si="2"/>
         <v>-93577.76</v>
       </c>
-      <c r="Q29" s="378"/>
+      <c r="Q29" s="389"/>
       <c r="R29" s="190">
         <f t="shared" si="3"/>
         <v>-96415.76</v>
@@ -8532,7 +8518,7 @@
       <c r="E30" s="154">
         <v>775884.25</v>
       </c>
-      <c r="F30" s="424">
+      <c r="F30" s="343">
         <f>E30</f>
         <v>775884.25</v>
       </c>
@@ -8569,11 +8555,11 @@
       <c r="O30" s="266">
         <v>0</v>
       </c>
-      <c r="P30" s="378">
+      <c r="P30" s="389">
         <f t="shared" si="2"/>
         <v>775884.25</v>
       </c>
-      <c r="Q30" s="378"/>
+      <c r="Q30" s="389"/>
       <c r="R30" s="190">
         <f t="shared" si="3"/>
         <v>799417.25</v>
@@ -8641,11 +8627,11 @@
       <c r="O31" s="266">
         <v>0</v>
       </c>
-      <c r="P31" s="378">
+      <c r="P31" s="389">
         <f t="shared" si="2"/>
         <v>775148.26</v>
       </c>
-      <c r="Q31" s="378"/>
+      <c r="Q31" s="389"/>
       <c r="R31" s="190">
         <f t="shared" si="3"/>
         <v>798659.26</v>
@@ -8714,11 +8700,11 @@
       <c r="O32" s="266">
         <v>0</v>
       </c>
-      <c r="P32" s="378">
+      <c r="P32" s="389">
         <f t="shared" si="2"/>
         <v>775884.27</v>
       </c>
-      <c r="Q32" s="378"/>
+      <c r="Q32" s="389"/>
       <c r="R32" s="190">
         <f t="shared" si="3"/>
         <v>799417.27</v>
@@ -8747,12 +8733,12 @@
       <c r="E33" s="154">
         <v>573644.28</v>
       </c>
-      <c r="F33" s="157">
-        <v>900000</v>
+      <c r="F33" s="342">
+        <v>600000</v>
       </c>
       <c r="G33" s="46">
         <f t="shared" si="0"/>
-        <v>-326355.71999999997</v>
+        <v>-26355.719999999972</v>
       </c>
       <c r="H33" s="46">
         <f t="shared" si="10"/>
@@ -8783,14 +8769,14 @@
       <c r="O33" s="266">
         <v>0</v>
       </c>
-      <c r="P33" s="378">
+      <c r="P33" s="389">
         <f t="shared" si="2"/>
-        <v>425325.28</v>
-      </c>
-      <c r="Q33" s="378"/>
+        <v>725325.28</v>
+      </c>
+      <c r="Q33" s="389"/>
       <c r="R33" s="190">
         <f t="shared" si="3"/>
-        <v>438225.28</v>
+        <v>747324.28</v>
       </c>
       <c r="S33" s="215">
         <f t="shared" si="4"/>
@@ -8819,7 +8805,7 @@
       <c r="E34" s="154">
         <v>775884.29</v>
       </c>
-      <c r="F34" s="424">
+      <c r="F34" s="343">
         <f>E34</f>
         <v>775884.29</v>
       </c>
@@ -8856,11 +8842,11 @@
       <c r="O34" s="266">
         <v>0</v>
       </c>
-      <c r="P34" s="378">
+      <c r="P34" s="389">
         <f t="shared" si="2"/>
         <v>775884.29</v>
       </c>
-      <c r="Q34" s="378"/>
+      <c r="Q34" s="389"/>
       <c r="R34" s="190">
         <f t="shared" si="3"/>
         <v>799417.29</v>
@@ -8892,7 +8878,7 @@
       <c r="E35" s="154">
         <v>751681.3</v>
       </c>
-      <c r="F35" s="424">
+      <c r="F35" s="343">
         <f>E35</f>
         <v>751681.3</v>
       </c>
@@ -8929,11 +8915,11 @@
       <c r="O35" s="266">
         <v>0</v>
       </c>
-      <c r="P35" s="378">
+      <c r="P35" s="389">
         <f t="shared" si="2"/>
         <v>751681.3</v>
       </c>
-      <c r="Q35" s="378"/>
+      <c r="Q35" s="389"/>
       <c r="R35" s="190">
         <f t="shared" si="3"/>
         <v>774480.3</v>
@@ -8965,14 +8951,16 @@
       <c r="E36" s="154">
         <v>4080719.31</v>
       </c>
-      <c r="F36" s="157"/>
+      <c r="F36" s="342">
+        <v>4104610</v>
+      </c>
       <c r="G36" s="46">
         <f t="shared" si="0"/>
-        <v>4080719.31</v>
+        <v>-23890.689999999944</v>
       </c>
       <c r="H36" s="46">
         <f t="shared" si="10"/>
-        <v>125971.80509970001</v>
+        <v>0</v>
       </c>
       <c r="I36" s="268">
         <f t="shared" si="6"/>
@@ -8999,14 +8987,14 @@
       <c r="O36" s="266">
         <v>0</v>
       </c>
-      <c r="P36" s="378">
+      <c r="P36" s="389">
         <f t="shared" si="2"/>
-        <v>4958372.3099999996</v>
-      </c>
-      <c r="Q36" s="378"/>
+        <v>727790.31</v>
+      </c>
+      <c r="Q36" s="389"/>
       <c r="R36" s="190">
         <f t="shared" si="3"/>
-        <v>5108760.3099999996</v>
+        <v>749864.31</v>
       </c>
       <c r="S36" s="215">
         <f t="shared" si="4"/>
@@ -9035,7 +9023,7 @@
       <c r="E37" s="154">
         <v>618436.31999999995</v>
       </c>
-      <c r="F37" s="423">
+      <c r="F37" s="342">
         <f>4526224.66-F21-F38-F151-F152-F154</f>
         <v>751681.32</v>
       </c>
@@ -9072,11 +9060,11 @@
       <c r="O37" s="266">
         <v>0</v>
       </c>
-      <c r="P37" s="378">
+      <c r="P37" s="389">
         <f t="shared" si="2"/>
         <v>618436.31999999995</v>
       </c>
-      <c r="Q37" s="378"/>
+      <c r="Q37" s="389"/>
       <c r="R37" s="190">
         <f t="shared" si="3"/>
         <v>637193.31999999995</v>
@@ -9104,7 +9092,7 @@
       <c r="E38" s="154">
         <v>751681.33</v>
       </c>
-      <c r="F38" s="423">
+      <c r="F38" s="342">
         <f>E38</f>
         <v>751681.33</v>
       </c>
@@ -9141,11 +9129,11 @@
       <c r="O38" s="266">
         <v>0</v>
       </c>
-      <c r="P38" s="378">
+      <c r="P38" s="389">
         <f t="shared" ref="P38:P69" si="13">ROUND(SUM(G38:O38),0) + S38</f>
         <v>751681.33</v>
       </c>
-      <c r="Q38" s="378"/>
+      <c r="Q38" s="389"/>
       <c r="R38" s="190">
         <f t="shared" ref="R38:R69" si="14">ROUND(P38+P38*3.033%,0) + S38</f>
         <v>774480.33</v>
@@ -9173,16 +9161,16 @@
       <c r="E39" s="154">
         <v>4128501.34</v>
       </c>
-      <c r="F39" s="157">
-        <v>0</v>
+      <c r="F39" s="342">
+        <v>4104610</v>
       </c>
       <c r="G39" s="46">
         <f t="shared" si="0"/>
-        <v>4128501.34</v>
+        <v>23891.339999999851</v>
       </c>
       <c r="H39" s="46">
         <f t="shared" si="10"/>
-        <v>127446.8363658</v>
+        <v>737.52566579999541</v>
       </c>
       <c r="I39" s="268">
         <f t="shared" ref="I39:I102" si="17">K$2*D39</f>
@@ -9209,14 +9197,14 @@
       <c r="O39" s="266">
         <v>0</v>
       </c>
-      <c r="P39" s="378">
+      <c r="P39" s="389">
         <f t="shared" si="13"/>
-        <v>5007629.34</v>
-      </c>
-      <c r="Q39" s="378"/>
+        <v>776310.34</v>
+      </c>
+      <c r="Q39" s="389"/>
       <c r="R39" s="190">
         <f t="shared" si="14"/>
-        <v>5159511.34</v>
+        <v>799856.34</v>
       </c>
       <c r="S39" s="215">
         <f t="shared" si="15"/>
@@ -9283,11 +9271,11 @@
       <c r="O40" s="266">
         <v>0</v>
       </c>
-      <c r="P40" s="378">
+      <c r="P40" s="389">
         <f t="shared" si="13"/>
         <v>759748.35</v>
       </c>
-      <c r="Q40" s="378"/>
+      <c r="Q40" s="389"/>
       <c r="R40" s="190">
         <f t="shared" si="14"/>
         <v>782792.35</v>
@@ -9320,7 +9308,7 @@
       <c r="E41" s="154">
         <v>732078.36</v>
       </c>
-      <c r="F41" s="423">
+      <c r="F41" s="342">
         <v>760000</v>
       </c>
       <c r="G41" s="46">
@@ -9356,11 +9344,11 @@
       <c r="O41" s="266">
         <v>0</v>
       </c>
-      <c r="P41" s="378">
+      <c r="P41" s="389">
         <f t="shared" si="13"/>
         <v>731827.36</v>
       </c>
-      <c r="Q41" s="378"/>
+      <c r="Q41" s="389"/>
       <c r="R41" s="190">
         <f t="shared" si="14"/>
         <v>754024.36</v>
@@ -9427,11 +9415,11 @@
       <c r="O42" s="266">
         <v>0</v>
       </c>
-      <c r="P42" s="378">
+      <c r="P42" s="389">
         <f t="shared" si="13"/>
         <v>775909.37</v>
       </c>
-      <c r="Q42" s="378"/>
+      <c r="Q42" s="389"/>
       <c r="R42" s="190">
         <f t="shared" si="14"/>
         <v>799443.37</v>
@@ -9462,7 +9450,7 @@
       <c r="E43" s="154">
         <v>1503064.38</v>
       </c>
-      <c r="F43" s="424">
+      <c r="F43" s="343">
         <f>E43</f>
         <v>1503064.38</v>
       </c>
@@ -9499,11 +9487,11 @@
       <c r="O43" s="266">
         <v>0</v>
       </c>
-      <c r="P43" s="378">
+      <c r="P43" s="389">
         <f t="shared" si="13"/>
         <v>751681.38</v>
       </c>
-      <c r="Q43" s="378"/>
+      <c r="Q43" s="389"/>
       <c r="R43" s="190">
         <f t="shared" si="14"/>
         <v>774480.38</v>
@@ -9536,7 +9524,7 @@
       <c r="E44" s="154">
         <v>751605.39</v>
       </c>
-      <c r="F44" s="423">
+      <c r="F44" s="342">
         <v>774500</v>
       </c>
       <c r="G44" s="46">
@@ -9572,11 +9560,11 @@
       <c r="O44" s="266">
         <v>0</v>
       </c>
-      <c r="P44" s="378">
+      <c r="P44" s="389">
         <f t="shared" si="13"/>
         <v>728786.39</v>
       </c>
-      <c r="Q44" s="378"/>
+      <c r="Q44" s="389"/>
       <c r="R44" s="190">
         <f t="shared" si="14"/>
         <v>750890.39</v>
@@ -9646,11 +9634,11 @@
       <c r="O45" s="266">
         <v>0</v>
       </c>
-      <c r="P45" s="378">
+      <c r="P45" s="389">
         <f t="shared" si="13"/>
         <v>751681.4</v>
       </c>
-      <c r="Q45" s="378"/>
+      <c r="Q45" s="389"/>
       <c r="R45" s="190">
         <f t="shared" si="14"/>
         <v>774480.4</v>
@@ -9680,7 +9668,7 @@
       <c r="E46" s="154">
         <v>751362.41</v>
       </c>
-      <c r="F46" s="424">
+      <c r="F46" s="343">
         <f>E46</f>
         <v>751362.41</v>
       </c>
@@ -9717,11 +9705,11 @@
       <c r="O46" s="266">
         <v>0</v>
       </c>
-      <c r="P46" s="378">
+      <c r="P46" s="389">
         <f t="shared" si="13"/>
         <v>751681.41</v>
       </c>
-      <c r="Q46" s="378"/>
+      <c r="Q46" s="389"/>
       <c r="R46" s="190">
         <f t="shared" si="14"/>
         <v>774480.41</v>
@@ -9754,7 +9742,7 @@
       <c r="E47" s="154">
         <v>751681.42</v>
       </c>
-      <c r="F47" s="423">
+      <c r="F47" s="342">
         <f>E47</f>
         <v>751681.42</v>
       </c>
@@ -9791,11 +9779,11 @@
       <c r="O47" s="266">
         <v>0</v>
       </c>
-      <c r="P47" s="378">
+      <c r="P47" s="389">
         <f t="shared" si="13"/>
         <v>751681.42</v>
       </c>
-      <c r="Q47" s="378"/>
+      <c r="Q47" s="389"/>
       <c r="R47" s="190">
         <f t="shared" si="14"/>
         <v>774480.42</v>
@@ -9828,7 +9816,7 @@
       <c r="E48" s="154">
         <v>679072.43</v>
       </c>
-      <c r="F48" s="423">
+      <c r="F48" s="342">
         <f>E48</f>
         <v>679072.43</v>
       </c>
@@ -9865,11 +9853,11 @@
       <c r="O48" s="266">
         <v>0</v>
       </c>
-      <c r="P48" s="378">
+      <c r="P48" s="389">
         <f t="shared" si="13"/>
         <v>679072.43</v>
       </c>
-      <c r="Q48" s="378"/>
+      <c r="Q48" s="389"/>
       <c r="R48" s="190">
         <f t="shared" si="14"/>
         <v>699669.43</v>
@@ -9933,11 +9921,11 @@
       <c r="O49" s="266">
         <v>0</v>
       </c>
-      <c r="P49" s="378">
+      <c r="P49" s="389">
         <f t="shared" si="13"/>
         <v>1267609.44</v>
       </c>
-      <c r="Q49" s="378"/>
+      <c r="Q49" s="389"/>
       <c r="R49" s="190">
         <f t="shared" si="14"/>
         <v>1306056.44</v>
@@ -9970,7 +9958,7 @@
       <c r="E50" s="154">
         <v>1695003.45</v>
       </c>
-      <c r="F50" s="423">
+      <c r="F50" s="342">
         <v>1000000.45</v>
       </c>
       <c r="G50" s="46">
@@ -10006,11 +9994,11 @@
       <c r="O50" s="266">
         <v>0</v>
       </c>
-      <c r="P50" s="378">
+      <c r="P50" s="389">
         <f t="shared" si="13"/>
         <v>1500409.45</v>
       </c>
-      <c r="Q50" s="378"/>
+      <c r="Q50" s="389"/>
       <c r="R50" s="190">
         <f t="shared" si="14"/>
         <v>1545917.45</v>
@@ -10040,7 +10028,7 @@
       <c r="E51" s="154">
         <v>1451354.46</v>
       </c>
-      <c r="F51" s="423">
+      <c r="F51" s="342">
         <v>725677.46</v>
       </c>
       <c r="G51" s="46">
@@ -10076,11 +10064,11 @@
       <c r="O51" s="266">
         <v>0</v>
       </c>
-      <c r="P51" s="378">
+      <c r="P51" s="389">
         <f t="shared" si="13"/>
         <v>1451354.46</v>
       </c>
-      <c r="Q51" s="378"/>
+      <c r="Q51" s="389"/>
       <c r="R51" s="190">
         <f t="shared" si="14"/>
         <v>1495374.46</v>
@@ -10113,7 +10101,7 @@
       <c r="E52" s="154">
         <v>1526567.47</v>
       </c>
-      <c r="F52" s="423">
+      <c r="F52" s="342">
         <v>1527000</v>
       </c>
       <c r="G52" s="46">
@@ -10149,11 +10137,11 @@
       <c r="O52" s="266">
         <v>0</v>
       </c>
-      <c r="P52" s="378">
+      <c r="P52" s="389">
         <f t="shared" si="13"/>
         <v>751248.47</v>
       </c>
-      <c r="Q52" s="378"/>
+      <c r="Q52" s="389"/>
       <c r="R52" s="190">
         <f t="shared" si="14"/>
         <v>774034.47</v>
@@ -10224,11 +10212,11 @@
       <c r="O53" s="266">
         <v>0</v>
       </c>
-      <c r="P53" s="378">
+      <c r="P53" s="389">
         <f t="shared" si="13"/>
         <v>1187332.48</v>
       </c>
-      <c r="Q53" s="378"/>
+      <c r="Q53" s="389"/>
       <c r="R53" s="190">
         <f t="shared" si="14"/>
         <v>1223344.48</v>
@@ -10259,7 +10247,7 @@
       <c r="E54" s="154">
         <v>751681.49</v>
       </c>
-      <c r="F54" s="423">
+      <c r="F54" s="342">
         <f>E54</f>
         <v>751681.49</v>
       </c>
@@ -10296,11 +10284,11 @@
       <c r="O54" s="266">
         <v>0</v>
       </c>
-      <c r="P54" s="378">
+      <c r="P54" s="389">
         <f t="shared" si="13"/>
         <v>751681.49</v>
       </c>
-      <c r="Q54" s="378"/>
+      <c r="Q54" s="389"/>
       <c r="R54" s="190">
         <f t="shared" si="14"/>
         <v>774480.49</v>
@@ -10333,7 +10321,7 @@
       <c r="E55" s="154">
         <v>751681.5</v>
       </c>
-      <c r="F55" s="424">
+      <c r="F55" s="343">
         <f>E55</f>
         <v>751681.5</v>
       </c>
@@ -10370,11 +10358,11 @@
       <c r="O55" s="266">
         <v>0</v>
       </c>
-      <c r="P55" s="378">
+      <c r="P55" s="389">
         <f t="shared" si="13"/>
         <v>751681.5</v>
       </c>
-      <c r="Q55" s="378"/>
+      <c r="Q55" s="389"/>
       <c r="R55" s="190">
         <f t="shared" si="14"/>
         <v>774480.5</v>
@@ -10443,11 +10431,11 @@
       <c r="O56" s="266">
         <v>0</v>
       </c>
-      <c r="P56" s="378">
+      <c r="P56" s="389">
         <f t="shared" si="13"/>
         <v>1527416.51</v>
       </c>
-      <c r="Q56" s="378"/>
+      <c r="Q56" s="389"/>
       <c r="R56" s="190">
         <f t="shared" si="14"/>
         <v>1573743.51</v>
@@ -10480,7 +10468,7 @@
       <c r="E57" s="154">
         <v>759748.52</v>
       </c>
-      <c r="F57" s="423">
+      <c r="F57" s="342">
         <f>E57</f>
         <v>759748.52</v>
       </c>
@@ -10517,11 +10505,11 @@
       <c r="O57" s="266">
         <v>0</v>
       </c>
-      <c r="P57" s="378">
+      <c r="P57" s="389">
         <f t="shared" si="13"/>
         <v>759748.52</v>
       </c>
-      <c r="Q57" s="378"/>
+      <c r="Q57" s="389"/>
       <c r="R57" s="190">
         <f t="shared" si="14"/>
         <v>782792.52</v>
@@ -10588,11 +10576,11 @@
       <c r="O58" s="266">
         <v>0</v>
       </c>
-      <c r="P58" s="378">
+      <c r="P58" s="389">
         <f t="shared" si="13"/>
         <v>5132076.53</v>
       </c>
-      <c r="Q58" s="378"/>
+      <c r="Q58" s="389"/>
       <c r="R58" s="190">
         <f t="shared" si="14"/>
         <v>5287732.53</v>
@@ -10622,7 +10610,7 @@
       <c r="E59" s="154">
         <v>781584.54</v>
       </c>
-      <c r="F59" s="424">
+      <c r="F59" s="343">
         <f>E59</f>
         <v>781584.54</v>
       </c>
@@ -10659,11 +10647,11 @@
       <c r="O59" s="266">
         <v>0</v>
       </c>
-      <c r="P59" s="378">
+      <c r="P59" s="389">
         <f t="shared" si="13"/>
         <v>751681.54</v>
       </c>
-      <c r="Q59" s="378"/>
+      <c r="Q59" s="389"/>
       <c r="R59" s="190">
         <f t="shared" si="14"/>
         <v>774480.54</v>
@@ -10696,7 +10684,7 @@
       <c r="E60" s="154">
         <v>730463.55</v>
       </c>
-      <c r="F60" s="423">
+      <c r="F60" s="342">
         <v>752619.55</v>
       </c>
       <c r="G60" s="46">
@@ -10732,11 +10720,11 @@
       <c r="O60" s="266">
         <v>0</v>
       </c>
-      <c r="P60" s="378">
+      <c r="P60" s="389">
         <f t="shared" si="13"/>
         <v>729525.55</v>
       </c>
-      <c r="Q60" s="378"/>
+      <c r="Q60" s="389"/>
       <c r="R60" s="190">
         <f t="shared" si="14"/>
         <v>751652.55</v>
@@ -10806,11 +10794,11 @@
       <c r="O61" s="266">
         <v>0</v>
       </c>
-      <c r="P61" s="378">
+      <c r="P61" s="389">
         <f t="shared" si="13"/>
         <v>751681.56</v>
       </c>
-      <c r="Q61" s="378"/>
+      <c r="Q61" s="389"/>
       <c r="R61" s="190">
         <f t="shared" si="14"/>
         <v>774480.56</v>
@@ -10843,7 +10831,7 @@
       <c r="E62" s="154">
         <v>751681.57</v>
       </c>
-      <c r="F62" s="424">
+      <c r="F62" s="343">
         <f>E62</f>
         <v>751681.57</v>
       </c>
@@ -10880,11 +10868,11 @@
       <c r="O62" s="266">
         <v>0</v>
       </c>
-      <c r="P62" s="378">
+      <c r="P62" s="389">
         <f t="shared" si="13"/>
         <v>751681.57</v>
       </c>
-      <c r="Q62" s="378"/>
+      <c r="Q62" s="389"/>
       <c r="R62" s="190">
         <f t="shared" si="14"/>
         <v>774480.57</v>
@@ -10951,11 +10939,11 @@
       <c r="O63" s="266">
         <v>0</v>
       </c>
-      <c r="P63" s="378">
+      <c r="P63" s="389">
         <f t="shared" si="13"/>
         <v>-91613.42</v>
       </c>
-      <c r="Q63" s="378"/>
+      <c r="Q63" s="389"/>
       <c r="R63" s="190">
         <f t="shared" si="14"/>
         <v>-94391.42</v>
@@ -10983,15 +10971,14 @@
         <v>4.1000000000000003E-3</v>
       </c>
       <c r="E64" s="154">
-        <v>698821.59</v>
-      </c>
-      <c r="F64" s="155">
-        <f>686000+74000</f>
-        <v>760000</v>
+        <v>720017.59</v>
+      </c>
+      <c r="F64" s="343">
+        <v>730000</v>
       </c>
       <c r="G64" s="46">
         <f t="shared" si="0"/>
-        <v>-61178.410000000033</v>
+        <v>-9982.4100000000326</v>
       </c>
       <c r="H64" s="46">
         <f t="shared" si="10"/>
@@ -11022,14 +11009,14 @@
       <c r="O64" s="266">
         <v>0</v>
       </c>
-      <c r="P64" s="378">
+      <c r="P64" s="389">
         <f t="shared" si="13"/>
-        <v>658232.59</v>
-      </c>
-      <c r="Q64" s="378"/>
+        <v>709428.59</v>
+      </c>
+      <c r="Q64" s="389"/>
       <c r="R64" s="190">
         <f t="shared" si="14"/>
-        <v>678197.59</v>
+        <v>730946.59</v>
       </c>
       <c r="S64" s="215">
         <f t="shared" si="15"/>
@@ -11059,7 +11046,7 @@
       <c r="E65" s="154">
         <v>1684101.6</v>
       </c>
-      <c r="F65" s="423">
+      <c r="F65" s="342">
         <f>751000+912000+21102</f>
         <v>1684102</v>
       </c>
@@ -11096,11 +11083,11 @@
       <c r="O65" s="266">
         <v>0</v>
       </c>
-      <c r="P65" s="378">
+      <c r="P65" s="389">
         <f t="shared" si="13"/>
         <v>751680.6</v>
       </c>
-      <c r="Q65" s="378"/>
+      <c r="Q65" s="389"/>
       <c r="R65" s="190">
         <f t="shared" si="14"/>
         <v>774479.6</v>
@@ -11133,7 +11120,7 @@
       <c r="E66" s="154">
         <v>751387.61</v>
       </c>
-      <c r="F66" s="423">
+      <c r="F66" s="342">
         <v>752000</v>
       </c>
       <c r="G66" s="46">
@@ -11169,11 +11156,11 @@
       <c r="O66" s="266">
         <v>0</v>
       </c>
-      <c r="P66" s="378">
+      <c r="P66" s="389">
         <f t="shared" si="13"/>
         <v>751068.61</v>
       </c>
-      <c r="Q66" s="378"/>
+      <c r="Q66" s="389"/>
       <c r="R66" s="190">
         <f t="shared" si="14"/>
         <v>773849.61</v>
@@ -11206,7 +11193,7 @@
       <c r="E67" s="154">
         <v>719410.62</v>
       </c>
-      <c r="F67" s="424">
+      <c r="F67" s="343">
         <f>E67</f>
         <v>719410.62</v>
       </c>
@@ -11243,11 +11230,11 @@
       <c r="O67" s="266">
         <v>0</v>
       </c>
-      <c r="P67" s="378">
+      <c r="P67" s="389">
         <f t="shared" si="13"/>
         <v>719410.62</v>
       </c>
-      <c r="Q67" s="378"/>
+      <c r="Q67" s="389"/>
       <c r="R67" s="190">
         <f t="shared" si="14"/>
         <v>741230.62</v>
@@ -11277,7 +11264,7 @@
       <c r="E68" s="154">
         <v>751681.63</v>
       </c>
-      <c r="F68" s="424">
+      <c r="F68" s="343">
         <f>E68</f>
         <v>751681.63</v>
       </c>
@@ -11314,11 +11301,11 @@
       <c r="O68" s="266">
         <v>0</v>
       </c>
-      <c r="P68" s="378">
+      <c r="P68" s="389">
         <f t="shared" si="13"/>
         <v>751681.63</v>
       </c>
-      <c r="Q68" s="378"/>
+      <c r="Q68" s="389"/>
       <c r="R68" s="190">
         <f t="shared" si="14"/>
         <v>774480.63</v>
@@ -11351,7 +11338,7 @@
       <c r="E69" s="154">
         <v>751681.64</v>
       </c>
-      <c r="F69" s="424">
+      <c r="F69" s="343">
         <f>E69</f>
         <v>751681.64</v>
       </c>
@@ -11388,11 +11375,11 @@
       <c r="O69" s="266">
         <v>0</v>
       </c>
-      <c r="P69" s="378">
+      <c r="P69" s="389">
         <f t="shared" si="13"/>
         <v>751681.64</v>
       </c>
-      <c r="Q69" s="378"/>
+      <c r="Q69" s="389"/>
       <c r="R69" s="190">
         <f t="shared" si="14"/>
         <v>774480.64</v>
@@ -11425,7 +11412,7 @@
       <c r="E70" s="154">
         <v>751681.65</v>
       </c>
-      <c r="F70" s="423">
+      <c r="F70" s="342">
         <f t="shared" ref="F70" si="18">E70</f>
         <v>751681.65</v>
       </c>
@@ -11462,11 +11449,11 @@
       <c r="O70" s="266">
         <v>0</v>
       </c>
-      <c r="P70" s="378">
+      <c r="P70" s="389">
         <f t="shared" ref="P70:P101" si="21">ROUND(SUM(G70:O70),0) + S70</f>
         <v>751681.65</v>
       </c>
-      <c r="Q70" s="378"/>
+      <c r="Q70" s="389"/>
       <c r="R70" s="190">
         <f t="shared" ref="R70:R101" si="22">ROUND(P70+P70*3.033%,0) + S70</f>
         <v>774480.65</v>
@@ -11496,7 +11483,7 @@
       <c r="E71" s="154">
         <v>751681.66</v>
       </c>
-      <c r="F71" s="424">
+      <c r="F71" s="343">
         <f>E71</f>
         <v>751681.66</v>
       </c>
@@ -11533,11 +11520,11 @@
       <c r="O71" s="266">
         <v>0</v>
       </c>
-      <c r="P71" s="378">
+      <c r="P71" s="389">
         <f t="shared" si="21"/>
         <v>751681.66</v>
       </c>
-      <c r="Q71" s="378"/>
+      <c r="Q71" s="389"/>
       <c r="R71" s="190">
         <f t="shared" si="22"/>
         <v>774480.66</v>
@@ -11604,11 +11591,11 @@
       <c r="O72" s="266">
         <v>0</v>
       </c>
-      <c r="P72" s="378">
+      <c r="P72" s="389">
         <f t="shared" si="21"/>
         <v>3231431.67</v>
       </c>
-      <c r="Q72" s="378"/>
+      <c r="Q72" s="389"/>
       <c r="R72" s="190">
         <f t="shared" si="22"/>
         <v>3329441.67</v>
@@ -11675,11 +11662,11 @@
       <c r="O73" s="266">
         <v>0</v>
       </c>
-      <c r="P73" s="378">
+      <c r="P73" s="389">
         <f t="shared" si="21"/>
         <v>9121869.6799999997</v>
       </c>
-      <c r="Q73" s="378"/>
+      <c r="Q73" s="389"/>
       <c r="R73" s="190">
         <f t="shared" si="22"/>
         <v>9398536.6799999997</v>
@@ -11745,11 +11732,11 @@
       <c r="O74" s="266">
         <v>0</v>
       </c>
-      <c r="P74" s="378">
+      <c r="P74" s="389">
         <f t="shared" si="21"/>
         <v>679072.69</v>
       </c>
-      <c r="Q74" s="378"/>
+      <c r="Q74" s="389"/>
       <c r="R74" s="190">
         <f t="shared" si="22"/>
         <v>699669.69</v>
@@ -11781,7 +11768,7 @@
       <c r="E75" s="154">
         <v>1782528.7</v>
       </c>
-      <c r="F75" s="423">
+      <c r="F75" s="342">
         <v>151500</v>
       </c>
       <c r="G75" s="46">
@@ -11817,11 +11804,11 @@
       <c r="O75" s="266">
         <v>0</v>
       </c>
-      <c r="P75" s="378">
+      <c r="P75" s="389">
         <f t="shared" si="21"/>
         <v>2424992.7000000002</v>
       </c>
-      <c r="Q75" s="378"/>
+      <c r="Q75" s="389"/>
       <c r="R75" s="190">
         <f t="shared" si="22"/>
         <v>2498543.7000000002</v>
@@ -11889,11 +11876,11 @@
       <c r="O76" s="266">
         <v>0</v>
       </c>
-      <c r="P76" s="378">
+      <c r="P76" s="389">
         <f t="shared" si="21"/>
         <v>1716515.71</v>
       </c>
-      <c r="Q76" s="378"/>
+      <c r="Q76" s="389"/>
       <c r="R76" s="190">
         <f t="shared" si="22"/>
         <v>1768578.71</v>
@@ -11925,7 +11912,7 @@
       <c r="E77" s="154">
         <v>711343.72</v>
       </c>
-      <c r="F77" s="424">
+      <c r="F77" s="343">
         <f>61344+650000</f>
         <v>711344</v>
       </c>
@@ -11962,11 +11949,11 @@
       <c r="O77" s="266">
         <v>0</v>
       </c>
-      <c r="P77" s="378">
+      <c r="P77" s="389">
         <f t="shared" si="21"/>
         <v>711343.72</v>
       </c>
-      <c r="Q77" s="378"/>
+      <c r="Q77" s="389"/>
       <c r="R77" s="190">
         <f t="shared" si="22"/>
         <v>732919.72</v>
@@ -11998,7 +11985,7 @@
       <c r="E78" s="154">
         <v>711343.73</v>
       </c>
-      <c r="F78" s="424">
+      <c r="F78" s="343">
         <f>E78</f>
         <v>711343.73</v>
       </c>
@@ -12035,11 +12022,11 @@
       <c r="O78" s="266">
         <v>0</v>
       </c>
-      <c r="P78" s="378">
+      <c r="P78" s="389">
         <f t="shared" si="21"/>
         <v>711343.73</v>
       </c>
-      <c r="Q78" s="378"/>
+      <c r="Q78" s="389"/>
       <c r="R78" s="190">
         <f t="shared" si="22"/>
         <v>732919.73</v>
@@ -12105,11 +12092,11 @@
       <c r="O79" s="266">
         <v>0</v>
       </c>
-      <c r="P79" s="378">
+      <c r="P79" s="389">
         <f t="shared" si="21"/>
         <v>743613.74</v>
       </c>
-      <c r="Q79" s="378"/>
+      <c r="Q79" s="389"/>
       <c r="R79" s="190">
         <f t="shared" si="22"/>
         <v>766168.74</v>
@@ -12175,11 +12162,11 @@
       <c r="O80" s="266">
         <v>0</v>
       </c>
-      <c r="P80" s="378">
+      <c r="P80" s="389">
         <f t="shared" si="21"/>
         <v>719410.75</v>
       </c>
-      <c r="Q80" s="378"/>
+      <c r="Q80" s="389"/>
       <c r="R80" s="190">
         <f t="shared" si="22"/>
         <v>741230.75</v>
@@ -12211,7 +12198,7 @@
       <c r="E81" s="154">
         <v>751681.76</v>
       </c>
-      <c r="F81" s="423">
+      <c r="F81" s="342">
         <f>E81</f>
         <v>751681.76</v>
       </c>
@@ -12248,11 +12235,11 @@
       <c r="O81" s="266">
         <v>0</v>
       </c>
-      <c r="P81" s="378">
+      <c r="P81" s="389">
         <f t="shared" si="21"/>
         <v>751681.76</v>
       </c>
-      <c r="Q81" s="378"/>
+      <c r="Q81" s="389"/>
       <c r="R81" s="190">
         <f t="shared" si="22"/>
         <v>774480.76</v>
@@ -12281,7 +12268,7 @@
       <c r="E82" s="154">
         <v>1105325.77</v>
       </c>
-      <c r="F82" s="424">
+      <c r="F82" s="343">
         <f>225800+880000</f>
         <v>1105800</v>
       </c>
@@ -12318,11 +12305,11 @@
       <c r="O82" s="266">
         <v>0</v>
       </c>
-      <c r="P82" s="378">
+      <c r="P82" s="389">
         <f t="shared" si="21"/>
         <v>880288.77</v>
       </c>
-      <c r="Q82" s="378"/>
+      <c r="Q82" s="389"/>
       <c r="R82" s="190">
         <f t="shared" si="22"/>
         <v>906988.77</v>
@@ -12354,7 +12341,7 @@
       <c r="E83" s="154">
         <v>978501.78</v>
       </c>
-      <c r="F83" s="423">
+      <c r="F83" s="342">
         <v>1009000</v>
       </c>
       <c r="G83" s="46">
@@ -12390,11 +12377,11 @@
       <c r="O83" s="266">
         <v>0</v>
       </c>
-      <c r="P83" s="378">
+      <c r="P83" s="389">
         <f t="shared" si="21"/>
         <v>745385.78</v>
       </c>
-      <c r="Q83" s="378"/>
+      <c r="Q83" s="389"/>
       <c r="R83" s="190">
         <f t="shared" si="22"/>
         <v>767993.78</v>
@@ -12426,7 +12413,7 @@
       <c r="E84" s="154">
         <v>1525697.79</v>
       </c>
-      <c r="F84" s="423">
+      <c r="F84" s="342">
         <v>775700.79</v>
       </c>
       <c r="G84" s="46">
@@ -12459,17 +12446,18 @@
       <c r="N84" s="266">
         <v>0</v>
       </c>
-      <c r="O84" s="266">
-        <v>0</v>
-      </c>
-      <c r="P84" s="378">
+      <c r="O84" s="428">
+        <f>2258*100</f>
+        <v>225800</v>
+      </c>
+      <c r="P84" s="389">
         <f t="shared" si="21"/>
-        <v>1524830.79</v>
-      </c>
-      <c r="Q84" s="378"/>
+        <v>1750630.79</v>
+      </c>
+      <c r="Q84" s="389"/>
       <c r="R84" s="190">
         <f t="shared" si="22"/>
-        <v>1571079.79</v>
+        <v>1803727.79</v>
       </c>
       <c r="S84" s="269">
         <f t="shared" si="23"/>
@@ -12501,7 +12489,7 @@
       <c r="E85" s="154">
         <v>728882.8</v>
       </c>
-      <c r="F85" s="424">
+      <c r="F85" s="343">
         <f>E85</f>
         <v>728882.8</v>
       </c>
@@ -12538,11 +12526,11 @@
       <c r="O85" s="266">
         <v>0</v>
       </c>
-      <c r="P85" s="378">
+      <c r="P85" s="389">
         <f t="shared" si="21"/>
         <v>751681.8</v>
       </c>
-      <c r="Q85" s="378"/>
+      <c r="Q85" s="389"/>
       <c r="R85" s="190">
         <f t="shared" si="22"/>
         <v>774480.8</v>
@@ -12611,11 +12599,11 @@
       <c r="O86" s="266">
         <v>0</v>
       </c>
-      <c r="P86" s="378">
+      <c r="P86" s="389">
         <f t="shared" si="21"/>
         <v>751681.81</v>
       </c>
-      <c r="Q86" s="378"/>
+      <c r="Q86" s="389"/>
       <c r="R86" s="190">
         <f t="shared" si="22"/>
         <v>774480.81</v>
@@ -12684,11 +12672,11 @@
       <c r="O87" s="266">
         <v>0</v>
       </c>
-      <c r="P87" s="378">
+      <c r="P87" s="389">
         <f t="shared" si="21"/>
         <v>735939.82</v>
       </c>
-      <c r="Q87" s="378"/>
+      <c r="Q87" s="389"/>
       <c r="R87" s="190">
         <f t="shared" si="22"/>
         <v>758261.82</v>
@@ -12721,7 +12709,7 @@
       <c r="E88" s="154">
         <v>752351.83</v>
       </c>
-      <c r="F88" s="423">
+      <c r="F88" s="342">
         <v>775171.83</v>
       </c>
       <c r="G88" s="46">
@@ -12757,11 +12745,11 @@
       <c r="O88" s="266">
         <v>0</v>
       </c>
-      <c r="P88" s="378">
+      <c r="P88" s="389">
         <f t="shared" si="21"/>
         <v>753064.83</v>
       </c>
-      <c r="Q88" s="378"/>
+      <c r="Q88" s="389"/>
       <c r="R88" s="190">
         <f t="shared" si="22"/>
         <v>775905.83</v>
@@ -12790,7 +12778,7 @@
       <c r="E89" s="154">
         <v>752351.84</v>
       </c>
-      <c r="F89" s="423">
+      <c r="F89" s="342">
         <v>775171.84</v>
       </c>
       <c r="G89" s="46">
@@ -12826,11 +12814,11 @@
       <c r="O89" s="266">
         <v>0</v>
       </c>
-      <c r="P89" s="378">
+      <c r="P89" s="389">
         <f t="shared" si="21"/>
         <v>753064.84</v>
       </c>
-      <c r="Q89" s="378"/>
+      <c r="Q89" s="389"/>
       <c r="R89" s="190">
         <f t="shared" si="22"/>
         <v>775905.84</v>
@@ -12859,7 +12847,7 @@
       <c r="E90" s="154">
         <v>775884.85</v>
       </c>
-      <c r="F90" s="423">
+      <c r="F90" s="342">
         <f>E90</f>
         <v>775884.85</v>
       </c>
@@ -12896,11 +12884,11 @@
       <c r="O90" s="266">
         <v>0</v>
       </c>
-      <c r="P90" s="378">
+      <c r="P90" s="389">
         <f t="shared" si="21"/>
         <v>775884.85</v>
       </c>
-      <c r="Q90" s="378"/>
+      <c r="Q90" s="389"/>
       <c r="R90" s="190">
         <f t="shared" si="22"/>
         <v>799417.85</v>
@@ -12970,11 +12958,11 @@
       <c r="O91" s="266">
         <v>0</v>
       </c>
-      <c r="P91" s="378">
+      <c r="P91" s="389">
         <f t="shared" si="21"/>
         <v>885726.86</v>
       </c>
-      <c r="Q91" s="378"/>
+      <c r="Q91" s="389"/>
       <c r="R91" s="190">
         <f t="shared" si="22"/>
         <v>912591.86</v>
@@ -13006,7 +12994,7 @@
       <c r="E92" s="154">
         <v>775884.87</v>
       </c>
-      <c r="F92" s="423">
+      <c r="F92" s="342">
         <f>E92</f>
         <v>775884.87</v>
       </c>
@@ -13043,11 +13031,11 @@
       <c r="O92" s="266">
         <v>0</v>
       </c>
-      <c r="P92" s="378">
+      <c r="P92" s="389">
         <f t="shared" si="21"/>
         <v>775884.87</v>
       </c>
-      <c r="Q92" s="378"/>
+      <c r="Q92" s="389"/>
       <c r="R92" s="190">
         <f t="shared" si="22"/>
         <v>799417.87</v>
@@ -13076,7 +13064,7 @@
       <c r="E93" s="154">
         <v>775424.88</v>
       </c>
-      <c r="F93" s="424">
+      <c r="F93" s="343">
         <v>780000</v>
       </c>
       <c r="G93" s="46">
@@ -13112,11 +13100,11 @@
       <c r="O93" s="266">
         <v>0</v>
       </c>
-      <c r="P93" s="378">
+      <c r="P93" s="389">
         <f t="shared" si="21"/>
         <v>771309.88</v>
       </c>
-      <c r="Q93" s="378"/>
+      <c r="Q93" s="389"/>
       <c r="R93" s="190">
         <f t="shared" si="22"/>
         <v>794704.88</v>
@@ -13179,11 +13167,11 @@
       <c r="O94" s="266">
         <v>0</v>
       </c>
-      <c r="P94" s="378">
+      <c r="P94" s="389">
         <f t="shared" si="21"/>
         <v>2617780.89</v>
       </c>
-      <c r="Q94" s="378"/>
+      <c r="Q94" s="389"/>
       <c r="R94" s="190">
         <f t="shared" si="22"/>
         <v>2697178.89</v>
@@ -13215,7 +13203,7 @@
       <c r="E95" s="154">
         <v>1407107.9</v>
       </c>
-      <c r="F95" s="423">
+      <c r="F95" s="342">
         <v>1400000.9</v>
       </c>
       <c r="G95" s="46">
@@ -13251,11 +13239,11 @@
       <c r="O95" s="266">
         <v>0</v>
       </c>
-      <c r="P95" s="378">
+      <c r="P95" s="389">
         <f t="shared" si="21"/>
         <v>783210.9</v>
       </c>
-      <c r="Q95" s="378"/>
+      <c r="Q95" s="389"/>
       <c r="R95" s="190">
         <f t="shared" si="22"/>
         <v>806966.9</v>
@@ -13287,7 +13275,7 @@
       <c r="E96" s="154">
         <v>775884.91</v>
       </c>
-      <c r="F96" s="423">
+      <c r="F96" s="342">
         <f>E96</f>
         <v>775884.91</v>
       </c>
@@ -13324,11 +13312,11 @@
       <c r="O96" s="266">
         <v>0</v>
       </c>
-      <c r="P96" s="378">
+      <c r="P96" s="389">
         <f t="shared" si="21"/>
         <v>775884.91</v>
       </c>
-      <c r="Q96" s="378"/>
+      <c r="Q96" s="389"/>
       <c r="R96" s="190">
         <f t="shared" si="22"/>
         <v>799417.91</v>
@@ -13360,7 +13348,7 @@
       <c r="E97" s="154">
         <v>775884.92</v>
       </c>
-      <c r="F97" s="424">
+      <c r="F97" s="343">
         <f>E97</f>
         <v>775884.92</v>
       </c>
@@ -13397,11 +13385,11 @@
       <c r="O97" s="266">
         <v>0</v>
       </c>
-      <c r="P97" s="378">
+      <c r="P97" s="389">
         <f t="shared" si="21"/>
         <v>775884.92</v>
       </c>
-      <c r="Q97" s="378"/>
+      <c r="Q97" s="389"/>
       <c r="R97" s="190">
         <f t="shared" si="22"/>
         <v>799418.92</v>
@@ -13433,7 +13421,7 @@
       <c r="E98" s="154">
         <v>1524078.93</v>
       </c>
-      <c r="F98" s="423">
+      <c r="F98" s="342">
         <v>800000</v>
       </c>
       <c r="G98" s="46">
@@ -13469,11 +13457,11 @@
       <c r="O98" s="266">
         <v>0</v>
       </c>
-      <c r="P98" s="378">
+      <c r="P98" s="389">
         <f t="shared" si="21"/>
         <v>1506180.93</v>
       </c>
-      <c r="Q98" s="378"/>
+      <c r="Q98" s="389"/>
       <c r="R98" s="190">
         <f t="shared" si="22"/>
         <v>1551863.93</v>
@@ -13505,7 +13493,7 @@
       <c r="E99" s="154">
         <v>775884.94</v>
       </c>
-      <c r="F99" s="423">
+      <c r="F99" s="342">
         <f>E99</f>
         <v>775884.94</v>
       </c>
@@ -13542,11 +13530,11 @@
       <c r="O99" s="266">
         <v>0</v>
       </c>
-      <c r="P99" s="378">
+      <c r="P99" s="389">
         <f t="shared" si="21"/>
         <v>775884.94</v>
       </c>
-      <c r="Q99" s="378"/>
+      <c r="Q99" s="389"/>
       <c r="R99" s="190">
         <f t="shared" si="22"/>
         <v>799418.94</v>
@@ -13612,11 +13600,11 @@
       <c r="O100" s="266">
         <v>0</v>
       </c>
-      <c r="P100" s="378">
+      <c r="P100" s="389">
         <f t="shared" si="21"/>
         <v>8383643.9500000002</v>
       </c>
-      <c r="Q100" s="378"/>
+      <c r="Q100" s="389"/>
       <c r="R100" s="190">
         <f t="shared" si="22"/>
         <v>8637920.9499999993</v>
@@ -13645,7 +13633,7 @@
       <c r="E101" s="154">
         <v>703583.96</v>
       </c>
-      <c r="F101" s="423">
+      <c r="F101" s="342">
         <v>730000</v>
       </c>
       <c r="G101" s="46">
@@ -13681,11 +13669,11 @@
       <c r="O101" s="266">
         <v>0</v>
       </c>
-      <c r="P101" s="378">
+      <c r="P101" s="389">
         <f t="shared" si="21"/>
         <v>749468.96</v>
       </c>
-      <c r="Q101" s="378"/>
+      <c r="Q101" s="389"/>
       <c r="R101" s="190">
         <f t="shared" si="22"/>
         <v>772200.95999999996</v>
@@ -13717,7 +13705,7 @@
       <c r="E102" s="154">
         <v>727186.97</v>
       </c>
-      <c r="F102" s="424">
+      <c r="F102" s="343">
         <v>749250</v>
       </c>
       <c r="G102" s="46">
@@ -13753,11 +13741,11 @@
       <c r="O102" s="266">
         <v>0</v>
       </c>
-      <c r="P102" s="378">
+      <c r="P102" s="389">
         <f t="shared" ref="P102:P133" si="30">ROUND(SUM(G102:O102),0) + S102</f>
         <v>753821.97</v>
       </c>
-      <c r="Q102" s="378"/>
+      <c r="Q102" s="389"/>
       <c r="R102" s="190">
         <f t="shared" ref="R102:R133" si="31">ROUND(P102+P102*3.033%,0) + S102</f>
         <v>776685.97</v>
@@ -13789,7 +13777,7 @@
       <c r="E103" s="154">
         <v>775884.98</v>
       </c>
-      <c r="F103" s="423">
+      <c r="F103" s="342">
         <f>E103</f>
         <v>775884.98</v>
       </c>
@@ -13826,11 +13814,11 @@
       <c r="O103" s="266">
         <v>0</v>
       </c>
-      <c r="P103" s="378">
+      <c r="P103" s="389">
         <f t="shared" si="30"/>
         <v>775884.98</v>
       </c>
-      <c r="Q103" s="378"/>
+      <c r="Q103" s="389"/>
       <c r="R103" s="190">
         <f t="shared" si="31"/>
         <v>799418.98</v>
@@ -13896,11 +13884,11 @@
       <c r="O104" s="266">
         <v>0</v>
       </c>
-      <c r="P104" s="378">
+      <c r="P104" s="389">
         <f t="shared" si="30"/>
         <v>775884.99</v>
       </c>
-      <c r="Q104" s="378"/>
+      <c r="Q104" s="389"/>
       <c r="R104" s="190">
         <f t="shared" si="31"/>
         <v>799418.99</v>
@@ -13932,7 +13920,7 @@
       <c r="E105" s="154">
         <v>775885</v>
       </c>
-      <c r="F105" s="424">
+      <c r="F105" s="343">
         <f>E105</f>
         <v>775885</v>
       </c>
@@ -13969,11 +13957,11 @@
       <c r="O105" s="266">
         <v>0</v>
       </c>
-      <c r="P105" s="378">
+      <c r="P105" s="389">
         <f t="shared" si="30"/>
         <v>775885</v>
       </c>
-      <c r="Q105" s="378"/>
+      <c r="Q105" s="389"/>
       <c r="R105" s="190">
         <f t="shared" si="31"/>
         <v>799419</v>
@@ -14002,7 +13990,7 @@
       <c r="E106" s="154">
         <v>898439.01</v>
       </c>
-      <c r="F106" s="424">
+      <c r="F106" s="343">
         <v>925690.01</v>
       </c>
       <c r="G106" s="46">
@@ -14038,11 +14026,11 @@
       <c r="O106" s="266">
         <v>0</v>
       </c>
-      <c r="P106" s="378">
+      <c r="P106" s="389">
         <f t="shared" si="30"/>
         <v>748634.01</v>
       </c>
-      <c r="Q106" s="378"/>
+      <c r="Q106" s="389"/>
       <c r="R106" s="190">
         <f t="shared" si="31"/>
         <v>771341.01</v>
@@ -14071,7 +14059,7 @@
       <c r="E107" s="154">
         <v>776326.02</v>
       </c>
-      <c r="F107" s="423">
+      <c r="F107" s="342">
         <v>780000</v>
       </c>
       <c r="G107" s="46">
@@ -14107,11 +14095,11 @@
       <c r="O107" s="266">
         <v>0</v>
       </c>
-      <c r="P107" s="378">
+      <c r="P107" s="389">
         <f t="shared" si="30"/>
         <v>772211.02</v>
       </c>
-      <c r="Q107" s="378"/>
+      <c r="Q107" s="389"/>
       <c r="R107" s="190">
         <f t="shared" si="31"/>
         <v>795633.02</v>
@@ -14143,7 +14131,7 @@
       <c r="E108" s="154">
         <v>775885.03</v>
       </c>
-      <c r="F108" s="424">
+      <c r="F108" s="343">
         <v>799419.03</v>
       </c>
       <c r="G108" s="46">
@@ -14179,11 +14167,11 @@
       <c r="O108" s="266">
         <v>0</v>
       </c>
-      <c r="P108" s="378">
+      <c r="P108" s="389">
         <f t="shared" si="30"/>
         <v>752351.03</v>
       </c>
-      <c r="Q108" s="378"/>
+      <c r="Q108" s="389"/>
       <c r="R108" s="190">
         <f t="shared" si="31"/>
         <v>775171.03</v>
@@ -14212,7 +14200,7 @@
       <c r="E109" s="154">
         <v>767817.04</v>
       </c>
-      <c r="F109" s="424">
+      <c r="F109" s="343">
         <v>791106.04</v>
       </c>
       <c r="G109" s="46">
@@ -14248,11 +14236,11 @@
       <c r="O109" s="266">
         <v>0</v>
       </c>
-      <c r="P109" s="378">
+      <c r="P109" s="389">
         <f t="shared" si="30"/>
         <v>744528.04</v>
       </c>
-      <c r="Q109" s="378"/>
+      <c r="Q109" s="389"/>
       <c r="R109" s="190">
         <f t="shared" si="31"/>
         <v>767111.04</v>
@@ -14282,18 +14270,19 @@
         <v>4.1999999999999997E-3</v>
       </c>
       <c r="E110" s="154">
-        <v>1201854.05</v>
-      </c>
-      <c r="F110" s="155">
-        <v>727479</v>
+        <v>1238307.05</v>
+      </c>
+      <c r="F110" s="343">
+        <f>E110</f>
+        <v>1238307.05</v>
       </c>
       <c r="G110" s="46">
         <f t="shared" si="19"/>
-        <v>474375.05000000005</v>
+        <v>0</v>
       </c>
       <c r="H110" s="46">
         <f t="shared" si="27"/>
-        <v>14643.957793500002</v>
+        <v>0</v>
       </c>
       <c r="I110" s="268">
         <f t="shared" si="34"/>
@@ -14321,14 +14310,14 @@
       <c r="O110" s="266">
         <v>0</v>
       </c>
-      <c r="P110" s="378">
+      <c r="P110" s="389">
         <f t="shared" si="30"/>
-        <v>1690873.05</v>
-      </c>
-      <c r="Q110" s="378"/>
+        <v>1201854.05</v>
+      </c>
+      <c r="Q110" s="389"/>
       <c r="R110" s="190">
         <f t="shared" si="31"/>
-        <v>1742158.05</v>
+        <v>1238307.05</v>
       </c>
       <c r="S110" s="269">
         <f t="shared" si="32"/>
@@ -14358,7 +14347,7 @@
       <c r="E111" s="154">
         <v>6220287.0599999996</v>
       </c>
-      <c r="F111" s="424">
+      <c r="F111" s="343">
         <v>2000000</v>
       </c>
       <c r="G111" s="46">
@@ -14395,11 +14384,11 @@
       <c r="O111" s="266">
         <v>0</v>
       </c>
-      <c r="P111" s="378">
+      <c r="P111" s="389">
         <f t="shared" si="30"/>
         <v>5520151.0599999996</v>
       </c>
-      <c r="Q111" s="378"/>
+      <c r="Q111" s="389"/>
       <c r="R111" s="190">
         <f t="shared" si="31"/>
         <v>5687578.0599999996</v>
@@ -14431,7 +14420,7 @@
       <c r="E112" s="154">
         <v>743614.07</v>
       </c>
-      <c r="F112" s="423">
+      <c r="F112" s="342">
         <f>E112</f>
         <v>743614.07</v>
       </c>
@@ -14468,11 +14457,11 @@
       <c r="O112" s="266">
         <v>0</v>
       </c>
-      <c r="P112" s="378">
+      <c r="P112" s="389">
         <f t="shared" si="30"/>
         <v>743614.07</v>
       </c>
-      <c r="Q112" s="378"/>
+      <c r="Q112" s="389"/>
       <c r="R112" s="190">
         <f t="shared" si="31"/>
         <v>766169.07</v>
@@ -14504,7 +14493,7 @@
       <c r="E113" s="154">
         <v>743614.08</v>
       </c>
-      <c r="F113" s="424">
+      <c r="F113" s="343">
         <f>E113</f>
         <v>743614.08</v>
       </c>
@@ -14541,11 +14530,11 @@
       <c r="O113" s="266">
         <v>0</v>
       </c>
-      <c r="P113" s="378">
+      <c r="P113" s="389">
         <f t="shared" si="30"/>
         <v>743614.08</v>
       </c>
-      <c r="Q113" s="378"/>
+      <c r="Q113" s="389"/>
       <c r="R113" s="190">
         <f t="shared" si="31"/>
         <v>766169.08</v>
@@ -14574,16 +14563,16 @@
       <c r="E114" s="154">
         <v>1614062.09</v>
       </c>
-      <c r="F114" s="157">
-        <v>1430000</v>
+      <c r="F114" s="342">
+        <v>810000</v>
       </c>
       <c r="G114" s="46">
         <f t="shared" si="19"/>
-        <v>184062.09000000008</v>
+        <v>804062.09000000008</v>
       </c>
       <c r="H114" s="46">
         <f t="shared" si="27"/>
-        <v>5681.9967183000026</v>
+        <v>24821.396718300002</v>
       </c>
       <c r="I114" s="268">
         <f t="shared" si="34"/>
@@ -14610,14 +14599,14 @@
       <c r="O114" s="266">
         <v>0</v>
       </c>
-      <c r="P114" s="378">
+      <c r="P114" s="389">
         <f t="shared" si="30"/>
-        <v>941426.09</v>
-      </c>
-      <c r="Q114" s="378"/>
+        <v>1580565.09</v>
+      </c>
+      <c r="Q114" s="389"/>
       <c r="R114" s="190">
         <f t="shared" si="31"/>
-        <v>969981.09</v>
+        <v>1628505.09</v>
       </c>
       <c r="S114" s="215">
         <f t="shared" si="32"/>
@@ -14683,11 +14672,11 @@
       <c r="O115" s="266">
         <v>0</v>
       </c>
-      <c r="P115" s="378">
+      <c r="P115" s="389">
         <f t="shared" si="30"/>
         <v>759749.1</v>
       </c>
-      <c r="Q115" s="378"/>
+      <c r="Q115" s="389"/>
       <c r="R115" s="190">
         <f t="shared" si="31"/>
         <v>782793.1</v>
@@ -14720,7 +14709,7 @@
       <c r="E116" s="154">
         <v>751682.11</v>
       </c>
-      <c r="F116" s="423">
+      <c r="F116" s="342">
         <f>E116</f>
         <v>751682.11</v>
       </c>
@@ -14757,11 +14746,11 @@
       <c r="O116" s="266">
         <v>0</v>
       </c>
-      <c r="P116" s="378">
+      <c r="P116" s="389">
         <f t="shared" si="30"/>
         <v>751682.11</v>
       </c>
-      <c r="Q116" s="378"/>
+      <c r="Q116" s="389"/>
       <c r="R116" s="190">
         <f t="shared" si="31"/>
         <v>774482.11</v>
@@ -14790,7 +14779,7 @@
       <c r="E117" s="154">
         <v>1473295.12</v>
       </c>
-      <c r="F117" s="423">
+      <c r="F117" s="342">
         <v>800000</v>
       </c>
       <c r="G117" s="46">
@@ -14826,11 +14815,11 @@
       <c r="O117" s="266">
         <v>0</v>
       </c>
-      <c r="P117" s="378">
+      <c r="P117" s="389">
         <f t="shared" si="30"/>
         <v>1445762.12</v>
       </c>
-      <c r="Q117" s="378"/>
+      <c r="Q117" s="389"/>
       <c r="R117" s="190">
         <f t="shared" si="31"/>
         <v>1489613.12</v>
@@ -14862,7 +14851,7 @@
       <c r="E118" s="154">
         <v>745215.13</v>
       </c>
-      <c r="F118" s="423">
+      <c r="F118" s="342">
         <v>767816.13</v>
       </c>
       <c r="G118" s="46">
@@ -14898,11 +14887,11 @@
       <c r="O118" s="266">
         <v>0</v>
       </c>
-      <c r="P118" s="378">
+      <c r="P118" s="389">
         <f t="shared" si="30"/>
         <v>745216.13</v>
       </c>
-      <c r="Q118" s="378"/>
+      <c r="Q118" s="389"/>
       <c r="R118" s="190">
         <f t="shared" si="31"/>
         <v>767820.13</v>
@@ -14931,7 +14920,7 @@
       <c r="E119" s="154">
         <v>751682.14</v>
       </c>
-      <c r="F119" s="424">
+      <c r="F119" s="343">
         <f>E119</f>
         <v>751682.14</v>
       </c>
@@ -14968,11 +14957,11 @@
       <c r="O119" s="266">
         <v>0</v>
       </c>
-      <c r="P119" s="378">
+      <c r="P119" s="389">
         <f t="shared" si="30"/>
         <v>751682.14</v>
       </c>
-      <c r="Q119" s="378"/>
+      <c r="Q119" s="389"/>
       <c r="R119" s="190">
         <f t="shared" si="31"/>
         <v>774482.14</v>
@@ -15001,7 +14990,7 @@
       <c r="E120" s="154">
         <v>904966.15</v>
       </c>
-      <c r="F120" s="423">
+      <c r="F120" s="342">
         <f>E120</f>
         <v>904966.15</v>
       </c>
@@ -15038,11 +15027,11 @@
       <c r="O120" s="266">
         <v>0</v>
       </c>
-      <c r="P120" s="378">
+      <c r="P120" s="389">
         <f t="shared" si="30"/>
         <v>904966.15</v>
       </c>
-      <c r="Q120" s="378"/>
+      <c r="Q120" s="389"/>
       <c r="R120" s="190">
         <f t="shared" si="31"/>
         <v>932415.15</v>
@@ -15074,7 +15063,7 @@
       <c r="E121" s="154">
         <v>931484.16000000003</v>
       </c>
-      <c r="F121" s="423">
+      <c r="F121" s="342">
         <v>959737.16</v>
       </c>
       <c r="G121" s="46">
@@ -15110,11 +15099,11 @@
       <c r="O121" s="266">
         <v>0</v>
       </c>
-      <c r="P121" s="378">
+      <c r="P121" s="389">
         <f t="shared" si="30"/>
         <v>828308.16</v>
       </c>
-      <c r="Q121" s="378"/>
+      <c r="Q121" s="389"/>
       <c r="R121" s="190">
         <f t="shared" si="31"/>
         <v>853432.16</v>
@@ -15143,7 +15132,7 @@
       <c r="E122" s="154">
         <v>880763.17</v>
       </c>
-      <c r="F122" s="423">
+      <c r="F122" s="342">
         <f>E122</f>
         <v>880763.17</v>
       </c>
@@ -15180,11 +15169,11 @@
       <c r="O122" s="266">
         <v>0</v>
       </c>
-      <c r="P122" s="378">
+      <c r="P122" s="389">
         <f t="shared" si="30"/>
         <v>880763.17</v>
       </c>
-      <c r="Q122" s="378"/>
+      <c r="Q122" s="389"/>
       <c r="R122" s="190">
         <f t="shared" si="31"/>
         <v>907478.17</v>
@@ -15216,7 +15205,7 @@
       <c r="E123" s="154">
         <v>856559.18</v>
       </c>
-      <c r="F123" s="423">
+      <c r="F123" s="342">
         <f>2358500-F125-F126</f>
         <v>839001.59000000008</v>
       </c>
@@ -15253,11 +15242,11 @@
       <c r="O123" s="266">
         <v>0</v>
       </c>
-      <c r="P123" s="378">
+      <c r="P123" s="389">
         <f t="shared" si="30"/>
         <v>874660.18</v>
       </c>
-      <c r="Q123" s="378"/>
+      <c r="Q123" s="389"/>
       <c r="R123" s="190">
         <f t="shared" si="31"/>
         <v>901190.18</v>
@@ -15289,7 +15278,7 @@
       <c r="E124" s="154">
         <v>824588.19</v>
       </c>
-      <c r="F124" s="423">
+      <c r="F124" s="342">
         <v>822000</v>
       </c>
       <c r="G124" s="46">
@@ -15325,11 +15314,11 @@
       <c r="O124" s="266">
         <v>0</v>
       </c>
-      <c r="P124" s="378">
+      <c r="P124" s="389">
         <f t="shared" si="30"/>
         <v>826958.19</v>
       </c>
-      <c r="Q124" s="378"/>
+      <c r="Q124" s="389"/>
       <c r="R124" s="190">
         <f t="shared" si="31"/>
         <v>852041.19</v>
@@ -15361,7 +15350,7 @@
       <c r="E125" s="154">
         <v>759749.2</v>
       </c>
-      <c r="F125" s="423">
+      <c r="F125" s="342">
         <f>E125</f>
         <v>759749.2</v>
       </c>
@@ -15398,11 +15387,11 @@
       <c r="O125" s="266">
         <v>0</v>
       </c>
-      <c r="P125" s="378">
+      <c r="P125" s="389">
         <f t="shared" si="30"/>
         <v>759749.2</v>
       </c>
-      <c r="Q125" s="378"/>
+      <c r="Q125" s="389"/>
       <c r="R125" s="190">
         <f t="shared" si="31"/>
         <v>782793.2</v>
@@ -15434,7 +15423,7 @@
       <c r="E126" s="154">
         <v>759749.21</v>
       </c>
-      <c r="F126" s="423">
+      <c r="F126" s="342">
         <f>E126</f>
         <v>759749.21</v>
       </c>
@@ -15471,11 +15460,11 @@
       <c r="O126" s="266">
         <v>0</v>
       </c>
-      <c r="P126" s="378">
+      <c r="P126" s="389">
         <f t="shared" si="30"/>
         <v>759749.21</v>
       </c>
-      <c r="Q126" s="378"/>
+      <c r="Q126" s="389"/>
       <c r="R126" s="190">
         <f t="shared" si="31"/>
         <v>782793.21</v>
@@ -15507,7 +15496,7 @@
       <c r="E127" s="154">
         <v>759749.22</v>
       </c>
-      <c r="F127" s="424">
+      <c r="F127" s="343">
         <f>E127</f>
         <v>759749.22</v>
       </c>
@@ -15544,11 +15533,11 @@
       <c r="O127" s="266">
         <v>0</v>
       </c>
-      <c r="P127" s="378">
+      <c r="P127" s="389">
         <f t="shared" si="30"/>
         <v>759749.22</v>
       </c>
-      <c r="Q127" s="378"/>
+      <c r="Q127" s="389"/>
       <c r="R127" s="190">
         <f t="shared" si="31"/>
         <v>782793.22</v>
@@ -15614,11 +15603,11 @@
       <c r="O128" s="266">
         <v>0</v>
       </c>
-      <c r="P128" s="378">
+      <c r="P128" s="389">
         <f t="shared" si="30"/>
         <v>759749.23</v>
       </c>
-      <c r="Q128" s="378"/>
+      <c r="Q128" s="389"/>
       <c r="R128" s="190">
         <f t="shared" si="31"/>
         <v>782793.23</v>
@@ -15650,7 +15639,7 @@
       <c r="E129" s="154">
         <v>737383.24</v>
       </c>
-      <c r="F129" s="423">
+      <c r="F129" s="342">
         <v>759749.24</v>
       </c>
       <c r="G129" s="46">
@@ -15686,11 +15675,11 @@
       <c r="O129" s="266">
         <v>0</v>
       </c>
-      <c r="P129" s="378">
+      <c r="P129" s="389">
         <f t="shared" si="30"/>
         <v>737383.24</v>
       </c>
-      <c r="Q129" s="378"/>
+      <c r="Q129" s="389"/>
       <c r="R129" s="190">
         <f t="shared" si="31"/>
         <v>759749.24</v>
@@ -15719,7 +15708,7 @@
       <c r="E130" s="154">
         <v>759749.25</v>
       </c>
-      <c r="F130" s="424">
+      <c r="F130" s="343">
         <f>E130</f>
         <v>759749.25</v>
       </c>
@@ -15756,11 +15745,11 @@
       <c r="O130" s="266">
         <v>0</v>
       </c>
-      <c r="P130" s="378">
+      <c r="P130" s="389">
         <f t="shared" si="30"/>
         <v>759749.25</v>
       </c>
-      <c r="Q130" s="378"/>
+      <c r="Q130" s="389"/>
       <c r="R130" s="190">
         <f t="shared" si="31"/>
         <v>782793.25</v>
@@ -15829,11 +15818,11 @@
       <c r="O131" s="266">
         <v>0</v>
       </c>
-      <c r="P131" s="378">
+      <c r="P131" s="389">
         <f t="shared" si="30"/>
         <v>759749.26</v>
       </c>
-      <c r="Q131" s="378"/>
+      <c r="Q131" s="389"/>
       <c r="R131" s="190">
         <f t="shared" si="31"/>
         <v>782793.26</v>
@@ -15862,7 +15851,7 @@
       <c r="E132" s="154">
         <v>840425.27</v>
       </c>
-      <c r="F132" s="423">
+      <c r="F132" s="342">
         <v>865916.27</v>
       </c>
       <c r="G132" s="46">
@@ -15898,11 +15887,11 @@
       <c r="O132" s="266">
         <v>0</v>
       </c>
-      <c r="P132" s="378">
+      <c r="P132" s="389">
         <f t="shared" si="30"/>
         <v>814934.27</v>
       </c>
-      <c r="Q132" s="378"/>
+      <c r="Q132" s="389"/>
       <c r="R132" s="190">
         <f t="shared" si="31"/>
         <v>839652.27</v>
@@ -15934,7 +15923,7 @@
       <c r="E133" s="154">
         <v>880763.28</v>
       </c>
-      <c r="F133" s="424">
+      <c r="F133" s="343">
         <f>E133</f>
         <v>880763.28</v>
       </c>
@@ -15971,11 +15960,11 @@
       <c r="O133" s="266">
         <v>0</v>
       </c>
-      <c r="P133" s="378">
+      <c r="P133" s="389">
         <f t="shared" si="30"/>
         <v>880763.28</v>
       </c>
-      <c r="Q133" s="378"/>
+      <c r="Q133" s="389"/>
       <c r="R133" s="190">
         <f t="shared" si="31"/>
         <v>907478.28</v>
@@ -16004,7 +15993,7 @@
       <c r="E134" s="154">
         <v>880763.29</v>
       </c>
-      <c r="F134" s="423">
+      <c r="F134" s="342">
         <f>E134</f>
         <v>880763.29</v>
       </c>
@@ -16041,11 +16030,11 @@
       <c r="O134" s="266">
         <v>0</v>
       </c>
-      <c r="P134" s="378">
+      <c r="P134" s="389">
         <f t="shared" ref="P134:P144" si="36">ROUND(SUM(G134:O134),0) + S134</f>
         <v>880763.29</v>
       </c>
-      <c r="Q134" s="378"/>
+      <c r="Q134" s="389"/>
       <c r="R134" s="190">
         <f t="shared" ref="R134:R144" si="37">ROUND(P134+P134*3.033%,0) + S134</f>
         <v>907478.29</v>
@@ -16077,7 +16066,7 @@
       <c r="E135" s="154">
         <v>848316.3</v>
       </c>
-      <c r="F135" s="423">
+      <c r="F135" s="342">
         <v>850000</v>
       </c>
       <c r="G135" s="46">
@@ -16113,11 +16102,11 @@
       <c r="O135" s="266">
         <v>0</v>
       </c>
-      <c r="P135" s="378">
+      <c r="P135" s="389">
         <f t="shared" si="36"/>
         <v>846809.3</v>
       </c>
-      <c r="Q135" s="378"/>
+      <c r="Q135" s="389"/>
       <c r="R135" s="190">
         <f t="shared" si="37"/>
         <v>872494.3</v>
@@ -16149,7 +16138,7 @@
       <c r="E136" s="154">
         <v>880763.31</v>
       </c>
-      <c r="F136" s="423">
+      <c r="F136" s="342">
         <f>E136</f>
         <v>880763.31</v>
       </c>
@@ -16186,11 +16175,11 @@
       <c r="O136" s="266">
         <v>0</v>
       </c>
-      <c r="P136" s="378">
+      <c r="P136" s="389">
         <f t="shared" si="36"/>
         <v>880763.31</v>
       </c>
-      <c r="Q136" s="378"/>
+      <c r="Q136" s="389"/>
       <c r="R136" s="190">
         <f t="shared" si="37"/>
         <v>907478.31</v>
@@ -16222,7 +16211,7 @@
       <c r="E137" s="154">
         <v>899166.32</v>
       </c>
-      <c r="F137" s="424">
+      <c r="F137" s="343">
         <f>E137</f>
         <v>899166.32</v>
       </c>
@@ -16259,11 +16248,11 @@
       <c r="O137" s="266">
         <v>0</v>
       </c>
-      <c r="P137" s="378">
+      <c r="P137" s="389">
         <f t="shared" si="36"/>
         <v>872696.31999999995</v>
       </c>
-      <c r="Q137" s="378"/>
+      <c r="Q137" s="389"/>
       <c r="R137" s="190">
         <f t="shared" si="37"/>
         <v>899166.32</v>
@@ -16295,7 +16284,7 @@
       <c r="E138" s="154">
         <v>904966.33</v>
       </c>
-      <c r="F138" s="424">
+      <c r="F138" s="343">
         <f>E138</f>
         <v>904966.33</v>
       </c>
@@ -16332,11 +16321,11 @@
       <c r="O138" s="266">
         <v>0</v>
       </c>
-      <c r="P138" s="378">
+      <c r="P138" s="389">
         <f t="shared" si="36"/>
         <v>904966.33</v>
       </c>
-      <c r="Q138" s="378"/>
+      <c r="Q138" s="389"/>
       <c r="R138" s="190">
         <f t="shared" si="37"/>
         <v>932415.33</v>
@@ -16368,7 +16357,7 @@
       <c r="E139" s="154">
         <v>792194.34</v>
       </c>
-      <c r="F139" s="423">
+      <c r="F139" s="342">
         <v>816223.34</v>
       </c>
       <c r="G139" s="46">
@@ -16404,11 +16393,11 @@
       <c r="O139" s="266">
         <v>0</v>
       </c>
-      <c r="P139" s="378">
+      <c r="P139" s="389">
         <f t="shared" si="36"/>
         <v>792194.34</v>
       </c>
-      <c r="Q139" s="378"/>
+      <c r="Q139" s="389"/>
       <c r="R139" s="190">
         <f t="shared" si="37"/>
         <v>816223.34</v>
@@ -16440,7 +16429,7 @@
       <c r="E140" s="154">
         <v>854834.35</v>
       </c>
-      <c r="F140" s="423">
+      <c r="F140" s="342">
         <v>880764.35</v>
       </c>
       <c r="G140" s="46">
@@ -16476,11 +16465,11 @@
       <c r="O140" s="266">
         <v>0</v>
       </c>
-      <c r="P140" s="378">
+      <c r="P140" s="389">
         <f t="shared" si="36"/>
         <v>854833.35</v>
       </c>
-      <c r="Q140" s="378"/>
+      <c r="Q140" s="389"/>
       <c r="R140" s="190">
         <f t="shared" si="37"/>
         <v>880761.35</v>
@@ -16512,7 +16501,7 @@
       <c r="E141" s="154">
         <v>888831.36</v>
       </c>
-      <c r="F141" s="424">
+      <c r="F141" s="343">
         <f>E141</f>
         <v>888831.36</v>
       </c>
@@ -16549,11 +16538,11 @@
       <c r="O141" s="266">
         <v>0</v>
       </c>
-      <c r="P141" s="378">
+      <c r="P141" s="389">
         <f t="shared" si="36"/>
         <v>888831.36</v>
       </c>
-      <c r="Q141" s="378"/>
+      <c r="Q141" s="389"/>
       <c r="R141" s="190">
         <f t="shared" si="37"/>
         <v>915791.35999999999</v>
@@ -16585,7 +16574,7 @@
       <c r="E142" s="154">
         <v>824290.37</v>
       </c>
-      <c r="F142" s="423">
+      <c r="F142" s="342">
         <f>E142</f>
         <v>824290.37</v>
       </c>
@@ -16622,11 +16611,11 @@
       <c r="O142" s="266">
         <v>0</v>
       </c>
-      <c r="P142" s="378">
+      <c r="P142" s="389">
         <f t="shared" si="36"/>
         <v>824290.37</v>
       </c>
-      <c r="Q142" s="378"/>
+      <c r="Q142" s="389"/>
       <c r="R142" s="190">
         <f t="shared" si="37"/>
         <v>849292.37</v>
@@ -16655,7 +16644,7 @@
       <c r="E143" s="154">
         <v>877401.38</v>
       </c>
-      <c r="F143" s="423">
+      <c r="F143" s="342">
         <f>4014.38+990000</f>
         <v>994014.38</v>
       </c>
@@ -16692,11 +16681,11 @@
       <c r="O143" s="266">
         <v>0</v>
       </c>
-      <c r="P143" s="378">
+      <c r="P143" s="389">
         <f t="shared" si="36"/>
         <v>796421.38</v>
       </c>
-      <c r="Q143" s="378"/>
+      <c r="Q143" s="389"/>
       <c r="R143" s="190">
         <f t="shared" si="37"/>
         <v>820578.38</v>
@@ -16728,7 +16717,7 @@
       <c r="E144" s="154">
         <v>785399.39</v>
       </c>
-      <c r="F144" s="423">
+      <c r="F144" s="342">
         <v>785400</v>
       </c>
       <c r="G144" s="46">
@@ -16764,11 +16753,11 @@
       <c r="O144" s="266">
         <v>0</v>
       </c>
-      <c r="P144" s="378">
+      <c r="P144" s="389">
         <f t="shared" si="36"/>
         <v>880763.39</v>
       </c>
-      <c r="Q144" s="378"/>
+      <c r="Q144" s="389"/>
       <c r="R144" s="190">
         <f t="shared" si="37"/>
         <v>907478.39</v>
@@ -16814,8 +16803,8 @@
       <c r="O145" s="266">
         <v>0</v>
       </c>
-      <c r="P145" s="378"/>
-      <c r="Q145" s="378"/>
+      <c r="P145" s="389"/>
+      <c r="Q145" s="389"/>
       <c r="R145" s="191"/>
       <c r="S145" s="215">
         <f t="shared" si="38"/>
@@ -16855,8 +16844,8 @@
       <c r="O146" s="266">
         <v>0</v>
       </c>
-      <c r="P146" s="378"/>
-      <c r="Q146" s="378"/>
+      <c r="P146" s="389"/>
+      <c r="Q146" s="389"/>
       <c r="R146" s="191"/>
       <c r="S146" s="215">
         <f t="shared" si="38"/>
@@ -16889,8 +16878,8 @@
       <c r="O147" s="266">
         <v>0</v>
       </c>
-      <c r="P147" s="378"/>
-      <c r="Q147" s="378"/>
+      <c r="P147" s="389"/>
+      <c r="Q147" s="389"/>
       <c r="R147" s="191"/>
       <c r="S147" s="215">
         <f t="shared" si="38"/>
@@ -16923,8 +16912,8 @@
       <c r="O148" s="266">
         <v>0</v>
       </c>
-      <c r="P148" s="378"/>
-      <c r="Q148" s="378"/>
+      <c r="P148" s="389"/>
+      <c r="Q148" s="389"/>
       <c r="R148" s="191"/>
       <c r="S148" s="215">
         <f t="shared" si="38"/>
@@ -16949,7 +16938,7 @@
       <c r="E149" s="155">
         <v>695209.46</v>
       </c>
-      <c r="F149" s="423">
+      <c r="F149" s="342">
         <f>E149</f>
         <v>695209.46</v>
       </c>
@@ -16986,11 +16975,11 @@
       <c r="O149" s="266">
         <v>0</v>
       </c>
-      <c r="P149" s="378">
+      <c r="P149" s="389">
         <f t="shared" ref="P149:P158" si="46">ROUND(SUM(G149:O149),0) + S149</f>
         <v>695209.46</v>
       </c>
-      <c r="Q149" s="378"/>
+      <c r="Q149" s="389"/>
       <c r="R149" s="190">
         <f t="shared" ref="R149:R158" si="47">ROUND(P149+P149*3.033%,0) + S149</f>
         <v>716296.46</v>
@@ -17018,7 +17007,7 @@
       <c r="E150" s="155">
         <v>1139411.55</v>
       </c>
-      <c r="F150" s="423">
+      <c r="F150" s="342">
         <f>E150</f>
         <v>1139411.55</v>
       </c>
@@ -17053,11 +17042,11 @@
       <c r="O150" s="266">
         <v>0</v>
       </c>
-      <c r="P150" s="378">
+      <c r="P150" s="389">
         <f t="shared" si="46"/>
         <v>1139411.55</v>
       </c>
-      <c r="Q150" s="378"/>
+      <c r="Q150" s="389"/>
       <c r="R150" s="190">
         <f t="shared" si="47"/>
         <v>1173971.55</v>
@@ -17088,7 +17077,7 @@
       <c r="E151" s="155">
         <v>759749.58</v>
       </c>
-      <c r="F151" s="423">
+      <c r="F151" s="342">
         <f t="shared" ref="F151:F154" si="48">E151</f>
         <v>759749.58</v>
       </c>
@@ -17125,11 +17114,11 @@
       <c r="O151" s="266">
         <v>0</v>
       </c>
-      <c r="P151" s="378">
+      <c r="P151" s="389">
         <f t="shared" si="46"/>
         <v>759749.58</v>
       </c>
-      <c r="Q151" s="378"/>
+      <c r="Q151" s="389"/>
       <c r="R151" s="190">
         <f t="shared" si="47"/>
         <v>782794.58</v>
@@ -17157,7 +17146,7 @@
       <c r="E152" s="155">
         <v>759749.59</v>
       </c>
-      <c r="F152" s="423">
+      <c r="F152" s="342">
         <f t="shared" si="48"/>
         <v>759749.59</v>
       </c>
@@ -17194,11 +17183,11 @@
       <c r="O152" s="266">
         <v>0</v>
       </c>
-      <c r="P152" s="378">
+      <c r="P152" s="389">
         <f t="shared" si="46"/>
         <v>759749.59</v>
       </c>
-      <c r="Q152" s="378"/>
+      <c r="Q152" s="389"/>
       <c r="R152" s="190">
         <f t="shared" si="47"/>
         <v>782794.59</v>
@@ -17226,7 +17215,7 @@
       <c r="E153" s="155">
         <v>759749.63</v>
       </c>
-      <c r="F153" s="424">
+      <c r="F153" s="343">
         <f>E153</f>
         <v>759749.63</v>
       </c>
@@ -17263,11 +17252,11 @@
       <c r="O153" s="266">
         <v>0</v>
       </c>
-      <c r="P153" s="378">
+      <c r="P153" s="389">
         <f t="shared" si="46"/>
         <v>759749.63</v>
       </c>
-      <c r="Q153" s="378"/>
+      <c r="Q153" s="389"/>
       <c r="R153" s="190">
         <f t="shared" si="47"/>
         <v>782794.63</v>
@@ -17295,7 +17284,7 @@
       <c r="E154" s="155">
         <v>743614.68</v>
       </c>
-      <c r="F154" s="423">
+      <c r="F154" s="342">
         <f t="shared" si="48"/>
         <v>743614.68</v>
       </c>
@@ -17332,11 +17321,11 @@
       <c r="O154" s="266">
         <v>0</v>
       </c>
-      <c r="P154" s="378">
+      <c r="P154" s="389">
         <f t="shared" si="46"/>
         <v>743614.68</v>
       </c>
-      <c r="Q154" s="378"/>
+      <c r="Q154" s="389"/>
       <c r="R154" s="190">
         <f t="shared" si="47"/>
         <v>766170.68</v>
@@ -17400,11 +17389,11 @@
       <c r="O155" s="266">
         <v>0</v>
       </c>
-      <c r="P155" s="378">
+      <c r="P155" s="389">
         <f t="shared" si="46"/>
         <v>759750.73</v>
       </c>
-      <c r="Q155" s="378"/>
+      <c r="Q155" s="389"/>
       <c r="R155" s="190">
         <f t="shared" si="47"/>
         <v>782795.73</v>
@@ -17471,11 +17460,11 @@
       <c r="O156" s="266">
         <v>0</v>
       </c>
-      <c r="P156" s="378">
+      <c r="P156" s="389">
         <f t="shared" si="46"/>
         <v>759750.75</v>
       </c>
-      <c r="Q156" s="378"/>
+      <c r="Q156" s="389"/>
       <c r="R156" s="190">
         <f t="shared" si="47"/>
         <v>782795.75</v>
@@ -17506,7 +17495,7 @@
       <c r="E157" s="155">
         <v>759749.76</v>
       </c>
-      <c r="F157" s="424">
+      <c r="F157" s="343">
         <f>E157</f>
         <v>759749.76</v>
       </c>
@@ -17543,11 +17532,11 @@
       <c r="O157" s="266">
         <v>0</v>
       </c>
-      <c r="P157" s="378">
+      <c r="P157" s="389">
         <f t="shared" si="46"/>
         <v>759749.76</v>
       </c>
-      <c r="Q157" s="378"/>
+      <c r="Q157" s="389"/>
       <c r="R157" s="190">
         <f t="shared" si="47"/>
         <v>782794.76</v>
@@ -17575,7 +17564,7 @@
       <c r="E158" s="155">
         <v>760873.04</v>
       </c>
-      <c r="F158" s="423">
+      <c r="F158" s="342">
         <v>783952</v>
       </c>
       <c r="G158" s="46">
@@ -17611,11 +17600,11 @@
       <c r="O158" s="266">
         <v>0</v>
       </c>
-      <c r="P158" s="378">
+      <c r="P158" s="389">
         <f t="shared" si="46"/>
         <v>760874.04</v>
       </c>
-      <c r="Q158" s="378"/>
+      <c r="Q158" s="389"/>
       <c r="R158" s="190">
         <f t="shared" si="47"/>
         <v>783953.04</v>
@@ -17650,8 +17639,8 @@
         <v>0</v>
       </c>
       <c r="O159" s="268"/>
-      <c r="P159" s="384"/>
-      <c r="Q159" s="384"/>
+      <c r="P159" s="415"/>
+      <c r="Q159" s="415"/>
       <c r="R159" s="255"/>
       <c r="S159" s="215"/>
       <c r="T159" s="19"/>
@@ -17672,8 +17661,8 @@
       <c r="M160" s="275"/>
       <c r="N160" s="275"/>
       <c r="O160" s="276"/>
-      <c r="P160" s="385"/>
-      <c r="Q160" s="385"/>
+      <c r="P160" s="416"/>
+      <c r="Q160" s="416"/>
       <c r="R160" s="256"/>
       <c r="S160" s="215"/>
       <c r="T160" s="150"/>
@@ -17688,15 +17677,15 @@
       </c>
       <c r="E161" s="279">
         <f t="shared" si="50"/>
-        <v>169618751.07000002</v>
+        <v>169676400.07000002</v>
       </c>
       <c r="F161" s="280">
         <f>SUM(F6:F160)</f>
-        <v>117066792.15999998</v>
+        <v>124836840.20999998</v>
       </c>
       <c r="G161" s="281">
         <f t="shared" si="50"/>
-        <v>52551958.910000019</v>
+        <v>44839559.859999999</v>
       </c>
       <c r="H161" s="282"/>
       <c r="I161" s="282">
@@ -17725,152 +17714,314 @@
       </c>
       <c r="O161" s="283">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="P161" s="382">
+        <v>225800</v>
+      </c>
+      <c r="P161" s="413">
         <f>SUM(P6:P160)</f>
-        <v>171613620.07000002</v>
-      </c>
-      <c r="Q161" s="383"/>
+        <v>163878835.06999999</v>
+      </c>
+      <c r="Q161" s="414"/>
       <c r="R161" s="286">
         <f>SUM(R6:R160)</f>
-        <v>176818778.07000002</v>
-      </c>
-      <c r="S161" s="382"/>
-      <c r="T161" s="383"/>
+        <v>168849396.06999999</v>
+      </c>
+      <c r="S161" s="413"/>
+      <c r="T161" s="414"/>
     </row>
     <row r="162" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B162" s="379" t="s">
+      <c r="B162" s="410" t="s">
         <v>310</v>
       </c>
-      <c r="C162" s="379"/>
-      <c r="D162" s="379"/>
-      <c r="E162" s="379"/>
-      <c r="F162" s="379"/>
-      <c r="G162" s="379"/>
-      <c r="H162" s="379"/>
-      <c r="I162" s="379"/>
-      <c r="J162" s="379"/>
-      <c r="K162" s="379"/>
-      <c r="L162" s="379"/>
-      <c r="M162" s="379"/>
-      <c r="N162" s="379"/>
-      <c r="O162" s="379"/>
-      <c r="P162" s="379"/>
-      <c r="Q162" s="379"/>
-      <c r="R162" s="379"/>
-      <c r="S162" s="379"/>
-      <c r="T162" s="379"/>
+      <c r="C162" s="410"/>
+      <c r="D162" s="410"/>
+      <c r="E162" s="410"/>
+      <c r="F162" s="410"/>
+      <c r="G162" s="410"/>
+      <c r="H162" s="410"/>
+      <c r="I162" s="410"/>
+      <c r="J162" s="410"/>
+      <c r="K162" s="410"/>
+      <c r="L162" s="410"/>
+      <c r="M162" s="410"/>
+      <c r="N162" s="410"/>
+      <c r="O162" s="410"/>
+      <c r="P162" s="410"/>
+      <c r="Q162" s="410"/>
+      <c r="R162" s="410"/>
+      <c r="S162" s="410"/>
+      <c r="T162" s="410"/>
     </row>
     <row r="163" spans="1:20" ht="49.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B163" s="380"/>
-      <c r="C163" s="380"/>
-      <c r="D163" s="380"/>
-      <c r="E163" s="380"/>
-      <c r="F163" s="380"/>
-      <c r="G163" s="380"/>
-      <c r="H163" s="380"/>
-      <c r="I163" s="380"/>
-      <c r="J163" s="380"/>
-      <c r="K163" s="380"/>
-      <c r="L163" s="380"/>
-      <c r="M163" s="380"/>
-      <c r="N163" s="380"/>
-      <c r="O163" s="380"/>
-      <c r="P163" s="380"/>
-      <c r="Q163" s="380"/>
-      <c r="R163" s="380"/>
-      <c r="S163" s="380"/>
-      <c r="T163" s="380"/>
+      <c r="B163" s="411"/>
+      <c r="C163" s="411"/>
+      <c r="D163" s="411"/>
+      <c r="E163" s="411"/>
+      <c r="F163" s="411"/>
+      <c r="G163" s="411"/>
+      <c r="H163" s="411"/>
+      <c r="I163" s="411"/>
+      <c r="J163" s="411"/>
+      <c r="K163" s="411"/>
+      <c r="L163" s="411"/>
+      <c r="M163" s="411"/>
+      <c r="N163" s="411"/>
+      <c r="O163" s="411"/>
+      <c r="P163" s="411"/>
+      <c r="Q163" s="411"/>
+      <c r="R163" s="411"/>
+      <c r="S163" s="411"/>
+      <c r="T163" s="411"/>
     </row>
     <row r="164" spans="1:20" ht="13.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B164" s="381" t="s">
+      <c r="B164" s="412" t="s">
         <v>257</v>
       </c>
-      <c r="C164" s="381"/>
-      <c r="D164" s="381"/>
-      <c r="E164" s="381"/>
-      <c r="F164" s="381"/>
-      <c r="G164" s="381"/>
-      <c r="H164" s="381"/>
-      <c r="I164" s="381"/>
-      <c r="J164" s="381"/>
-      <c r="K164" s="381"/>
-      <c r="L164" s="381"/>
-      <c r="M164" s="381"/>
-      <c r="N164" s="381"/>
-      <c r="O164" s="381"/>
-      <c r="P164" s="381"/>
-      <c r="Q164" s="381"/>
-      <c r="R164" s="381"/>
-      <c r="S164" s="381"/>
-      <c r="T164" s="381"/>
+      <c r="C164" s="412"/>
+      <c r="D164" s="412"/>
+      <c r="E164" s="412"/>
+      <c r="F164" s="412"/>
+      <c r="G164" s="412"/>
+      <c r="H164" s="412"/>
+      <c r="I164" s="412"/>
+      <c r="J164" s="412"/>
+      <c r="K164" s="412"/>
+      <c r="L164" s="412"/>
+      <c r="M164" s="412"/>
+      <c r="N164" s="412"/>
+      <c r="O164" s="412"/>
+      <c r="P164" s="412"/>
+      <c r="Q164" s="412"/>
+      <c r="R164" s="412"/>
+      <c r="S164" s="412"/>
+      <c r="T164" s="412"/>
     </row>
     <row r="165" spans="1:20" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B165" s="381"/>
-      <c r="C165" s="381"/>
-      <c r="D165" s="381"/>
-      <c r="E165" s="381"/>
-      <c r="F165" s="381"/>
-      <c r="G165" s="381"/>
-      <c r="H165" s="381"/>
-      <c r="I165" s="381"/>
-      <c r="J165" s="381"/>
-      <c r="K165" s="381"/>
-      <c r="L165" s="381"/>
-      <c r="M165" s="381"/>
-      <c r="N165" s="381"/>
-      <c r="O165" s="381"/>
-      <c r="P165" s="381"/>
-      <c r="Q165" s="381"/>
-      <c r="R165" s="381"/>
-      <c r="S165" s="381"/>
-      <c r="T165" s="381"/>
+      <c r="B165" s="412"/>
+      <c r="C165" s="412"/>
+      <c r="D165" s="412"/>
+      <c r="E165" s="412"/>
+      <c r="F165" s="412"/>
+      <c r="G165" s="412"/>
+      <c r="H165" s="412"/>
+      <c r="I165" s="412"/>
+      <c r="J165" s="412"/>
+      <c r="K165" s="412"/>
+      <c r="L165" s="412"/>
+      <c r="M165" s="412"/>
+      <c r="N165" s="412"/>
+      <c r="O165" s="412"/>
+      <c r="P165" s="412"/>
+      <c r="Q165" s="412"/>
+      <c r="R165" s="412"/>
+      <c r="S165" s="412"/>
+      <c r="T165" s="412"/>
     </row>
     <row r="166" spans="1:20" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B166" s="381"/>
-      <c r="C166" s="381"/>
-      <c r="D166" s="381"/>
-      <c r="E166" s="381"/>
-      <c r="F166" s="381"/>
-      <c r="G166" s="381"/>
-      <c r="H166" s="381"/>
-      <c r="I166" s="381"/>
-      <c r="J166" s="381"/>
-      <c r="K166" s="381"/>
-      <c r="L166" s="381"/>
-      <c r="M166" s="381"/>
-      <c r="N166" s="381"/>
-      <c r="O166" s="381"/>
-      <c r="P166" s="381"/>
-      <c r="Q166" s="381"/>
-      <c r="R166" s="381"/>
-      <c r="S166" s="381"/>
-      <c r="T166" s="381"/>
+      <c r="B166" s="412"/>
+      <c r="C166" s="412"/>
+      <c r="D166" s="412"/>
+      <c r="E166" s="412"/>
+      <c r="F166" s="412"/>
+      <c r="G166" s="412"/>
+      <c r="H166" s="412"/>
+      <c r="I166" s="412"/>
+      <c r="J166" s="412"/>
+      <c r="K166" s="412"/>
+      <c r="L166" s="412"/>
+      <c r="M166" s="412"/>
+      <c r="N166" s="412"/>
+      <c r="O166" s="412"/>
+      <c r="P166" s="412"/>
+      <c r="Q166" s="412"/>
+      <c r="R166" s="412"/>
+      <c r="S166" s="412"/>
+      <c r="T166" s="412"/>
     </row>
     <row r="167" spans="1:20" ht="128.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B167" s="381"/>
-      <c r="C167" s="381"/>
-      <c r="D167" s="381"/>
-      <c r="E167" s="381"/>
-      <c r="F167" s="381"/>
-      <c r="G167" s="381"/>
-      <c r="H167" s="381"/>
-      <c r="I167" s="381"/>
-      <c r="J167" s="381"/>
-      <c r="K167" s="381"/>
-      <c r="L167" s="381"/>
-      <c r="M167" s="381"/>
-      <c r="N167" s="381"/>
-      <c r="O167" s="381"/>
-      <c r="P167" s="381"/>
-      <c r="Q167" s="381"/>
-      <c r="R167" s="381"/>
-      <c r="S167" s="381"/>
-      <c r="T167" s="381"/>
+      <c r="B167" s="412"/>
+      <c r="C167" s="412"/>
+      <c r="D167" s="412"/>
+      <c r="E167" s="412"/>
+      <c r="F167" s="412"/>
+      <c r="G167" s="412"/>
+      <c r="H167" s="412"/>
+      <c r="I167" s="412"/>
+      <c r="J167" s="412"/>
+      <c r="K167" s="412"/>
+      <c r="L167" s="412"/>
+      <c r="M167" s="412"/>
+      <c r="N167" s="412"/>
+      <c r="O167" s="412"/>
+      <c r="P167" s="412"/>
+      <c r="Q167" s="412"/>
+      <c r="R167" s="412"/>
+      <c r="S167" s="412"/>
+      <c r="T167" s="412"/>
     </row>
   </sheetData>
   <mergeCells count="186">
+    <mergeCell ref="P146:Q146"/>
+    <mergeCell ref="P147:Q147"/>
+    <mergeCell ref="P148:Q148"/>
+    <mergeCell ref="P149:Q149"/>
+    <mergeCell ref="P151:Q151"/>
+    <mergeCell ref="P141:Q141"/>
+    <mergeCell ref="P142:Q142"/>
+    <mergeCell ref="P143:Q143"/>
+    <mergeCell ref="P144:Q144"/>
+    <mergeCell ref="P145:Q145"/>
+    <mergeCell ref="P150:Q150"/>
+    <mergeCell ref="B162:T163"/>
+    <mergeCell ref="B164:T167"/>
+    <mergeCell ref="P157:Q157"/>
+    <mergeCell ref="P158:Q158"/>
+    <mergeCell ref="P161:Q161"/>
+    <mergeCell ref="P159:Q159"/>
+    <mergeCell ref="P160:Q160"/>
+    <mergeCell ref="P152:Q152"/>
+    <mergeCell ref="P153:Q153"/>
+    <mergeCell ref="P154:Q154"/>
+    <mergeCell ref="P155:Q155"/>
+    <mergeCell ref="P156:Q156"/>
+    <mergeCell ref="S161:T161"/>
+    <mergeCell ref="P136:Q136"/>
+    <mergeCell ref="P137:Q137"/>
+    <mergeCell ref="P138:Q138"/>
+    <mergeCell ref="P139:Q139"/>
+    <mergeCell ref="P140:Q140"/>
+    <mergeCell ref="P131:Q131"/>
+    <mergeCell ref="P132:Q132"/>
+    <mergeCell ref="P133:Q133"/>
+    <mergeCell ref="P134:Q134"/>
+    <mergeCell ref="P135:Q135"/>
+    <mergeCell ref="P126:Q126"/>
+    <mergeCell ref="P127:Q127"/>
+    <mergeCell ref="P128:Q128"/>
+    <mergeCell ref="P129:Q129"/>
+    <mergeCell ref="P130:Q130"/>
+    <mergeCell ref="P121:Q121"/>
+    <mergeCell ref="P122:Q122"/>
+    <mergeCell ref="P123:Q123"/>
+    <mergeCell ref="P124:Q124"/>
+    <mergeCell ref="P125:Q125"/>
+    <mergeCell ref="P116:Q116"/>
+    <mergeCell ref="P117:Q117"/>
+    <mergeCell ref="P118:Q118"/>
+    <mergeCell ref="P119:Q119"/>
+    <mergeCell ref="P120:Q120"/>
+    <mergeCell ref="P111:Q111"/>
+    <mergeCell ref="P112:Q112"/>
+    <mergeCell ref="P113:Q113"/>
+    <mergeCell ref="P114:Q114"/>
+    <mergeCell ref="P115:Q115"/>
+    <mergeCell ref="P106:Q106"/>
+    <mergeCell ref="P107:Q107"/>
+    <mergeCell ref="P108:Q108"/>
+    <mergeCell ref="P109:Q109"/>
+    <mergeCell ref="P110:Q110"/>
+    <mergeCell ref="P101:Q101"/>
+    <mergeCell ref="P102:Q102"/>
+    <mergeCell ref="P103:Q103"/>
+    <mergeCell ref="P104:Q104"/>
+    <mergeCell ref="P105:Q105"/>
+    <mergeCell ref="P96:Q96"/>
+    <mergeCell ref="P97:Q97"/>
+    <mergeCell ref="P98:Q98"/>
+    <mergeCell ref="P99:Q99"/>
+    <mergeCell ref="P100:Q100"/>
+    <mergeCell ref="P91:Q91"/>
+    <mergeCell ref="P92:Q92"/>
+    <mergeCell ref="P93:Q93"/>
+    <mergeCell ref="P94:Q94"/>
+    <mergeCell ref="P95:Q95"/>
+    <mergeCell ref="P86:Q86"/>
+    <mergeCell ref="P87:Q87"/>
+    <mergeCell ref="P88:Q88"/>
+    <mergeCell ref="P89:Q89"/>
+    <mergeCell ref="P90:Q90"/>
+    <mergeCell ref="P81:Q81"/>
+    <mergeCell ref="P82:Q82"/>
+    <mergeCell ref="P83:Q83"/>
+    <mergeCell ref="P84:Q84"/>
+    <mergeCell ref="P85:Q85"/>
+    <mergeCell ref="P76:Q76"/>
+    <mergeCell ref="P77:Q77"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="P75:Q75"/>
+    <mergeCell ref="P66:Q66"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="P68:Q68"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="P64:Q64"/>
+    <mergeCell ref="P65:Q65"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="P46:Q46"/>
+    <mergeCell ref="P47:Q47"/>
+    <mergeCell ref="P48:Q48"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="P50:Q50"/>
+    <mergeCell ref="P41:Q41"/>
+    <mergeCell ref="P42:Q42"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="P45:Q45"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="P37:Q37"/>
+    <mergeCell ref="P38:Q38"/>
+    <mergeCell ref="P39:Q39"/>
+    <mergeCell ref="P40:Q40"/>
+    <mergeCell ref="P31:Q31"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="R4:S5"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="P6:Q6"/>
@@ -17895,168 +18046,6 @@
     <mergeCell ref="P23:Q23"/>
     <mergeCell ref="P24:Q24"/>
     <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="A3:T3"/>
-    <mergeCell ref="R4:S5"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="P27:Q27"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="P30:Q30"/>
-    <mergeCell ref="P46:Q46"/>
-    <mergeCell ref="P47:Q47"/>
-    <mergeCell ref="P48:Q48"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="P50:Q50"/>
-    <mergeCell ref="P41:Q41"/>
-    <mergeCell ref="P42:Q42"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="P45:Q45"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="P37:Q37"/>
-    <mergeCell ref="P38:Q38"/>
-    <mergeCell ref="P39:Q39"/>
-    <mergeCell ref="P40:Q40"/>
-    <mergeCell ref="P31:Q31"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="P56:Q56"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="P60:Q60"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="P55:Q55"/>
-    <mergeCell ref="P66:Q66"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="P62:Q62"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="P64:Q64"/>
-    <mergeCell ref="P65:Q65"/>
-    <mergeCell ref="P76:Q76"/>
-    <mergeCell ref="P77:Q77"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="P75:Q75"/>
-    <mergeCell ref="P86:Q86"/>
-    <mergeCell ref="P87:Q87"/>
-    <mergeCell ref="P88:Q88"/>
-    <mergeCell ref="P89:Q89"/>
-    <mergeCell ref="P90:Q90"/>
-    <mergeCell ref="P81:Q81"/>
-    <mergeCell ref="P82:Q82"/>
-    <mergeCell ref="P83:Q83"/>
-    <mergeCell ref="P84:Q84"/>
-    <mergeCell ref="P85:Q85"/>
-    <mergeCell ref="P96:Q96"/>
-    <mergeCell ref="P97:Q97"/>
-    <mergeCell ref="P98:Q98"/>
-    <mergeCell ref="P99:Q99"/>
-    <mergeCell ref="P100:Q100"/>
-    <mergeCell ref="P91:Q91"/>
-    <mergeCell ref="P92:Q92"/>
-    <mergeCell ref="P93:Q93"/>
-    <mergeCell ref="P94:Q94"/>
-    <mergeCell ref="P95:Q95"/>
-    <mergeCell ref="P106:Q106"/>
-    <mergeCell ref="P107:Q107"/>
-    <mergeCell ref="P108:Q108"/>
-    <mergeCell ref="P109:Q109"/>
-    <mergeCell ref="P110:Q110"/>
-    <mergeCell ref="P101:Q101"/>
-    <mergeCell ref="P102:Q102"/>
-    <mergeCell ref="P103:Q103"/>
-    <mergeCell ref="P104:Q104"/>
-    <mergeCell ref="P105:Q105"/>
-    <mergeCell ref="P116:Q116"/>
-    <mergeCell ref="P117:Q117"/>
-    <mergeCell ref="P118:Q118"/>
-    <mergeCell ref="P119:Q119"/>
-    <mergeCell ref="P120:Q120"/>
-    <mergeCell ref="P111:Q111"/>
-    <mergeCell ref="P112:Q112"/>
-    <mergeCell ref="P113:Q113"/>
-    <mergeCell ref="P114:Q114"/>
-    <mergeCell ref="P115:Q115"/>
-    <mergeCell ref="P126:Q126"/>
-    <mergeCell ref="P127:Q127"/>
-    <mergeCell ref="P128:Q128"/>
-    <mergeCell ref="P129:Q129"/>
-    <mergeCell ref="P130:Q130"/>
-    <mergeCell ref="P121:Q121"/>
-    <mergeCell ref="P122:Q122"/>
-    <mergeCell ref="P123:Q123"/>
-    <mergeCell ref="P124:Q124"/>
-    <mergeCell ref="P125:Q125"/>
-    <mergeCell ref="P136:Q136"/>
-    <mergeCell ref="P137:Q137"/>
-    <mergeCell ref="P138:Q138"/>
-    <mergeCell ref="P139:Q139"/>
-    <mergeCell ref="P140:Q140"/>
-    <mergeCell ref="P131:Q131"/>
-    <mergeCell ref="P132:Q132"/>
-    <mergeCell ref="P133:Q133"/>
-    <mergeCell ref="P134:Q134"/>
-    <mergeCell ref="P135:Q135"/>
-    <mergeCell ref="B162:T163"/>
-    <mergeCell ref="B164:T167"/>
-    <mergeCell ref="P157:Q157"/>
-    <mergeCell ref="P158:Q158"/>
-    <mergeCell ref="P161:Q161"/>
-    <mergeCell ref="P159:Q159"/>
-    <mergeCell ref="P160:Q160"/>
-    <mergeCell ref="P152:Q152"/>
-    <mergeCell ref="P153:Q153"/>
-    <mergeCell ref="P154:Q154"/>
-    <mergeCell ref="P155:Q155"/>
-    <mergeCell ref="P156:Q156"/>
-    <mergeCell ref="S161:T161"/>
-    <mergeCell ref="P146:Q146"/>
-    <mergeCell ref="P147:Q147"/>
-    <mergeCell ref="P148:Q148"/>
-    <mergeCell ref="P149:Q149"/>
-    <mergeCell ref="P151:Q151"/>
-    <mergeCell ref="P141:Q141"/>
-    <mergeCell ref="P142:Q142"/>
-    <mergeCell ref="P143:Q143"/>
-    <mergeCell ref="P144:Q144"/>
-    <mergeCell ref="P145:Q145"/>
-    <mergeCell ref="P150:Q150"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="U66" r:id="rId1" xr:uid="{60CCA824-04D7-4098-BB5B-CC4EC0E5DE92}"/>
@@ -18071,7 +18060,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D69DBA-AA88-413A-80A7-A9BAAE7F2C32}">
-  <dimension ref="A1:M188"/>
+  <dimension ref="C1:M188"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="8" max="8" width="10.88671875" customWidth="1"/>
@@ -18128,11 +18117,11 @@
       <c r="G4" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H4" s="412">
+      <c r="H4" s="417">
         <v>70</v>
       </c>
-      <c r="I4" s="412"/>
-      <c r="J4" s="413"/>
+      <c r="I4" s="417"/>
+      <c r="J4" s="418"/>
       <c r="K4" s="246"/>
       <c r="L4" s="246"/>
     </row>
@@ -18151,40 +18140,40 @@
       <c r="L5" s="246"/>
     </row>
     <row r="6" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C6" s="414" t="s">
+      <c r="C6" s="419" t="s">
         <v>410</v>
       </c>
-      <c r="D6" s="415"/>
-      <c r="E6" s="415"/>
-      <c r="F6" s="415"/>
-      <c r="G6" s="415"/>
-      <c r="H6" s="415"/>
-      <c r="I6" s="415"/>
-      <c r="J6" s="416"/>
+      <c r="D6" s="420"/>
+      <c r="E6" s="420"/>
+      <c r="F6" s="420"/>
+      <c r="G6" s="420"/>
+      <c r="H6" s="420"/>
+      <c r="I6" s="420"/>
+      <c r="J6" s="421"/>
       <c r="K6" s="246"/>
       <c r="L6" s="246"/>
     </row>
     <row r="7" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C7" s="417"/>
-      <c r="D7" s="418"/>
-      <c r="E7" s="418"/>
-      <c r="F7" s="418"/>
-      <c r="G7" s="418"/>
-      <c r="H7" s="418"/>
-      <c r="I7" s="418"/>
-      <c r="J7" s="419"/>
+      <c r="C7" s="422"/>
+      <c r="D7" s="423"/>
+      <c r="E7" s="423"/>
+      <c r="F7" s="423"/>
+      <c r="G7" s="423"/>
+      <c r="H7" s="423"/>
+      <c r="I7" s="423"/>
+      <c r="J7" s="424"/>
       <c r="K7" s="30"/>
       <c r="L7" s="30"/>
     </row>
     <row r="8" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="420"/>
-      <c r="D8" s="421"/>
-      <c r="E8" s="421"/>
-      <c r="F8" s="421"/>
-      <c r="G8" s="421"/>
-      <c r="H8" s="421"/>
-      <c r="I8" s="421"/>
-      <c r="J8" s="422"/>
+      <c r="C8" s="425"/>
+      <c r="D8" s="426"/>
+      <c r="E8" s="426"/>
+      <c r="F8" s="426"/>
+      <c r="G8" s="426"/>
+      <c r="H8" s="426"/>
+      <c r="I8" s="426"/>
+      <c r="J8" s="427"/>
       <c r="K8" s="30"/>
       <c r="L8" s="30"/>
     </row>
@@ -18240,11 +18229,11 @@
       <c r="G13" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H13" s="412">
+      <c r="H13" s="417">
         <v>60</v>
       </c>
-      <c r="I13" s="412"/>
-      <c r="J13" s="413"/>
+      <c r="I13" s="417"/>
+      <c r="J13" s="418"/>
       <c r="K13" s="246"/>
       <c r="L13" s="246"/>
     </row>
@@ -18263,49 +18252,49 @@
       <c r="L14" s="246"/>
     </row>
     <row r="15" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C15" s="414" t="s">
+      <c r="C15" s="419" t="s">
         <v>419</v>
       </c>
-      <c r="D15" s="415"/>
-      <c r="E15" s="415"/>
-      <c r="F15" s="415"/>
-      <c r="G15" s="415"/>
-      <c r="H15" s="415"/>
-      <c r="I15" s="415"/>
-      <c r="J15" s="416"/>
+      <c r="D15" s="420"/>
+      <c r="E15" s="420"/>
+      <c r="F15" s="420"/>
+      <c r="G15" s="420"/>
+      <c r="H15" s="420"/>
+      <c r="I15" s="420"/>
+      <c r="J15" s="421"/>
       <c r="K15" s="246"/>
       <c r="L15" s="246"/>
     </row>
     <row r="16" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C16" s="417"/>
-      <c r="D16" s="418"/>
-      <c r="E16" s="418"/>
-      <c r="F16" s="418"/>
-      <c r="G16" s="418"/>
-      <c r="H16" s="418"/>
-      <c r="I16" s="418"/>
-      <c r="J16" s="419"/>
+      <c r="C16" s="422"/>
+      <c r="D16" s="423"/>
+      <c r="E16" s="423"/>
+      <c r="F16" s="423"/>
+      <c r="G16" s="423"/>
+      <c r="H16" s="423"/>
+      <c r="I16" s="423"/>
+      <c r="J16" s="424"/>
       <c r="K16" s="246"/>
       <c r="L16" s="246"/>
     </row>
-    <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="420"/>
-      <c r="D17" s="421"/>
-      <c r="E17" s="421"/>
-      <c r="F17" s="421"/>
-      <c r="G17" s="421"/>
-      <c r="H17" s="421"/>
-      <c r="I17" s="421"/>
-      <c r="J17" s="422"/>
+    <row r="17" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="425"/>
+      <c r="D17" s="426"/>
+      <c r="E17" s="426"/>
+      <c r="F17" s="426"/>
+      <c r="G17" s="426"/>
+      <c r="H17" s="426"/>
+      <c r="I17" s="426"/>
+      <c r="J17" s="427"/>
       <c r="K17" s="246"/>
       <c r="L17" s="246"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.3">
       <c r="K18" s="246"/>
       <c r="L18" s="246"/>
     </row>
-    <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C20" s="293" t="s">
         <v>158</v>
       </c>
@@ -18319,7 +18308,7 @@
       <c r="I20" s="199"/>
       <c r="J20" s="200"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C21" s="295"/>
       <c r="D21" s="296"/>
       <c r="E21" s="202"/>
@@ -18336,7 +18325,7 @@
       <c r="K21" s="246"/>
       <c r="L21" s="246"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C22" s="295" t="s">
         <v>159</v>
       </c>
@@ -18350,15 +18339,15 @@
       <c r="G22" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H22" s="412">
+      <c r="H22" s="417">
         <v>72</v>
       </c>
-      <c r="I22" s="412"/>
-      <c r="J22" s="413"/>
+      <c r="I22" s="417"/>
+      <c r="J22" s="418"/>
       <c r="K22" s="246"/>
       <c r="L22" s="246"/>
     </row>
-    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C23" s="295" t="s">
         <v>162</v>
       </c>
@@ -18372,50 +18361,50 @@
       <c r="K23" s="246"/>
       <c r="L23" s="246"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C24" s="414" t="s">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C24" s="419" t="s">
         <v>411</v>
       </c>
-      <c r="D24" s="415"/>
-      <c r="E24" s="415"/>
-      <c r="F24" s="415"/>
-      <c r="G24" s="415"/>
-      <c r="H24" s="415"/>
-      <c r="I24" s="415"/>
-      <c r="J24" s="416"/>
+      <c r="D24" s="420"/>
+      <c r="E24" s="420"/>
+      <c r="F24" s="420"/>
+      <c r="G24" s="420"/>
+      <c r="H24" s="420"/>
+      <c r="I24" s="420"/>
+      <c r="J24" s="421"/>
       <c r="K24" s="246"/>
       <c r="L24" s="246"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C25" s="417"/>
-      <c r="D25" s="418"/>
-      <c r="E25" s="418"/>
-      <c r="F25" s="418"/>
-      <c r="G25" s="418"/>
-      <c r="H25" s="418"/>
-      <c r="I25" s="418"/>
-      <c r="J25" s="419"/>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C25" s="422"/>
+      <c r="D25" s="423"/>
+      <c r="E25" s="423"/>
+      <c r="F25" s="423"/>
+      <c r="G25" s="423"/>
+      <c r="H25" s="423"/>
+      <c r="I25" s="423"/>
+      <c r="J25" s="424"/>
       <c r="K25" s="246"/>
       <c r="L25" s="246"/>
     </row>
-    <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C26" s="420"/>
-      <c r="D26" s="421"/>
-      <c r="E26" s="421"/>
-      <c r="F26" s="421"/>
-      <c r="G26" s="421"/>
-      <c r="H26" s="421"/>
-      <c r="I26" s="421"/>
-      <c r="J26" s="422"/>
+    <row r="26" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C26" s="425"/>
+      <c r="D26" s="426"/>
+      <c r="E26" s="426"/>
+      <c r="F26" s="426"/>
+      <c r="G26" s="426"/>
+      <c r="H26" s="426"/>
+      <c r="I26" s="426"/>
+      <c r="J26" s="427"/>
       <c r="K26" s="246"/>
       <c r="L26" s="246"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.3">
       <c r="K27" s="246"/>
       <c r="L27" s="246"/>
     </row>
-    <row r="28" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C29" s="298" t="s">
         <v>158</v>
       </c>
@@ -18429,11 +18418,7 @@
       <c r="I29" s="199"/>
       <c r="J29" s="200"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="430" t="s">
-        <v>506</v>
-      </c>
-      <c r="B30" s="431"/>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C30" s="300"/>
       <c r="D30" s="301"/>
       <c r="E30" s="202"/>
@@ -18450,9 +18435,7 @@
       <c r="K30" s="246"/>
       <c r="L30" s="246"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="430"/>
-      <c r="B31" s="431"/>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C31" s="300" t="s">
         <v>159</v>
       </c>
@@ -18466,17 +18449,15 @@
       <c r="G31" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H31" s="412" t="s">
+      <c r="H31" s="417" t="s">
         <v>412</v>
       </c>
-      <c r="I31" s="412"/>
-      <c r="J31" s="413"/>
+      <c r="I31" s="417"/>
+      <c r="J31" s="418"/>
       <c r="K31" s="246"/>
       <c r="L31" s="246"/>
     </row>
-    <row r="32" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="430"/>
-      <c r="B32" s="431"/>
+    <row r="32" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C32" s="300" t="s">
         <v>162</v>
       </c>
@@ -18490,48 +18471,46 @@
       <c r="K32" s="246"/>
       <c r="L32" s="246"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="430"/>
-      <c r="B33" s="431"/>
-      <c r="C33" s="414" t="s">
-        <v>425</v>
-      </c>
-      <c r="D33" s="415"/>
-      <c r="E33" s="415"/>
-      <c r="F33" s="415"/>
-      <c r="G33" s="415"/>
-      <c r="H33" s="415"/>
-      <c r="I33" s="415"/>
-      <c r="J33" s="416"/>
+    <row r="33" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C33" s="419" t="s">
+        <v>424</v>
+      </c>
+      <c r="D33" s="420"/>
+      <c r="E33" s="420"/>
+      <c r="F33" s="420"/>
+      <c r="G33" s="420"/>
+      <c r="H33" s="420"/>
+      <c r="I33" s="420"/>
+      <c r="J33" s="421"/>
       <c r="K33" s="246"/>
       <c r="L33" s="246"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C34" s="417"/>
-      <c r="D34" s="418"/>
-      <c r="E34" s="418"/>
-      <c r="F34" s="418"/>
-      <c r="G34" s="418"/>
-      <c r="H34" s="418"/>
-      <c r="I34" s="418"/>
-      <c r="J34" s="419"/>
+    <row r="34" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C34" s="422"/>
+      <c r="D34" s="423"/>
+      <c r="E34" s="423"/>
+      <c r="F34" s="423"/>
+      <c r="G34" s="423"/>
+      <c r="H34" s="423"/>
+      <c r="I34" s="423"/>
+      <c r="J34" s="424"/>
       <c r="K34" s="246"/>
       <c r="L34" s="246"/>
     </row>
-    <row r="35" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C35" s="420"/>
-      <c r="D35" s="421"/>
-      <c r="E35" s="421"/>
-      <c r="F35" s="421"/>
-      <c r="G35" s="421"/>
-      <c r="H35" s="421"/>
-      <c r="I35" s="421"/>
-      <c r="J35" s="422"/>
+    <row r="35" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C35" s="425"/>
+      <c r="D35" s="426"/>
+      <c r="E35" s="426"/>
+      <c r="F35" s="426"/>
+      <c r="G35" s="426"/>
+      <c r="H35" s="426"/>
+      <c r="I35" s="426"/>
+      <c r="J35" s="427"/>
       <c r="K35" s="246"/>
       <c r="L35" s="246"/>
     </row>
-    <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="38" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C38" s="303" t="s">
         <v>158</v>
       </c>
@@ -18547,7 +18526,7 @@
       <c r="K38" s="246"/>
       <c r="L38" s="246"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C39" s="305"/>
       <c r="D39" s="306"/>
       <c r="E39" s="202"/>
@@ -18564,7 +18543,7 @@
       <c r="K39" s="246"/>
       <c r="L39" s="246"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C40" s="305" t="s">
         <v>159</v>
       </c>
@@ -18578,15 +18557,15 @@
       <c r="G40" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H40" s="412">
+      <c r="H40" s="417">
         <v>112</v>
       </c>
-      <c r="I40" s="412"/>
-      <c r="J40" s="413"/>
+      <c r="I40" s="417"/>
+      <c r="J40" s="418"/>
       <c r="K40" s="246"/>
       <c r="L40" s="246"/>
     </row>
-    <row r="41" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C41" s="305" t="s">
         <v>162</v>
       </c>
@@ -18600,46 +18579,46 @@
       <c r="K41" s="246"/>
       <c r="L41" s="246"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C42" s="414" t="s">
+    <row r="42" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C42" s="419" t="s">
         <v>413</v>
       </c>
-      <c r="D42" s="415"/>
-      <c r="E42" s="415"/>
-      <c r="F42" s="415"/>
-      <c r="G42" s="415"/>
-      <c r="H42" s="415"/>
-      <c r="I42" s="415"/>
-      <c r="J42" s="416"/>
+      <c r="D42" s="420"/>
+      <c r="E42" s="420"/>
+      <c r="F42" s="420"/>
+      <c r="G42" s="420"/>
+      <c r="H42" s="420"/>
+      <c r="I42" s="420"/>
+      <c r="J42" s="421"/>
       <c r="K42" s="246"/>
       <c r="L42" s="246"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C43" s="417"/>
-      <c r="D43" s="418"/>
-      <c r="E43" s="418"/>
-      <c r="F43" s="418"/>
-      <c r="G43" s="418"/>
-      <c r="H43" s="418"/>
-      <c r="I43" s="418"/>
-      <c r="J43" s="419"/>
+    <row r="43" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C43" s="422"/>
+      <c r="D43" s="423"/>
+      <c r="E43" s="423"/>
+      <c r="F43" s="423"/>
+      <c r="G43" s="423"/>
+      <c r="H43" s="423"/>
+      <c r="I43" s="423"/>
+      <c r="J43" s="424"/>
       <c r="K43" s="246"/>
       <c r="L43" s="246"/>
     </row>
-    <row r="44" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C44" s="420"/>
-      <c r="D44" s="421"/>
-      <c r="E44" s="421"/>
-      <c r="F44" s="421"/>
-      <c r="G44" s="421"/>
-      <c r="H44" s="421"/>
-      <c r="I44" s="421"/>
-      <c r="J44" s="422"/>
+    <row r="44" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C44" s="425"/>
+      <c r="D44" s="426"/>
+      <c r="E44" s="426"/>
+      <c r="F44" s="426"/>
+      <c r="G44" s="426"/>
+      <c r="H44" s="426"/>
+      <c r="I44" s="426"/>
+      <c r="J44" s="427"/>
       <c r="K44" s="246"/>
       <c r="L44" s="246"/>
     </row>
-    <row r="46" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="47" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C47" s="308" t="s">
         <v>158</v>
       </c>
@@ -18655,7 +18634,7 @@
       <c r="K47" s="246"/>
       <c r="L47" s="246"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C48" s="310"/>
       <c r="D48" s="311"/>
       <c r="E48" s="202"/>
@@ -18686,11 +18665,11 @@
       <c r="G49" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H49" s="412" t="s">
+      <c r="H49" s="417" t="s">
         <v>414</v>
       </c>
-      <c r="I49" s="412"/>
-      <c r="J49" s="413"/>
+      <c r="I49" s="417"/>
+      <c r="J49" s="418"/>
       <c r="K49" s="246"/>
       <c r="L49" s="246"/>
     </row>
@@ -18709,40 +18688,40 @@
       <c r="L50" s="246"/>
     </row>
     <row r="51" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C51" s="414" t="s">
+      <c r="C51" s="419" t="s">
         <v>415</v>
       </c>
-      <c r="D51" s="415"/>
-      <c r="E51" s="415"/>
-      <c r="F51" s="415"/>
-      <c r="G51" s="415"/>
-      <c r="H51" s="415"/>
-      <c r="I51" s="415"/>
-      <c r="J51" s="416"/>
+      <c r="D51" s="420"/>
+      <c r="E51" s="420"/>
+      <c r="F51" s="420"/>
+      <c r="G51" s="420"/>
+      <c r="H51" s="420"/>
+      <c r="I51" s="420"/>
+      <c r="J51" s="421"/>
       <c r="K51" s="246"/>
       <c r="L51" s="246"/>
     </row>
     <row r="52" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C52" s="417"/>
-      <c r="D52" s="418"/>
-      <c r="E52" s="418"/>
-      <c r="F52" s="418"/>
-      <c r="G52" s="418"/>
-      <c r="H52" s="418"/>
-      <c r="I52" s="418"/>
-      <c r="J52" s="419"/>
+      <c r="C52" s="422"/>
+      <c r="D52" s="423"/>
+      <c r="E52" s="423"/>
+      <c r="F52" s="423"/>
+      <c r="G52" s="423"/>
+      <c r="H52" s="423"/>
+      <c r="I52" s="423"/>
+      <c r="J52" s="424"/>
       <c r="K52" s="246"/>
       <c r="L52" s="246"/>
     </row>
     <row r="53" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C53" s="420"/>
-      <c r="D53" s="421"/>
-      <c r="E53" s="421"/>
-      <c r="F53" s="421"/>
-      <c r="G53" s="421"/>
-      <c r="H53" s="421"/>
-      <c r="I53" s="421"/>
-      <c r="J53" s="422"/>
+      <c r="C53" s="425"/>
+      <c r="D53" s="426"/>
+      <c r="E53" s="426"/>
+      <c r="F53" s="426"/>
+      <c r="G53" s="426"/>
+      <c r="H53" s="426"/>
+      <c r="I53" s="426"/>
+      <c r="J53" s="427"/>
       <c r="K53" s="246"/>
       <c r="L53" s="246"/>
     </row>
@@ -18798,11 +18777,11 @@
       <c r="G58" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H58" s="412" t="s">
+      <c r="H58" s="417" t="s">
         <v>416</v>
       </c>
-      <c r="I58" s="412"/>
-      <c r="J58" s="413"/>
+      <c r="I58" s="417"/>
+      <c r="J58" s="418"/>
       <c r="K58" s="246"/>
       <c r="L58" s="246"/>
     </row>
@@ -18821,40 +18800,40 @@
       <c r="L59" s="246"/>
     </row>
     <row r="60" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C60" s="414" t="s">
+      <c r="C60" s="419" t="s">
         <v>417</v>
       </c>
-      <c r="D60" s="415"/>
-      <c r="E60" s="415"/>
-      <c r="F60" s="415"/>
-      <c r="G60" s="415"/>
-      <c r="H60" s="415"/>
-      <c r="I60" s="415"/>
-      <c r="J60" s="416"/>
+      <c r="D60" s="420"/>
+      <c r="E60" s="420"/>
+      <c r="F60" s="420"/>
+      <c r="G60" s="420"/>
+      <c r="H60" s="420"/>
+      <c r="I60" s="420"/>
+      <c r="J60" s="421"/>
       <c r="K60" s="246"/>
       <c r="L60" s="246"/>
     </row>
     <row r="61" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C61" s="417"/>
-      <c r="D61" s="418"/>
-      <c r="E61" s="418"/>
-      <c r="F61" s="418"/>
-      <c r="G61" s="418"/>
-      <c r="H61" s="418"/>
-      <c r="I61" s="418"/>
-      <c r="J61" s="419"/>
+      <c r="C61" s="422"/>
+      <c r="D61" s="423"/>
+      <c r="E61" s="423"/>
+      <c r="F61" s="423"/>
+      <c r="G61" s="423"/>
+      <c r="H61" s="423"/>
+      <c r="I61" s="423"/>
+      <c r="J61" s="424"/>
       <c r="K61" s="246"/>
       <c r="L61" s="246"/>
     </row>
     <row r="62" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C62" s="420"/>
-      <c r="D62" s="421"/>
-      <c r="E62" s="421"/>
-      <c r="F62" s="421"/>
-      <c r="G62" s="421"/>
-      <c r="H62" s="421"/>
-      <c r="I62" s="421"/>
-      <c r="J62" s="422"/>
+      <c r="C62" s="425"/>
+      <c r="D62" s="426"/>
+      <c r="E62" s="426"/>
+      <c r="F62" s="426"/>
+      <c r="G62" s="426"/>
+      <c r="H62" s="426"/>
+      <c r="I62" s="426"/>
+      <c r="J62" s="427"/>
       <c r="K62" s="246"/>
       <c r="L62" s="246"/>
     </row>
@@ -18905,11 +18884,11 @@
       <c r="G67" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H67" s="412">
+      <c r="H67" s="417">
         <v>119</v>
       </c>
-      <c r="I67" s="412"/>
-      <c r="J67" s="413"/>
+      <c r="I67" s="417"/>
+      <c r="J67" s="418"/>
       <c r="K67" s="246"/>
       <c r="L67" s="246"/>
       <c r="M67" s="246"/>
@@ -18930,42 +18909,42 @@
       <c r="M68" s="246"/>
     </row>
     <row r="69" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C69" s="414" t="s">
+      <c r="C69" s="419" t="s">
         <v>418</v>
       </c>
-      <c r="D69" s="415"/>
-      <c r="E69" s="415"/>
-      <c r="F69" s="415"/>
-      <c r="G69" s="415"/>
-      <c r="H69" s="415"/>
-      <c r="I69" s="415"/>
-      <c r="J69" s="416"/>
+      <c r="D69" s="420"/>
+      <c r="E69" s="420"/>
+      <c r="F69" s="420"/>
+      <c r="G69" s="420"/>
+      <c r="H69" s="420"/>
+      <c r="I69" s="420"/>
+      <c r="J69" s="421"/>
       <c r="K69" s="246"/>
       <c r="L69" s="246"/>
       <c r="M69" s="246"/>
     </row>
     <row r="70" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C70" s="417"/>
-      <c r="D70" s="418"/>
-      <c r="E70" s="418"/>
-      <c r="F70" s="418"/>
-      <c r="G70" s="418"/>
-      <c r="H70" s="418"/>
-      <c r="I70" s="418"/>
-      <c r="J70" s="419"/>
+      <c r="C70" s="422"/>
+      <c r="D70" s="423"/>
+      <c r="E70" s="423"/>
+      <c r="F70" s="423"/>
+      <c r="G70" s="423"/>
+      <c r="H70" s="423"/>
+      <c r="I70" s="423"/>
+      <c r="J70" s="424"/>
       <c r="K70" s="246"/>
       <c r="L70" s="246"/>
       <c r="M70" s="246"/>
     </row>
     <row r="71" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C71" s="420"/>
-      <c r="D71" s="421"/>
-      <c r="E71" s="421"/>
-      <c r="F71" s="421"/>
-      <c r="G71" s="421"/>
-      <c r="H71" s="421"/>
-      <c r="I71" s="421"/>
-      <c r="J71" s="422"/>
+      <c r="C71" s="425"/>
+      <c r="D71" s="426"/>
+      <c r="E71" s="426"/>
+      <c r="F71" s="426"/>
+      <c r="G71" s="426"/>
+      <c r="H71" s="426"/>
+      <c r="I71" s="426"/>
+      <c r="J71" s="427"/>
       <c r="K71" s="246"/>
       <c r="L71" s="246"/>
       <c r="M71" s="246"/>
@@ -19018,11 +18997,11 @@
       <c r="G76" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H76" s="412">
+      <c r="H76" s="417">
         <v>36</v>
       </c>
-      <c r="I76" s="412"/>
-      <c r="J76" s="413"/>
+      <c r="I76" s="417"/>
+      <c r="J76" s="418"/>
       <c r="K76" s="246"/>
       <c r="L76" s="246"/>
     </row>
@@ -19041,40 +19020,40 @@
       <c r="L77" s="246"/>
     </row>
     <row r="78" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C78" s="414" t="s">
+      <c r="C78" s="419" t="s">
         <v>421</v>
       </c>
-      <c r="D78" s="415"/>
-      <c r="E78" s="415"/>
-      <c r="F78" s="415"/>
-      <c r="G78" s="415"/>
-      <c r="H78" s="415"/>
-      <c r="I78" s="415"/>
-      <c r="J78" s="416"/>
+      <c r="D78" s="420"/>
+      <c r="E78" s="420"/>
+      <c r="F78" s="420"/>
+      <c r="G78" s="420"/>
+      <c r="H78" s="420"/>
+      <c r="I78" s="420"/>
+      <c r="J78" s="421"/>
       <c r="K78" s="246"/>
       <c r="L78" s="246"/>
     </row>
     <row r="79" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C79" s="417"/>
-      <c r="D79" s="418"/>
-      <c r="E79" s="418"/>
-      <c r="F79" s="418"/>
-      <c r="G79" s="418"/>
-      <c r="H79" s="418"/>
-      <c r="I79" s="418"/>
-      <c r="J79" s="419"/>
+      <c r="C79" s="422"/>
+      <c r="D79" s="423"/>
+      <c r="E79" s="423"/>
+      <c r="F79" s="423"/>
+      <c r="G79" s="423"/>
+      <c r="H79" s="423"/>
+      <c r="I79" s="423"/>
+      <c r="J79" s="424"/>
       <c r="K79" s="246"/>
       <c r="L79" s="246"/>
     </row>
     <row r="80" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C80" s="420"/>
-      <c r="D80" s="421"/>
-      <c r="E80" s="421"/>
-      <c r="F80" s="421"/>
-      <c r="G80" s="421"/>
-      <c r="H80" s="421"/>
-      <c r="I80" s="421"/>
-      <c r="J80" s="422"/>
+      <c r="C80" s="425"/>
+      <c r="D80" s="426"/>
+      <c r="E80" s="426"/>
+      <c r="F80" s="426"/>
+      <c r="G80" s="426"/>
+      <c r="H80" s="426"/>
+      <c r="I80" s="426"/>
+      <c r="J80" s="427"/>
       <c r="K80" s="246"/>
       <c r="L80" s="246"/>
     </row>
@@ -19109,10 +19088,8 @@
         <v>10</v>
       </c>
       <c r="J84" s="50"/>
-      <c r="K84" s="428" t="s">
-        <v>505</v>
-      </c>
-      <c r="L84" s="429"/>
+      <c r="K84" s="429"/>
+      <c r="L84" s="430"/>
     </row>
     <row r="85" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C85" s="326" t="s">
@@ -19128,13 +19105,13 @@
       <c r="G85" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H85" s="412" t="s">
-        <v>423</v>
-      </c>
-      <c r="I85" s="412"/>
-      <c r="J85" s="413"/>
-      <c r="K85" s="428"/>
-      <c r="L85" s="429"/>
+      <c r="H85" s="417">
+        <v>28</v>
+      </c>
+      <c r="I85" s="417"/>
+      <c r="J85" s="418"/>
+      <c r="K85" s="429"/>
+      <c r="L85" s="430"/>
     </row>
     <row r="86" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C86" s="326" t="s">
@@ -19147,42 +19124,42 @@
       <c r="H86" s="30"/>
       <c r="I86" s="30"/>
       <c r="J86" s="51"/>
-      <c r="K86" s="428"/>
-      <c r="L86" s="429"/>
+      <c r="K86" s="429"/>
+      <c r="L86" s="430"/>
     </row>
     <row r="87" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C87" s="414" t="s">
-        <v>424</v>
-      </c>
-      <c r="D87" s="415"/>
-      <c r="E87" s="415"/>
-      <c r="F87" s="415"/>
-      <c r="G87" s="415"/>
-      <c r="H87" s="415"/>
-      <c r="I87" s="415"/>
-      <c r="J87" s="416"/>
-      <c r="K87" s="428"/>
-      <c r="L87" s="429"/>
+      <c r="C87" s="419" t="s">
+        <v>423</v>
+      </c>
+      <c r="D87" s="420"/>
+      <c r="E87" s="420"/>
+      <c r="F87" s="420"/>
+      <c r="G87" s="420"/>
+      <c r="H87" s="420"/>
+      <c r="I87" s="420"/>
+      <c r="J87" s="421"/>
+      <c r="K87" s="429"/>
+      <c r="L87" s="430"/>
     </row>
     <row r="88" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C88" s="417"/>
-      <c r="D88" s="418"/>
-      <c r="E88" s="418"/>
-      <c r="F88" s="418"/>
-      <c r="G88" s="418"/>
-      <c r="H88" s="418"/>
-      <c r="I88" s="418"/>
-      <c r="J88" s="419"/>
+      <c r="C88" s="422"/>
+      <c r="D88" s="423"/>
+      <c r="E88" s="423"/>
+      <c r="F88" s="423"/>
+      <c r="G88" s="423"/>
+      <c r="H88" s="423"/>
+      <c r="I88" s="423"/>
+      <c r="J88" s="424"/>
     </row>
     <row r="89" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C89" s="420"/>
-      <c r="D89" s="421"/>
-      <c r="E89" s="421"/>
-      <c r="F89" s="421"/>
-      <c r="G89" s="421"/>
-      <c r="H89" s="421"/>
-      <c r="I89" s="421"/>
-      <c r="J89" s="422"/>
+      <c r="C89" s="425"/>
+      <c r="D89" s="426"/>
+      <c r="E89" s="426"/>
+      <c r="F89" s="426"/>
+      <c r="G89" s="426"/>
+      <c r="H89" s="426"/>
+      <c r="I89" s="426"/>
+      <c r="J89" s="427"/>
     </row>
     <row r="91" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="92" spans="3:12" x14ac:dyDescent="0.3">
@@ -19232,11 +19209,11 @@
       <c r="G94" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H94" s="412">
+      <c r="H94" s="417">
         <v>139</v>
       </c>
-      <c r="I94" s="412"/>
-      <c r="J94" s="413"/>
+      <c r="I94" s="417"/>
+      <c r="J94" s="418"/>
       <c r="K94" s="246"/>
       <c r="L94" s="246"/>
     </row>
@@ -19255,40 +19232,40 @@
       <c r="L95" s="246"/>
     </row>
     <row r="96" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C96" s="414" t="s">
-        <v>426</v>
-      </c>
-      <c r="D96" s="415"/>
-      <c r="E96" s="415"/>
-      <c r="F96" s="415"/>
-      <c r="G96" s="415"/>
-      <c r="H96" s="415"/>
-      <c r="I96" s="415"/>
-      <c r="J96" s="416"/>
+      <c r="C96" s="419" t="s">
+        <v>425</v>
+      </c>
+      <c r="D96" s="420"/>
+      <c r="E96" s="420"/>
+      <c r="F96" s="420"/>
+      <c r="G96" s="420"/>
+      <c r="H96" s="420"/>
+      <c r="I96" s="420"/>
+      <c r="J96" s="421"/>
       <c r="K96" s="246"/>
       <c r="L96" s="246"/>
     </row>
     <row r="97" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C97" s="417"/>
-      <c r="D97" s="418"/>
-      <c r="E97" s="418"/>
-      <c r="F97" s="418"/>
-      <c r="G97" s="418"/>
-      <c r="H97" s="418"/>
-      <c r="I97" s="418"/>
-      <c r="J97" s="419"/>
+      <c r="C97" s="422"/>
+      <c r="D97" s="423"/>
+      <c r="E97" s="423"/>
+      <c r="F97" s="423"/>
+      <c r="G97" s="423"/>
+      <c r="H97" s="423"/>
+      <c r="I97" s="423"/>
+      <c r="J97" s="424"/>
       <c r="K97" s="246"/>
       <c r="L97" s="246"/>
     </row>
     <row r="98" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C98" s="420"/>
-      <c r="D98" s="421"/>
-      <c r="E98" s="421"/>
-      <c r="F98" s="421"/>
-      <c r="G98" s="421"/>
-      <c r="H98" s="421"/>
-      <c r="I98" s="421"/>
-      <c r="J98" s="422"/>
+      <c r="C98" s="425"/>
+      <c r="D98" s="426"/>
+      <c r="E98" s="426"/>
+      <c r="F98" s="426"/>
+      <c r="G98" s="426"/>
+      <c r="H98" s="426"/>
+      <c r="I98" s="426"/>
+      <c r="J98" s="427"/>
     </row>
     <row r="100" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="101" spans="3:12" x14ac:dyDescent="0.3">
@@ -19338,11 +19315,11 @@
       <c r="G103" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H103" s="412">
+      <c r="H103" s="417">
         <v>39</v>
       </c>
-      <c r="I103" s="412"/>
-      <c r="J103" s="413"/>
+      <c r="I103" s="417"/>
+      <c r="J103" s="418"/>
       <c r="K103" s="246"/>
       <c r="L103" s="246"/>
     </row>
@@ -19361,40 +19338,40 @@
       <c r="L104" s="246"/>
     </row>
     <row r="105" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C105" s="414" t="s">
-        <v>427</v>
-      </c>
-      <c r="D105" s="415"/>
-      <c r="E105" s="415"/>
-      <c r="F105" s="415"/>
-      <c r="G105" s="415"/>
-      <c r="H105" s="415"/>
-      <c r="I105" s="415"/>
-      <c r="J105" s="416"/>
+      <c r="C105" s="419" t="s">
+        <v>426</v>
+      </c>
+      <c r="D105" s="420"/>
+      <c r="E105" s="420"/>
+      <c r="F105" s="420"/>
+      <c r="G105" s="420"/>
+      <c r="H105" s="420"/>
+      <c r="I105" s="420"/>
+      <c r="J105" s="421"/>
       <c r="K105" s="246"/>
       <c r="L105" s="246"/>
     </row>
     <row r="106" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C106" s="417"/>
-      <c r="D106" s="418"/>
-      <c r="E106" s="418"/>
-      <c r="F106" s="418"/>
-      <c r="G106" s="418"/>
-      <c r="H106" s="418"/>
-      <c r="I106" s="418"/>
-      <c r="J106" s="419"/>
+      <c r="C106" s="422"/>
+      <c r="D106" s="423"/>
+      <c r="E106" s="423"/>
+      <c r="F106" s="423"/>
+      <c r="G106" s="423"/>
+      <c r="H106" s="423"/>
+      <c r="I106" s="423"/>
+      <c r="J106" s="424"/>
       <c r="K106" s="246"/>
       <c r="L106" s="246"/>
     </row>
     <row r="107" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C107" s="420"/>
-      <c r="D107" s="421"/>
-      <c r="E107" s="421"/>
-      <c r="F107" s="421"/>
-      <c r="G107" s="421"/>
-      <c r="H107" s="421"/>
-      <c r="I107" s="421"/>
-      <c r="J107" s="422"/>
+      <c r="C107" s="425"/>
+      <c r="D107" s="426"/>
+      <c r="E107" s="426"/>
+      <c r="F107" s="426"/>
+      <c r="G107" s="426"/>
+      <c r="H107" s="426"/>
+      <c r="I107" s="426"/>
+      <c r="J107" s="427"/>
     </row>
     <row r="109" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="110" spans="3:12" x14ac:dyDescent="0.3">
@@ -19444,11 +19421,11 @@
       <c r="G112" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H112" s="412">
+      <c r="H112" s="417">
         <v>138</v>
       </c>
-      <c r="I112" s="412"/>
-      <c r="J112" s="413"/>
+      <c r="I112" s="417"/>
+      <c r="J112" s="418"/>
       <c r="K112" s="246"/>
       <c r="L112" s="246"/>
     </row>
@@ -19467,40 +19444,40 @@
       <c r="L113" s="246"/>
     </row>
     <row r="114" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C114" s="414" t="s">
-        <v>428</v>
-      </c>
-      <c r="D114" s="415"/>
-      <c r="E114" s="415"/>
-      <c r="F114" s="415"/>
-      <c r="G114" s="415"/>
-      <c r="H114" s="415"/>
-      <c r="I114" s="415"/>
-      <c r="J114" s="416"/>
+      <c r="C114" s="419" t="s">
+        <v>427</v>
+      </c>
+      <c r="D114" s="420"/>
+      <c r="E114" s="420"/>
+      <c r="F114" s="420"/>
+      <c r="G114" s="420"/>
+      <c r="H114" s="420"/>
+      <c r="I114" s="420"/>
+      <c r="J114" s="421"/>
       <c r="K114" s="246"/>
       <c r="L114" s="246"/>
     </row>
     <row r="115" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C115" s="417"/>
-      <c r="D115" s="418"/>
-      <c r="E115" s="418"/>
-      <c r="F115" s="418"/>
-      <c r="G115" s="418"/>
-      <c r="H115" s="418"/>
-      <c r="I115" s="418"/>
-      <c r="J115" s="419"/>
+      <c r="C115" s="422"/>
+      <c r="D115" s="423"/>
+      <c r="E115" s="423"/>
+      <c r="F115" s="423"/>
+      <c r="G115" s="423"/>
+      <c r="H115" s="423"/>
+      <c r="I115" s="423"/>
+      <c r="J115" s="424"/>
       <c r="K115" s="246"/>
       <c r="L115" s="246"/>
     </row>
     <row r="116" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C116" s="420"/>
-      <c r="D116" s="421"/>
-      <c r="E116" s="421"/>
-      <c r="F116" s="421"/>
-      <c r="G116" s="421"/>
-      <c r="H116" s="421"/>
-      <c r="I116" s="421"/>
-      <c r="J116" s="422"/>
+      <c r="C116" s="425"/>
+      <c r="D116" s="426"/>
+      <c r="E116" s="426"/>
+      <c r="F116" s="426"/>
+      <c r="G116" s="426"/>
+      <c r="H116" s="426"/>
+      <c r="I116" s="426"/>
+      <c r="J116" s="427"/>
       <c r="K116" s="246"/>
       <c r="L116" s="246"/>
     </row>
@@ -19556,11 +19533,11 @@
       <c r="G121" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H121" s="412" t="s">
-        <v>429</v>
-      </c>
-      <c r="I121" s="412"/>
-      <c r="J121" s="413"/>
+      <c r="H121" s="417" t="s">
+        <v>428</v>
+      </c>
+      <c r="I121" s="417"/>
+      <c r="J121" s="418"/>
       <c r="K121" s="246"/>
       <c r="L121" s="246"/>
     </row>
@@ -19579,40 +19556,40 @@
       <c r="L122" s="246"/>
     </row>
     <row r="123" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C123" s="414" t="s">
-        <v>430</v>
-      </c>
-      <c r="D123" s="415"/>
-      <c r="E123" s="415"/>
-      <c r="F123" s="415"/>
-      <c r="G123" s="415"/>
-      <c r="H123" s="415"/>
-      <c r="I123" s="415"/>
-      <c r="J123" s="416"/>
+      <c r="C123" s="419" t="s">
+        <v>429</v>
+      </c>
+      <c r="D123" s="420"/>
+      <c r="E123" s="420"/>
+      <c r="F123" s="420"/>
+      <c r="G123" s="420"/>
+      <c r="H123" s="420"/>
+      <c r="I123" s="420"/>
+      <c r="J123" s="421"/>
       <c r="K123" s="246"/>
       <c r="L123" s="246"/>
     </row>
     <row r="124" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C124" s="417"/>
-      <c r="D124" s="418"/>
-      <c r="E124" s="418"/>
-      <c r="F124" s="418"/>
-      <c r="G124" s="418"/>
-      <c r="H124" s="418"/>
-      <c r="I124" s="418"/>
-      <c r="J124" s="419"/>
+      <c r="C124" s="422"/>
+      <c r="D124" s="423"/>
+      <c r="E124" s="423"/>
+      <c r="F124" s="423"/>
+      <c r="G124" s="423"/>
+      <c r="H124" s="423"/>
+      <c r="I124" s="423"/>
+      <c r="J124" s="424"/>
       <c r="K124" s="246"/>
       <c r="L124" s="246"/>
     </row>
     <row r="125" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C125" s="420"/>
-      <c r="D125" s="421"/>
-      <c r="E125" s="421"/>
-      <c r="F125" s="421"/>
-      <c r="G125" s="421"/>
-      <c r="H125" s="421"/>
-      <c r="I125" s="421"/>
-      <c r="J125" s="422"/>
+      <c r="C125" s="425"/>
+      <c r="D125" s="426"/>
+      <c r="E125" s="426"/>
+      <c r="F125" s="426"/>
+      <c r="G125" s="426"/>
+      <c r="H125" s="426"/>
+      <c r="I125" s="426"/>
+      <c r="J125" s="427"/>
       <c r="K125" s="246"/>
       <c r="L125" s="246"/>
     </row>
@@ -19662,11 +19639,11 @@
       <c r="G130" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H130" s="412">
+      <c r="H130" s="417">
         <v>45</v>
       </c>
-      <c r="I130" s="412"/>
-      <c r="J130" s="413"/>
+      <c r="I130" s="417"/>
+      <c r="J130" s="418"/>
       <c r="K130" s="246"/>
       <c r="L130" s="246"/>
     </row>
@@ -19685,40 +19662,40 @@
       <c r="L131" s="246"/>
     </row>
     <row r="132" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C132" s="414" t="s">
-        <v>431</v>
-      </c>
-      <c r="D132" s="415"/>
-      <c r="E132" s="415"/>
-      <c r="F132" s="415"/>
-      <c r="G132" s="415"/>
-      <c r="H132" s="415"/>
-      <c r="I132" s="415"/>
-      <c r="J132" s="416"/>
+      <c r="C132" s="419" t="s">
+        <v>430</v>
+      </c>
+      <c r="D132" s="420"/>
+      <c r="E132" s="420"/>
+      <c r="F132" s="420"/>
+      <c r="G132" s="420"/>
+      <c r="H132" s="420"/>
+      <c r="I132" s="420"/>
+      <c r="J132" s="421"/>
       <c r="K132" s="246"/>
       <c r="L132" s="246"/>
     </row>
     <row r="133" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C133" s="417"/>
-      <c r="D133" s="418"/>
-      <c r="E133" s="418"/>
-      <c r="F133" s="418"/>
-      <c r="G133" s="418"/>
-      <c r="H133" s="418"/>
-      <c r="I133" s="418"/>
-      <c r="J133" s="419"/>
+      <c r="C133" s="422"/>
+      <c r="D133" s="423"/>
+      <c r="E133" s="423"/>
+      <c r="F133" s="423"/>
+      <c r="G133" s="423"/>
+      <c r="H133" s="423"/>
+      <c r="I133" s="423"/>
+      <c r="J133" s="424"/>
       <c r="K133" s="246"/>
       <c r="L133" s="246"/>
     </row>
     <row r="134" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C134" s="420"/>
-      <c r="D134" s="421"/>
-      <c r="E134" s="421"/>
-      <c r="F134" s="421"/>
-      <c r="G134" s="421"/>
-      <c r="H134" s="421"/>
-      <c r="I134" s="421"/>
-      <c r="J134" s="422"/>
+      <c r="C134" s="425"/>
+      <c r="D134" s="426"/>
+      <c r="E134" s="426"/>
+      <c r="F134" s="426"/>
+      <c r="G134" s="426"/>
+      <c r="H134" s="426"/>
+      <c r="I134" s="426"/>
+      <c r="J134" s="427"/>
     </row>
     <row r="136" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="137" spans="3:13" x14ac:dyDescent="0.3">
@@ -19770,11 +19747,11 @@
       <c r="G139" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H139" s="412">
+      <c r="H139" s="417">
         <v>78</v>
       </c>
-      <c r="I139" s="412"/>
-      <c r="J139" s="413"/>
+      <c r="I139" s="417"/>
+      <c r="J139" s="418"/>
       <c r="K139" s="246"/>
       <c r="L139" s="246"/>
       <c r="M139" s="246"/>
@@ -19795,42 +19772,42 @@
       <c r="M140" s="246"/>
     </row>
     <row r="141" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C141" s="414" t="s">
-        <v>432</v>
-      </c>
-      <c r="D141" s="415"/>
-      <c r="E141" s="415"/>
-      <c r="F141" s="415"/>
-      <c r="G141" s="415"/>
-      <c r="H141" s="415"/>
-      <c r="I141" s="415"/>
-      <c r="J141" s="416"/>
+      <c r="C141" s="419" t="s">
+        <v>431</v>
+      </c>
+      <c r="D141" s="420"/>
+      <c r="E141" s="420"/>
+      <c r="F141" s="420"/>
+      <c r="G141" s="420"/>
+      <c r="H141" s="420"/>
+      <c r="I141" s="420"/>
+      <c r="J141" s="421"/>
       <c r="K141" s="246"/>
       <c r="L141" s="246"/>
       <c r="M141" s="246"/>
     </row>
     <row r="142" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C142" s="417"/>
-      <c r="D142" s="418"/>
-      <c r="E142" s="418"/>
-      <c r="F142" s="418"/>
-      <c r="G142" s="418"/>
-      <c r="H142" s="418"/>
-      <c r="I142" s="418"/>
-      <c r="J142" s="419"/>
+      <c r="C142" s="422"/>
+      <c r="D142" s="423"/>
+      <c r="E142" s="423"/>
+      <c r="F142" s="423"/>
+      <c r="G142" s="423"/>
+      <c r="H142" s="423"/>
+      <c r="I142" s="423"/>
+      <c r="J142" s="424"/>
       <c r="K142" s="246"/>
       <c r="L142" s="246"/>
       <c r="M142" s="246"/>
     </row>
     <row r="143" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C143" s="420"/>
-      <c r="D143" s="421"/>
-      <c r="E143" s="421"/>
-      <c r="F143" s="421"/>
-      <c r="G143" s="421"/>
-      <c r="H143" s="421"/>
-      <c r="I143" s="421"/>
-      <c r="J143" s="422"/>
+      <c r="C143" s="425"/>
+      <c r="D143" s="426"/>
+      <c r="E143" s="426"/>
+      <c r="F143" s="426"/>
+      <c r="G143" s="426"/>
+      <c r="H143" s="426"/>
+      <c r="I143" s="426"/>
+      <c r="J143" s="427"/>
       <c r="K143" s="246"/>
       <c r="L143" s="246"/>
       <c r="M143" s="246"/>
@@ -19883,11 +19860,11 @@
       <c r="G148" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H148" s="412">
+      <c r="H148" s="417">
         <v>96</v>
       </c>
-      <c r="I148" s="412"/>
-      <c r="J148" s="413"/>
+      <c r="I148" s="417"/>
+      <c r="J148" s="418"/>
       <c r="K148" s="246"/>
       <c r="L148" s="246"/>
     </row>
@@ -19906,40 +19883,40 @@
       <c r="L149" s="246"/>
     </row>
     <row r="150" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C150" s="414" t="s">
-        <v>433</v>
-      </c>
-      <c r="D150" s="415"/>
-      <c r="E150" s="415"/>
-      <c r="F150" s="415"/>
-      <c r="G150" s="415"/>
-      <c r="H150" s="415"/>
-      <c r="I150" s="415"/>
-      <c r="J150" s="416"/>
+      <c r="C150" s="419" t="s">
+        <v>432</v>
+      </c>
+      <c r="D150" s="420"/>
+      <c r="E150" s="420"/>
+      <c r="F150" s="420"/>
+      <c r="G150" s="420"/>
+      <c r="H150" s="420"/>
+      <c r="I150" s="420"/>
+      <c r="J150" s="421"/>
       <c r="K150" s="246"/>
       <c r="L150" s="246"/>
     </row>
     <row r="151" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C151" s="417"/>
-      <c r="D151" s="418"/>
-      <c r="E151" s="418"/>
-      <c r="F151" s="418"/>
-      <c r="G151" s="418"/>
-      <c r="H151" s="418"/>
-      <c r="I151" s="418"/>
-      <c r="J151" s="419"/>
+      <c r="C151" s="422"/>
+      <c r="D151" s="423"/>
+      <c r="E151" s="423"/>
+      <c r="F151" s="423"/>
+      <c r="G151" s="423"/>
+      <c r="H151" s="423"/>
+      <c r="I151" s="423"/>
+      <c r="J151" s="424"/>
       <c r="K151" s="246"/>
       <c r="L151" s="246"/>
     </row>
     <row r="152" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C152" s="420"/>
-      <c r="D152" s="421"/>
-      <c r="E152" s="421"/>
-      <c r="F152" s="421"/>
-      <c r="G152" s="421"/>
-      <c r="H152" s="421"/>
-      <c r="I152" s="421"/>
-      <c r="J152" s="422"/>
+      <c r="C152" s="425"/>
+      <c r="D152" s="426"/>
+      <c r="E152" s="426"/>
+      <c r="F152" s="426"/>
+      <c r="G152" s="426"/>
+      <c r="H152" s="426"/>
+      <c r="I152" s="426"/>
+      <c r="J152" s="427"/>
       <c r="K152" s="246"/>
       <c r="L152" s="246"/>
     </row>
@@ -19991,11 +19968,11 @@
       <c r="G157" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H157" s="412">
+      <c r="H157" s="417">
         <v>88</v>
       </c>
-      <c r="I157" s="412"/>
-      <c r="J157" s="413"/>
+      <c r="I157" s="417"/>
+      <c r="J157" s="418"/>
       <c r="K157" s="246"/>
       <c r="L157" s="246"/>
     </row>
@@ -20014,40 +19991,40 @@
       <c r="L158" s="246"/>
     </row>
     <row r="159" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C159" s="414" t="s">
-        <v>434</v>
-      </c>
-      <c r="D159" s="415"/>
-      <c r="E159" s="415"/>
-      <c r="F159" s="415"/>
-      <c r="G159" s="415"/>
-      <c r="H159" s="415"/>
-      <c r="I159" s="415"/>
-      <c r="J159" s="416"/>
+      <c r="C159" s="419" t="s">
+        <v>433</v>
+      </c>
+      <c r="D159" s="420"/>
+      <c r="E159" s="420"/>
+      <c r="F159" s="420"/>
+      <c r="G159" s="420"/>
+      <c r="H159" s="420"/>
+      <c r="I159" s="420"/>
+      <c r="J159" s="421"/>
       <c r="K159" s="246"/>
       <c r="L159" s="246"/>
     </row>
     <row r="160" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="C160" s="417"/>
-      <c r="D160" s="418"/>
-      <c r="E160" s="418"/>
-      <c r="F160" s="418"/>
-      <c r="G160" s="418"/>
-      <c r="H160" s="418"/>
-      <c r="I160" s="418"/>
-      <c r="J160" s="419"/>
+      <c r="C160" s="422"/>
+      <c r="D160" s="423"/>
+      <c r="E160" s="423"/>
+      <c r="F160" s="423"/>
+      <c r="G160" s="423"/>
+      <c r="H160" s="423"/>
+      <c r="I160" s="423"/>
+      <c r="J160" s="424"/>
       <c r="K160" s="246"/>
       <c r="L160" s="246"/>
     </row>
     <row r="161" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C161" s="420"/>
-      <c r="D161" s="421"/>
-      <c r="E161" s="421"/>
-      <c r="F161" s="421"/>
-      <c r="G161" s="421"/>
-      <c r="H161" s="421"/>
-      <c r="I161" s="421"/>
-      <c r="J161" s="422"/>
+      <c r="C161" s="425"/>
+      <c r="D161" s="426"/>
+      <c r="E161" s="426"/>
+      <c r="F161" s="426"/>
+      <c r="G161" s="426"/>
+      <c r="H161" s="426"/>
+      <c r="I161" s="426"/>
+      <c r="J161" s="427"/>
     </row>
     <row r="163" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="164" spans="3:13" x14ac:dyDescent="0.3">
@@ -20095,11 +20072,11 @@
       <c r="G166" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H166" s="412">
+      <c r="H166" s="417">
         <v>130</v>
       </c>
-      <c r="I166" s="412"/>
-      <c r="J166" s="413"/>
+      <c r="I166" s="417"/>
+      <c r="J166" s="418"/>
       <c r="K166" s="246"/>
       <c r="L166" s="246"/>
     </row>
@@ -20118,40 +20095,40 @@
       <c r="L167" s="246"/>
     </row>
     <row r="168" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C168" s="414" t="s">
-        <v>435</v>
-      </c>
-      <c r="D168" s="415"/>
-      <c r="E168" s="415"/>
-      <c r="F168" s="415"/>
-      <c r="G168" s="415"/>
-      <c r="H168" s="415"/>
-      <c r="I168" s="415"/>
-      <c r="J168" s="416"/>
+      <c r="C168" s="419" t="s">
+        <v>434</v>
+      </c>
+      <c r="D168" s="420"/>
+      <c r="E168" s="420"/>
+      <c r="F168" s="420"/>
+      <c r="G168" s="420"/>
+      <c r="H168" s="420"/>
+      <c r="I168" s="420"/>
+      <c r="J168" s="421"/>
       <c r="K168" s="246"/>
       <c r="L168" s="246"/>
     </row>
     <row r="169" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C169" s="417"/>
-      <c r="D169" s="418"/>
-      <c r="E169" s="418"/>
-      <c r="F169" s="418"/>
-      <c r="G169" s="418"/>
-      <c r="H169" s="418"/>
-      <c r="I169" s="418"/>
-      <c r="J169" s="419"/>
+      <c r="C169" s="422"/>
+      <c r="D169" s="423"/>
+      <c r="E169" s="423"/>
+      <c r="F169" s="423"/>
+      <c r="G169" s="423"/>
+      <c r="H169" s="423"/>
+      <c r="I169" s="423"/>
+      <c r="J169" s="424"/>
       <c r="K169" s="246"/>
       <c r="L169" s="246"/>
     </row>
     <row r="170" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C170" s="420"/>
-      <c r="D170" s="421"/>
-      <c r="E170" s="421"/>
-      <c r="F170" s="421"/>
-      <c r="G170" s="421"/>
-      <c r="H170" s="421"/>
-      <c r="I170" s="421"/>
-      <c r="J170" s="422"/>
+      <c r="C170" s="425"/>
+      <c r="D170" s="426"/>
+      <c r="E170" s="426"/>
+      <c r="F170" s="426"/>
+      <c r="G170" s="426"/>
+      <c r="H170" s="426"/>
+      <c r="I170" s="426"/>
+      <c r="J170" s="427"/>
     </row>
     <row r="172" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="173" spans="3:13" x14ac:dyDescent="0.3">
@@ -20200,11 +20177,11 @@
       <c r="G175" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H175" s="412">
+      <c r="H175" s="417">
         <v>61</v>
       </c>
-      <c r="I175" s="412"/>
-      <c r="J175" s="413"/>
+      <c r="I175" s="417"/>
+      <c r="J175" s="418"/>
       <c r="K175" s="246"/>
       <c r="L175" s="246"/>
       <c r="M175" s="246"/>
@@ -20225,42 +20202,42 @@
       <c r="M176" s="246"/>
     </row>
     <row r="177" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C177" s="414" t="s">
-        <v>436</v>
-      </c>
-      <c r="D177" s="415"/>
-      <c r="E177" s="415"/>
-      <c r="F177" s="415"/>
-      <c r="G177" s="415"/>
-      <c r="H177" s="415"/>
-      <c r="I177" s="415"/>
-      <c r="J177" s="416"/>
+      <c r="C177" s="419" t="s">
+        <v>435</v>
+      </c>
+      <c r="D177" s="420"/>
+      <c r="E177" s="420"/>
+      <c r="F177" s="420"/>
+      <c r="G177" s="420"/>
+      <c r="H177" s="420"/>
+      <c r="I177" s="420"/>
+      <c r="J177" s="421"/>
       <c r="K177" s="246"/>
       <c r="L177" s="246"/>
       <c r="M177" s="246"/>
     </row>
     <row r="178" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C178" s="417"/>
-      <c r="D178" s="418"/>
-      <c r="E178" s="418"/>
-      <c r="F178" s="418"/>
-      <c r="G178" s="418"/>
-      <c r="H178" s="418"/>
-      <c r="I178" s="418"/>
-      <c r="J178" s="419"/>
+      <c r="C178" s="422"/>
+      <c r="D178" s="423"/>
+      <c r="E178" s="423"/>
+      <c r="F178" s="423"/>
+      <c r="G178" s="423"/>
+      <c r="H178" s="423"/>
+      <c r="I178" s="423"/>
+      <c r="J178" s="424"/>
       <c r="K178" s="246"/>
       <c r="L178" s="246"/>
       <c r="M178" s="246"/>
     </row>
     <row r="179" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C179" s="420"/>
-      <c r="D179" s="421"/>
-      <c r="E179" s="421"/>
-      <c r="F179" s="421"/>
-      <c r="G179" s="421"/>
-      <c r="H179" s="421"/>
-      <c r="I179" s="421"/>
-      <c r="J179" s="422"/>
+      <c r="C179" s="425"/>
+      <c r="D179" s="426"/>
+      <c r="E179" s="426"/>
+      <c r="F179" s="426"/>
+      <c r="G179" s="426"/>
+      <c r="H179" s="426"/>
+      <c r="I179" s="426"/>
+      <c r="J179" s="427"/>
       <c r="K179" s="246"/>
       <c r="L179" s="246"/>
       <c r="M179" s="246"/>
@@ -20315,11 +20292,11 @@
       <c r="G184" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H184" s="412">
+      <c r="H184" s="417">
         <v>102</v>
       </c>
-      <c r="I184" s="412"/>
-      <c r="J184" s="413"/>
+      <c r="I184" s="417"/>
+      <c r="J184" s="418"/>
       <c r="K184" s="246"/>
       <c r="L184" s="246"/>
       <c r="M184" s="246"/>
@@ -20340,44 +20317,71 @@
       <c r="M185" s="246"/>
     </row>
     <row r="186" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C186" s="414" t="s">
-        <v>437</v>
-      </c>
-      <c r="D186" s="415"/>
-      <c r="E186" s="415"/>
-      <c r="F186" s="415"/>
-      <c r="G186" s="415"/>
-      <c r="H186" s="415"/>
-      <c r="I186" s="415"/>
-      <c r="J186" s="416"/>
+      <c r="C186" s="419" t="s">
+        <v>436</v>
+      </c>
+      <c r="D186" s="420"/>
+      <c r="E186" s="420"/>
+      <c r="F186" s="420"/>
+      <c r="G186" s="420"/>
+      <c r="H186" s="420"/>
+      <c r="I186" s="420"/>
+      <c r="J186" s="421"/>
       <c r="K186" s="246"/>
       <c r="L186" s="246"/>
       <c r="M186" s="246"/>
     </row>
     <row r="187" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C187" s="417"/>
-      <c r="D187" s="418"/>
-      <c r="E187" s="418"/>
-      <c r="F187" s="418"/>
-      <c r="G187" s="418"/>
-      <c r="H187" s="418"/>
-      <c r="I187" s="418"/>
-      <c r="J187" s="419"/>
+      <c r="C187" s="422"/>
+      <c r="D187" s="423"/>
+      <c r="E187" s="423"/>
+      <c r="F187" s="423"/>
+      <c r="G187" s="423"/>
+      <c r="H187" s="423"/>
+      <c r="I187" s="423"/>
+      <c r="J187" s="424"/>
     </row>
     <row r="188" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C188" s="420"/>
-      <c r="D188" s="421"/>
-      <c r="E188" s="421"/>
-      <c r="F188" s="421"/>
-      <c r="G188" s="421"/>
-      <c r="H188" s="421"/>
-      <c r="I188" s="421"/>
-      <c r="J188" s="422"/>
+      <c r="C188" s="425"/>
+      <c r="D188" s="426"/>
+      <c r="E188" s="426"/>
+      <c r="F188" s="426"/>
+      <c r="G188" s="426"/>
+      <c r="H188" s="426"/>
+      <c r="I188" s="426"/>
+      <c r="J188" s="427"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="43">
+    <mergeCell ref="C159:J161"/>
+    <mergeCell ref="H166:J166"/>
+    <mergeCell ref="H94:J94"/>
+    <mergeCell ref="C96:J98"/>
+    <mergeCell ref="H148:J148"/>
+    <mergeCell ref="C150:J152"/>
+    <mergeCell ref="H157:J157"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="C6:J8"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="C15:J17"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H175:J175"/>
+    <mergeCell ref="C177:J179"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="C33:J35"/>
+    <mergeCell ref="C24:J26"/>
+    <mergeCell ref="C60:J62"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="C42:J44"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="C51:J53"/>
+    <mergeCell ref="H58:J58"/>
+    <mergeCell ref="H103:J103"/>
+    <mergeCell ref="C105:J107"/>
+    <mergeCell ref="H112:J112"/>
+    <mergeCell ref="H67:J67"/>
+    <mergeCell ref="C69:J71"/>
     <mergeCell ref="K84:L87"/>
-    <mergeCell ref="A30:B33"/>
     <mergeCell ref="H184:J184"/>
     <mergeCell ref="C186:J188"/>
     <mergeCell ref="H76:J76"/>
@@ -20392,34 +20396,6 @@
     <mergeCell ref="H139:J139"/>
     <mergeCell ref="C141:J143"/>
     <mergeCell ref="C168:J170"/>
-    <mergeCell ref="H175:J175"/>
-    <mergeCell ref="C177:J179"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="C33:J35"/>
-    <mergeCell ref="C24:J26"/>
-    <mergeCell ref="C60:J62"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="C42:J44"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="C6:J8"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="C15:J17"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="C51:J53"/>
-    <mergeCell ref="H58:J58"/>
-    <mergeCell ref="H103:J103"/>
-    <mergeCell ref="C105:J107"/>
-    <mergeCell ref="H112:J112"/>
-    <mergeCell ref="H67:J67"/>
-    <mergeCell ref="C69:J71"/>
-    <mergeCell ref="H94:J94"/>
-    <mergeCell ref="C96:J98"/>
-    <mergeCell ref="H148:J148"/>
-    <mergeCell ref="C150:J152"/>
-    <mergeCell ref="H157:J157"/>
-    <mergeCell ref="C159:J161"/>
-    <mergeCell ref="H166:J166"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -20472,11 +20448,11 @@
       <c r="G4" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H4" s="412">
+      <c r="H4" s="417">
         <v>41</v>
       </c>
-      <c r="I4" s="412"/>
-      <c r="J4" s="413"/>
+      <c r="I4" s="417"/>
+      <c r="J4" s="418"/>
     </row>
     <row r="5" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C5" s="245" t="s">
@@ -20491,36 +20467,36 @@
       <c r="J5" s="51"/>
     </row>
     <row r="6" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C6" s="414" t="s">
+      <c r="C6" s="419" t="s">
         <v>348</v>
       </c>
-      <c r="D6" s="415"/>
-      <c r="E6" s="415"/>
-      <c r="F6" s="415"/>
-      <c r="G6" s="415"/>
-      <c r="H6" s="415"/>
-      <c r="I6" s="415"/>
-      <c r="J6" s="416"/>
+      <c r="D6" s="420"/>
+      <c r="E6" s="420"/>
+      <c r="F6" s="420"/>
+      <c r="G6" s="420"/>
+      <c r="H6" s="420"/>
+      <c r="I6" s="420"/>
+      <c r="J6" s="421"/>
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="417"/>
-      <c r="D7" s="418"/>
-      <c r="E7" s="418"/>
-      <c r="F7" s="418"/>
-      <c r="G7" s="418"/>
-      <c r="H7" s="418"/>
-      <c r="I7" s="418"/>
-      <c r="J7" s="419"/>
+      <c r="C7" s="422"/>
+      <c r="D7" s="423"/>
+      <c r="E7" s="423"/>
+      <c r="F7" s="423"/>
+      <c r="G7" s="423"/>
+      <c r="H7" s="423"/>
+      <c r="I7" s="423"/>
+      <c r="J7" s="424"/>
     </row>
     <row r="8" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="420"/>
-      <c r="D8" s="421"/>
-      <c r="E8" s="421"/>
-      <c r="F8" s="421"/>
-      <c r="G8" s="421"/>
-      <c r="H8" s="421"/>
-      <c r="I8" s="421"/>
-      <c r="J8" s="422"/>
+      <c r="C8" s="425"/>
+      <c r="D8" s="426"/>
+      <c r="E8" s="426"/>
+      <c r="F8" s="426"/>
+      <c r="G8" s="426"/>
+      <c r="H8" s="426"/>
+      <c r="I8" s="426"/>
+      <c r="J8" s="427"/>
     </row>
   </sheetData>
   <mergeCells count="2">
